--- a/docs/downloads/2026-10-22/bursa-report-2026-10-22.xlsx
+++ b/docs/downloads/2026-10-22/bursa-report-2026-10-22.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-22" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-22'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-22'!$A$1:$M$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,13 +38,13 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
+      <color rgb="00D03B3B"/>
+    </font>
+    <font>
       <color rgb="00898781"/>
     </font>
-    <font>
-      <color rgb="00D03B3B"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F3E4E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,21 +74,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -535,49 +550,57 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>7215</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NIHSIN</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.475</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0.0106</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>50459300</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="H2" t="n">
-        <v>82.48999999999999</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>4723</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>JAKS</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.0588</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>20281900</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>59.65</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0.294</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" s="7" t="inlineStr"/>
+      <c r="J2" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 59.65未超买，现价高于50日均线约25%，技术面信号较为可靠。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -595,34 +618,34 @@
           <t>ZETRIX</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>33776100</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.09</v>
+      <c r="D3" s="9" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>50010600</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>0.14</v>
       </c>
       <c r="H3" t="n">
-        <v>23.85</v>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
+        <v>25.86</v>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="K3" s="2" t="n">
+      <c r="J3" s="9" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="K3" s="9" t="n">
         <v>0.284</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="7" t="inlineStr"/>
+      <c r="M3" s="14" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -632,42 +655,33 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GIIB</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.0142</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>22797800</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H4" t="n">
-        <v>81.19</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0.543</v>
-      </c>
+          <t>0479.KL</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>38312800</v>
+      </c>
+      <c r="G4" s="12" t="n"/>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="9" t="n"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="7" t="inlineStr"/>
+      <c r="M4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -677,42 +691,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0200</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>JAKS</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>3998900</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.07000000000000001</v>
+          <t>REVENUE</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>12933000</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>33.18</v>
       </c>
       <c r="H5" t="n">
-        <v>56.15</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
+        <v>77.75</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0.144</v>
+      <c r="J5" s="9" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0.076</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr"/>
+      <c r="M5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -722,45 +736,1573 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>0069</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>VINVEST</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>11478000</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>30.23</v>
+      </c>
+      <c r="H6" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6963</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>8967200</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H7" t="n">
+        <v>68.67</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>7192</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>7130500</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H8" t="n">
+        <v>81.19</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7215</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>-0.0211</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>6024900</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H9" t="n">
+        <v>77.25</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0.0242</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>4353500</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H10" t="n">
+        <v>62.65</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>1.966</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>1.777</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0301</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ZANTAT</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0.1176</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>3978300</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="H11" t="n">
+        <v>73.61</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0175</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HHRG</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>3930000</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>41.65</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0.136</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>7113</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TOPGLOV</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>-0.005500000000000001</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>3371700</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>65.26000000000001</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>2540000</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H14" t="n">
+        <v>50.43</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>2255900</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>56.54</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>2160500</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H16" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>1.622</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>1.902</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0024</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>JAG</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>1972600</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H17" t="n">
+        <v>61.3</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>1801500</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H18" t="n">
+        <v>37.99</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0198</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>GDB</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>-0.0297</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>1583700</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0193</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>KINERGY</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>1566200</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H20" t="n">
+        <v>24.34</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0.0339</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>1359800</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="H21" t="n">
+        <v>51.49</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0.912</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5259</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AVANGAAD</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>1308000</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H22" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0181</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AEMULUS</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>1289400</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H23" t="n">
+        <v>57.28</v>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0471</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PIONEER</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H24" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="K24" s="9" t="n"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>1191500</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H25" t="n">
+        <v>46.02</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>2.041</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>2.067</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>1113700</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H26" t="n">
+        <v>88.28</v>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>2.961</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>2.515</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>9679</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>WCT</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0.0357</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>1062900</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H27" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0.0117</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>1033400</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>1012400</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H29" t="n">
+        <v>59.68</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>994200</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H30" t="n">
+        <v>70.66</v>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>899000</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>42.75</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>1.026</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>883600</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H32" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>869000</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H33" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>-0.006999999999999999</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>852000</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H34" t="n">
+        <v>46.46</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>752900</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H35" t="n">
+        <v>51.02</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>751400</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H36" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>673000</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H37" t="n">
+        <v>47.65</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>2.561</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>608900</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H38" t="n">
+        <v>56.09</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>1.364</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>596300</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H39" t="n">
+        <v>68.73</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>0112</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>MIKROMB</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D40" s="9" t="n">
         <v>0.655</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E40" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>593600</v>
-      </c>
-      <c r="G6" s="5" t="n">
+      <c r="F40" s="11" t="n">
+        <v>594200</v>
+      </c>
+      <c r="G40" s="12" t="n">
         <v>0.27</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H40" t="n">
         <v>61.54</v>
       </c>
-      <c r="I6" s="6" t="inlineStr">
+      <c r="I40" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
+      <c r="J40" s="9" t="n">
         <v>0.64</v>
       </c>
-      <c r="K6" s="2" t="n">
+      <c r="K40" s="9" t="n">
         <v>0.627</v>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" s="7" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M6"/>
+  <autoFilter ref="A1:M40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-22/bursa-report-2026-10-22.xlsx
+++ b/docs/downloads/2026-10-22/bursa-report-2026-10-22.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-22" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-22'!$A$1:$M$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-22'!$A$1:$M$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,10 +38,10 @@
       <color rgb="000CA30C"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="00898781"/>
     </font>
     <font>
-      <color rgb="00898781"/>
+      <color rgb="00D03B3B"/>
     </font>
   </fonts>
   <fills count="4">
@@ -89,16 +89,16 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -557,95 +557,103 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.0992</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>2516700</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>1.097</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 60.75未超买，现价高于50日均线约21%，技术面信号偏可靠。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>4723</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>JAKS</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>0.0588</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>20281900</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>59.65</v>
-      </c>
-      <c r="I2" s="7" t="inlineStr">
+      <c r="D3" s="3" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>27748900</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>57.97</v>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="J3" s="3" t="n">
         <v>0.16</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K3" s="3" t="n">
         <v>0.144</v>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>🎯 SAR 转多</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr">
-        <is>
-          <t>SAR转多信号，RSI 59.65未超买，现价高于50日均线约25%，技术面信号较为可靠。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E3" s="10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F3" s="11" t="n">
-        <v>50010600</v>
-      </c>
-      <c r="G3" s="12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H3" t="n">
-        <v>25.86</v>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="K3" s="9" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" s="14" t="inlineStr"/>
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 57.97未超买，现价高于50日均线约21.5%，技术面信号较为可靠。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -655,31 +663,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0479.KL</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E4" s="15" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E4" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>38312800</v>
-      </c>
-      <c r="G4" s="12" t="n"/>
+        <v>52425300</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H4" t="n">
+        <v>23.85</v>
+      </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>0.284</v>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
     </row>
@@ -691,40 +708,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0200</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>REVENUE</t>
+          <t>0479.KL</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.09</v>
+        <v>0.28</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>12933000</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>33.18</v>
-      </c>
-      <c r="H5" t="n">
-        <v>77.75</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="n">
-        <v>0.077</v>
-      </c>
-      <c r="K5" s="9" t="n">
-        <v>0.076</v>
-      </c>
+        <v>49922200</v>
+      </c>
+      <c r="G5" s="12" t="n"/>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="9" t="n"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
     </row>
@@ -736,28 +744,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0069</t>
+          <t>0200</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VINVEST</t>
+          <t>REVENUE</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>0.3333</v>
+        <v>0.09</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>0.2</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>11478000</v>
+        <v>17920500</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>30.23</v>
+        <v>45.97</v>
       </c>
       <c r="H6" t="n">
-        <v>58.17</v>
+        <v>77.75</v>
       </c>
       <c r="I6" s="16" t="inlineStr">
         <is>
@@ -765,10 +773,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.016</v>
+        <v>0.077</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.017</v>
+        <v>0.076</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -781,39 +789,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0069</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>VINVEST</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>0.0145</v>
+        <v>0.02</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.3333</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>8967200</v>
+        <v>12930600</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.11</v>
+        <v>34.06</v>
       </c>
       <c r="H7" t="n">
-        <v>68.67</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.17</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.315</v>
+        <v>0.016</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.263</v>
+        <v>0.017</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -837,14 +845,14 @@
       <c r="D8" s="9" t="n">
         <v>0.715</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>7130500</v>
+        <v>12102700</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.28</v>
+        <v>0.48</v>
       </c>
       <c r="H8" t="n">
         <v>81.19</v>
@@ -871,39 +879,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>-0.0211</v>
+        <v>0.345</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>6024900</v>
+        <v>11448000</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="H9" t="n">
-        <v>77.25</v>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>67.47</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.407</v>
+        <v>0.314</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.302</v>
+        <v>0.263</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -916,28 +924,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0.0242</v>
+        <v>0.47</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>4353500</v>
+        <v>9122600</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="H10" t="n">
-        <v>62.65</v>
+        <v>79.78</v>
       </c>
       <c r="I10" s="16" t="inlineStr">
         <is>
@@ -945,10 +953,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1.966</v>
+        <v>0.407</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>1.777</v>
+        <v>0.302</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -961,39 +969,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ZANTAT</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0.1176</v>
+        <v>0.125</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>0.08699999999999999</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3978300</v>
+        <v>7437200</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>16.28</v>
+        <v>0.38</v>
       </c>
       <c r="H11" t="n">
-        <v>73.61</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.65</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.158</v>
+        <v>0.136</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.156</v>
+        <v>0.148</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1006,39 +1014,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0.08699999999999999</v>
+        <v>2.1</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>0.0145</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>3930000</v>
+        <v>6949600</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="H12" t="n">
-        <v>41.65</v>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.76</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.136</v>
+        <v>1.964</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.148</v>
+        <v>1.777</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1051,39 +1059,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>-0.005500000000000001</v>
+        <v>0.295</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>3371700</v>
+        <v>6114500</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.05</v>
+        <v>1.81</v>
       </c>
       <c r="H13" t="n">
-        <v>65.26000000000001</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.848</v>
+        <v>0.295</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.753</v>
+        <v>0.295</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1096,39 +1104,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.775</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>2540000</v>
+        <v>5637800</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.16</v>
+        <v>3.07</v>
       </c>
       <c r="H14" t="n">
-        <v>50.43</v>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.05</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.774</v>
+        <v>0.837</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.776</v>
+        <v>0.858</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1141,39 +1149,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>ZANTAT</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0.023</v>
+        <v>0.18</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>2255900</v>
+        <v>4650600</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.5</v>
+        <v>19.03</v>
       </c>
       <c r="H15" t="n">
-        <v>56.54</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.59999999999999</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.854</v>
+        <v>0.157</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.611</v>
+        <v>0.156</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1186,39 +1194,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1.4</v>
+        <v>0.905</v>
       </c>
       <c r="E16" s="17" t="n">
-        <v>-0.021</v>
+        <v>-0.005500000000000001</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>2160500</v>
+        <v>3753600</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
       <c r="H16" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.26000000000001</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1.622</v>
+        <v>0.848</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>1.902</v>
+        <v>0.753</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1231,28 +1239,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0.0133</v>
+        <v>0.775</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>1972600</v>
+        <v>3410000</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="H17" t="n">
-        <v>61.3</v>
+        <v>50.43</v>
       </c>
       <c r="I17" s="16" t="inlineStr">
         <is>
@@ -1260,10 +1268,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.372</v>
+        <v>0.774</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.37</v>
+        <v>0.776</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1276,28 +1284,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.43</v>
+        <v>0.155</v>
       </c>
       <c r="E18" s="15" t="n">
-        <v>0</v>
+        <v>0.0333</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>1801500</v>
+        <v>3299500</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.05</v>
+        <v>0.23</v>
       </c>
       <c r="H18" t="n">
-        <v>37.99</v>
+        <v>43.61</v>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
@@ -1305,10 +1313,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.464</v>
+        <v>0.155</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.478</v>
+        <v>0.182</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1321,40 +1329,33 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.49</v>
+        <v>0.25</v>
       </c>
       <c r="E19" s="17" t="n">
-        <v>-0.0297</v>
+        <v>-0.0196</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1583700</v>
+        <v>2987500</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="H19" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="K19" s="9" t="n">
-        <v>0.435</v>
-      </c>
+        <v>0.14</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="n"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
     </row>
@@ -1366,39 +1367,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.38</v>
+        <v>0.29</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>0</v>
+        <v>0.0357</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>1566200</v>
+        <v>2835100</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.17</v>
+        <v>0.45</v>
       </c>
       <c r="H20" t="n">
-        <v>24.34</v>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.67</v>
+      </c>
+      <c r="I20" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.393</v>
+        <v>0.319</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.405</v>
+        <v>0.363</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1411,28 +1412,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0.0339</v>
+        <v>1.41</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>-0.014</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1359800</v>
+        <v>2815400</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.77</v>
+        <v>0.24</v>
       </c>
       <c r="H21" t="n">
-        <v>51.49</v>
+        <v>20.85</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -1440,10 +1441,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.912</v>
+        <v>1.623</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.886</v>
+        <v>1.903</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1456,28 +1457,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E22" s="15" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="E22" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>1308000</v>
+        <v>2730000</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.39</v>
+        <v>0.14</v>
       </c>
       <c r="H22" t="n">
-        <v>49.23</v>
+        <v>47.42</v>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
@@ -1485,10 +1486,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.295</v>
+        <v>0.308</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.295</v>
+        <v>0.301</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1501,28 +1502,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>0</v>
+        <v>0.495</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>-0.0198</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>1289400</v>
+        <v>2485000</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.18</v>
+        <v>0.88</v>
       </c>
       <c r="H23" t="n">
-        <v>57.28</v>
+        <v>72.97</v>
       </c>
       <c r="I23" s="16" t="inlineStr">
         <is>
@@ -1530,10 +1531,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.429</v>
+        <v>0.436</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.418</v>
+        <v>0.435</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1546,38 +1547,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0.0133</v>
+        <v>0.865</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>1200000</v>
+        <v>2465500</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.21</v>
+        <v>0.55</v>
       </c>
       <c r="H24" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.99</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="K24" s="9" t="n"/>
+        <v>0.851</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>0.61</v>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
     </row>
@@ -1589,28 +1592,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>2.03</v>
+        <v>0.915</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>0</v>
+        <v>0.0339</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1191500</v>
+        <v>2404800</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.34</v>
+        <v>1.36</v>
       </c>
       <c r="H25" t="n">
-        <v>46.02</v>
+        <v>51.49</v>
       </c>
       <c r="I25" s="13" t="inlineStr">
         <is>
@@ -1618,10 +1621,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>2.041</v>
+        <v>0.912</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>2.067</v>
+        <v>0.886</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1634,39 +1637,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0.003</v>
+        <v>2.02</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1113700</v>
+        <v>2295200</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.35</v>
+        <v>0.66</v>
       </c>
       <c r="H26" t="n">
-        <v>88.28</v>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.07</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>2.961</v>
+        <v>2.04</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2.515</v>
+        <v>2.066</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1679,39 +1682,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0.0357</v>
+        <v>0.38</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>1062900</v>
+        <v>2282000</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.17</v>
+        <v>0.32</v>
       </c>
       <c r="H27" t="n">
-        <v>33.67</v>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.3</v>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.319</v>
+        <v>0.372</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.363</v>
+        <v>0.37</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1724,39 +1727,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0.0117</v>
+        <v>0.995</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>0.0311</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1033400</v>
+        <v>1915100</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
       <c r="H28" t="n">
-        <v>33.08</v>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.38</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.899</v>
+        <v>1.028</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.963</v>
+        <v>0.974</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1769,28 +1772,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.625</v>
+        <v>0.43</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>0.0163</v>
+        <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1012400</v>
+        <v>1888600</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.16</v>
+        <v>0.05</v>
       </c>
       <c r="H29" t="n">
-        <v>59.68</v>
+        <v>37.99</v>
       </c>
       <c r="I29" s="13" t="inlineStr">
         <is>
@@ -1798,10 +1801,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.579</v>
+        <v>0.464</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.48</v>
+        <v>0.478</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1814,28 +1817,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.625</v>
+        <v>0.63</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>0.0163</v>
+        <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>994200</v>
+        <v>1693500</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="H30" t="n">
-        <v>70.66</v>
+        <v>58.13</v>
       </c>
       <c r="I30" s="16" t="inlineStr">
         <is>
@@ -1843,10 +1846,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.535</v>
+        <v>0.621</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.48</v>
+        <v>0.617</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1859,39 +1862,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0.0052</v>
+        <v>0.435</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>0.0235</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>899000</v>
+        <v>1638600</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="H31" t="n">
-        <v>42.75</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.51</v>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>1.026</v>
+        <v>0.4</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.974</v>
+        <v>0.382</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1904,39 +1907,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E32" s="15" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E32" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>883600</v>
+        <v>1603300</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1.41</v>
+        <v>0.18</v>
       </c>
       <c r="H32" t="n">
-        <v>57.63</v>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.34</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>1.009</v>
+        <v>0.393</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.987</v>
+        <v>0.405</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1949,28 +1952,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.77</v>
+        <v>0.575</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>869000</v>
+        <v>1565200</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="H33" t="n">
-        <v>49.92</v>
+        <v>52.07</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1978,10 +1981,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.77</v>
+        <v>0.572</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.771</v>
+        <v>0.545</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1994,39 +1997,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E34" s="17" t="n">
-        <v>-0.006999999999999999</v>
+        <v>3.37</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>0.003</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>852000</v>
+        <v>1553900</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.06</v>
+        <v>0.48</v>
       </c>
       <c r="H34" t="n">
-        <v>46.46</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>88.28</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.734</v>
+        <v>2.961</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.723</v>
+        <v>2.515</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2039,28 +2042,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E35" s="17" t="n">
-        <v>-0.008699999999999999</v>
+        <v>0.62</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>752900</v>
+        <v>1486600</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.04</v>
+        <v>0.24</v>
       </c>
       <c r="H35" t="n">
-        <v>51.02</v>
+        <v>59.15</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2068,10 +2071,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.572</v>
+        <v>0.578</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.545</v>
+        <v>0.48</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2084,39 +2087,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.625</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0.0163</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>751400</v>
+        <v>1472400</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.08</v>
+        <v>0.33</v>
       </c>
       <c r="H36" t="n">
-        <v>41.07</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.66</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.624</v>
+        <v>0.535</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.619</v>
+        <v>0.48</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2129,39 +2132,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>0</v>
+        <v>0.24</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>673000</v>
+        <v>1421000</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.04</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>47.65</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.79000000000001</v>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>2.625</v>
+        <v>0.216</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>2.561</v>
+        <v>0.211</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2174,28 +2177,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0.0147</v>
+        <v>6.92</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>608900</v>
+        <v>1399700</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.3</v>
+        <v>0.13</v>
       </c>
       <c r="H38" t="n">
-        <v>56.09</v>
+        <v>39.44</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2203,10 +2206,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>1.364</v>
+        <v>7.116</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1.343</v>
+        <v>7.541</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2219,28 +2222,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.825</v>
+        <v>0.46</v>
       </c>
       <c r="E39" s="15" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>596300</v>
+        <v>1385500</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="H39" t="n">
-        <v>68.73</v>
+        <v>58.23</v>
       </c>
       <c r="I39" s="16" t="inlineStr">
         <is>
@@ -2248,10 +2251,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.801</v>
+        <v>0.43</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.776</v>
+        <v>0.418</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2264,45 +2267,1881 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E40" s="15" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E40" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>594200</v>
+        <v>1336800</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="H40" t="n">
-        <v>61.54</v>
-      </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.56</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.64</v>
+        <v>0.769</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.627</v>
+        <v>0.771</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0471</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PIONEER</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>0.0133</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>1304600</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H41" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="K41" s="9" t="n"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>1260600</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H42" t="n">
+        <v>39.45</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>1205800</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>47.03</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>2.624</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>2.561</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="14" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0.0175</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>1170700</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H44" t="n">
+        <v>35.11</v>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="14" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>1124200</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H45" t="n">
+        <v>48.52</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="14" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0367</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ENPRO</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>1060900</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H46" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="14" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>1043800</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H47" t="n">
+        <v>55.59</v>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="14" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>1037700</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H48" t="n">
+        <v>68.73</v>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>0.801</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>1034600</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H49" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>3557</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ECOFIRS</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>-0.0313</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>1008400</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="H50" t="n">
+        <v>39.44</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>-0.008100000000000001</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>941400</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H51" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>7.421</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>7.866</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>901500</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H52" t="n">
+        <v>48.55</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>4.729</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>4.826</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>883600</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H53" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="14" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>-0.0051</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>846500</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H54" t="n">
+        <v>52.71</v>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>1.929</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>1.952</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>835400</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H55" t="n">
+        <v>46.79</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>4.875</v>
+      </c>
+      <c r="K55" s="9" t="n">
+        <v>4.749</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="14" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>796700</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H56" t="n">
+        <v>55.78</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="K56" s="9" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="14" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0477</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ECOSYS</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>-0.0129</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>775600</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="n"/>
+      <c r="K57" s="9" t="n"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="14" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>0.0256</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>768500</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H58" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>1.084</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>0.945</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>0.0318</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>765100</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H59" t="n">
+        <v>25.48</v>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K59" s="9" t="n">
+        <v>1.055</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="14" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>0.0327</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>749500</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H60" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="K60" s="9" t="n">
+        <v>3.608</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>8052</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>CGB</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E61" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>748000</v>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H61" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K61" s="9" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>711700</v>
+      </c>
+      <c r="G62" s="12" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H62" t="n">
+        <v>75.20999999999999</v>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K62" s="9" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="14" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>0.0083</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>696600</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H63" t="n">
+        <v>35.35</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>2.698</v>
+      </c>
+      <c r="K63" s="9" t="n">
+        <v>2.856</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="14" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>0.0014</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>684900</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H64" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>7.412</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>7.648</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="14" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>651100</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H65" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="K65" s="9" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="14" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>647900</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H66" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>1.341</v>
+      </c>
+      <c r="K66" s="9" t="n">
+        <v>1.528</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="14" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>647100</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H67" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>5.455</v>
+      </c>
+      <c r="K67" s="9" t="n">
+        <v>5.496</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="14" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E68" s="17" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>644200</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H68" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="I68" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="K68" s="9" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="14" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>631900</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H69" t="n">
+        <v>53.13</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>1.363</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="14" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>623800</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H70" t="n">
+        <v>39.63</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>2.123</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="14" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>-0.0036</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>614800</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H71" t="n">
+        <v>41.09</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>2.862</v>
+      </c>
+      <c r="K71" s="9" t="n">
+        <v>2.992</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="14" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>596500</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H72" t="n">
+        <v>41.89</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="K72" s="9" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="14" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>593100</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H73" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>0.663</v>
+      </c>
+      <c r="K73" s="9" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="14" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>585200</v>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H74" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>1.216</v>
+      </c>
+      <c r="K74" s="9" t="n">
+        <v>1.304</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="14" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>-0.0106</v>
+      </c>
+      <c r="F75" s="11" t="n">
+        <v>581000</v>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H75" t="n">
+        <v>56.86</v>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>6.268</v>
+      </c>
+      <c r="K75" s="9" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="14" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>WPRTS</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>0.0222</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>577600</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H76" t="n">
+        <v>61.32</v>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>6.772</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>6.821</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="14" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E77" s="17" t="n">
+        <v>-0.0252</v>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>561500</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H77" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="K77" s="9" t="n">
+        <v>1.752</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="14" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>539300</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H78" t="n">
+        <v>58.51</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="K78" s="9" t="n">
+        <v>1.183</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="14" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E79" s="15" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F79" s="11" t="n">
+        <v>538000</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H79" t="n">
+        <v>53.23</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K79" s="9" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="14" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>524700</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H80" t="n">
+        <v>51.46</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="K80" s="9" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="14" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F81" s="11" t="n">
+        <v>518100</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H81" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="I81" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K81" s="9" t="n">
+        <v>10.121</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M40"/>
+  <autoFilter ref="A1:M81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-22/bursa-report-2026-10-22.xlsx
+++ b/docs/downloads/2026-10-22/bursa-report-2026-10-22.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-22" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-22'!$A$1:$M$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-22'!$A$1:$M$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0992</v>
+        <v>0.1074</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>2516700</v>
+        <v>5318900</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>60.75</v>
+        <v>61.4</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.24</v>
+        <v>1.241</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>1.097</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 60.75未超买，现价高于50日均线约21%，技术面信号偏可靠。</t>
+          <t>SAR转多信号，RSI 61.4未超买，现价高于50日均线约22%，技术面信号偏可靠。</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>0.0294</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>27748900</v>
+        <v>30649900</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>57.97</v>
@@ -663,40 +663,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>0479.KL</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.05</v>
+        <v>0.285</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>52425300</v>
-      </c>
-      <c r="G4" s="12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H4" t="n">
-        <v>23.85</v>
-      </c>
+        <v>58205900</v>
+      </c>
+      <c r="G4" s="12" t="n"/>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="n">
-        <v>0.104</v>
-      </c>
-      <c r="K4" s="9" t="n">
-        <v>0.284</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="9" t="n"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
     </row>
@@ -708,31 +699,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0479.KL</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>0</v>
+        <v>0.055</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0.1</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>49922200</v>
-      </c>
-      <c r="G5" s="12" t="n"/>
+        <v>55913200</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H5" t="n">
+        <v>25.86</v>
+      </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="9" t="n"/>
-      <c r="K5" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0.284</v>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
     </row>
@@ -759,10 +759,10 @@
         <v>0.2</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>17920500</v>
+        <v>18671700</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>45.97</v>
+        <v>47.9</v>
       </c>
       <c r="H6" t="n">
         <v>77.75</v>
@@ -789,28 +789,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0069</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VINVEST</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.3333</v>
+        <v>0.47</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>-0.0105</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>12930600</v>
+        <v>13328100</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>34.06</v>
+        <v>0.37</v>
       </c>
       <c r="H7" t="n">
-        <v>58.17</v>
+        <v>79.78</v>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.016</v>
+        <v>0.407</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.017</v>
+        <v>0.302</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -834,28 +834,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0069</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>VINVEST</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0</v>
+        <v>0.02</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0.3333</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>12102700</v>
+        <v>13304800</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.48</v>
+        <v>35.04</v>
       </c>
       <c r="H8" t="n">
-        <v>81.19</v>
+        <v>58.17</v>
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
@@ -863,10 +863,10 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.642</v>
+        <v>0.016</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.548</v>
+        <v>0.017</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -879,39 +879,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.345</v>
+        <v>0.715</v>
       </c>
       <c r="E9" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>11448000</v>
+        <v>12314800</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.14</v>
+        <v>0.49</v>
       </c>
       <c r="H9" t="n">
-        <v>67.47</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.19</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.314</v>
+        <v>0.642</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.263</v>
+        <v>0.548</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -924,39 +924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <v>-0.0105</v>
+        <v>0.345</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>9122600</v>
+        <v>12299800</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="H10" t="n">
-        <v>79.78</v>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>67.47</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.407</v>
+        <v>0.314</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.302</v>
+        <v>0.263</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -969,40 +969,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.24</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>-0.0588</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>7437200</v>
+        <v>8474000</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="H11" t="n">
-        <v>41.65</v>
+        <v>0.39</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J11" s="9" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="K11" s="9" t="n">
-        <v>0.148</v>
-      </c>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="9" t="n"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
     </row>
@@ -1023,19 +1016,19 @@
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>0.0145</v>
+        <v>0.0048</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>6949600</v>
+        <v>8339800</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="H12" t="n">
-        <v>61.76</v>
+        <v>60.83</v>
       </c>
       <c r="I12" s="16" t="inlineStr">
         <is>
@@ -1043,7 +1036,7 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.964</v>
+        <v>1.962</v>
       </c>
       <c r="K12" s="9" t="n">
         <v>1.777</v>
@@ -1059,28 +1052,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0</v>
+        <v>0.125</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>0.08699999999999999</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>6114500</v>
+        <v>7642300</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>1.81</v>
+        <v>0.39</v>
       </c>
       <c r="H13" t="n">
-        <v>49.23</v>
+        <v>41.65</v>
       </c>
       <c r="I13" s="13" t="inlineStr">
         <is>
@@ -1088,10 +1081,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.295</v>
+        <v>0.136</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.295</v>
+        <v>0.148</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1119,10 +1112,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>5637800</v>
+        <v>6154700</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>3.07</v>
+        <v>3.35</v>
       </c>
       <c r="H14" t="n">
         <v>33.05</v>
@@ -1149,39 +1142,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ZANTAT</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>0.0588</v>
+        <v>0.295</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>4650600</v>
+        <v>6114500</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>19.03</v>
+        <v>1.81</v>
       </c>
       <c r="H15" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.157</v>
+        <v>0.295</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.156</v>
+        <v>0.295</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1194,39 +1187,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>-0.005500000000000001</v>
+        <v>0.18</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>3753600</v>
+        <v>5646100</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.05</v>
+        <v>0.27</v>
       </c>
       <c r="H16" t="n">
-        <v>65.26000000000001</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.12</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.848</v>
+        <v>0.187</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.753</v>
+        <v>0.186</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1239,28 +1232,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.895</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>3410000</v>
+        <v>5455100</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>50.43</v>
+        <v>62.96</v>
       </c>
       <c r="I17" s="16" t="inlineStr">
         <is>
@@ -1268,10 +1261,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.774</v>
+        <v>0.847</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.776</v>
+        <v>0.753</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1284,39 +1277,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>ZANTAT</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>0.0333</v>
+        <v>0.17</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>3299500</v>
+        <v>5407900</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.23</v>
+        <v>22.13</v>
       </c>
       <c r="H18" t="n">
-        <v>43.61</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.15000000000001</v>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.155</v>
+        <v>0.156</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.182</v>
+        <v>0.156</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1329,33 +1322,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>-0.0196</v>
+        <v>0.775</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>2987500</v>
+        <v>4850000</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="9" t="n"/>
+        <v>0.31</v>
+      </c>
+      <c r="H19" t="n">
+        <v>50.43</v>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>0.776</v>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
     </row>
@@ -1367,39 +1367,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.29</v>
+        <v>0.995</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>0.0357</v>
+        <v>0.0311</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>2835100</v>
+        <v>4361300</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.45</v>
+        <v>0.49</v>
       </c>
       <c r="H20" t="n">
-        <v>33.67</v>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.38</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.319</v>
+        <v>1.028</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.363</v>
+        <v>0.974</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1412,28 +1412,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>-0.014</v>
+        <v>0.305</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2815400</v>
+        <v>3940000</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="H21" t="n">
-        <v>20.85</v>
+        <v>47.42</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -1441,10 +1441,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>1.623</v>
+        <v>0.308</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>1.903</v>
+        <v>0.301</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1457,28 +1457,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>0</v>
+        <v>0.425</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>-0.0116</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>2730000</v>
+        <v>3827700</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.14</v>
+        <v>0.1</v>
       </c>
       <c r="H22" t="n">
-        <v>47.42</v>
+        <v>36.88</v>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.308</v>
+        <v>0.463</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.301</v>
+        <v>0.478</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1502,39 +1502,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.495</v>
+        <v>0.255</v>
       </c>
       <c r="E23" s="17" t="n">
-        <v>-0.0198</v>
+        <v>-0.0192</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>2485000</v>
+        <v>3780100</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.88</v>
+        <v>0.47</v>
       </c>
       <c r="H23" t="n">
-        <v>72.97</v>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.436</v>
+        <v>0.271</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.435</v>
+        <v>0.296</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1547,28 +1547,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.155</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>2465500</v>
+        <v>3472100</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.55</v>
+        <v>0.24</v>
       </c>
       <c r="H24" t="n">
-        <v>54.99</v>
+        <v>43.61</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -1576,10 +1576,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.851</v>
+        <v>0.155</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.61</v>
+        <v>0.182</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1592,39 +1592,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.915</v>
+        <v>0.285</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>0.0339</v>
+        <v>0.0179</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>2404800</v>
+        <v>3276200</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>1.36</v>
+        <v>0.52</v>
       </c>
       <c r="H25" t="n">
-        <v>51.49</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>31.02</v>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.912</v>
+        <v>0.318</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.886</v>
+        <v>0.363</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1637,28 +1637,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>2.02</v>
+        <v>0.85</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>-0.0049</v>
+        <v>-0.023</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>2295200</v>
+        <v>3248400</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.66</v>
+        <v>0.72</v>
       </c>
       <c r="H26" t="n">
-        <v>44.07</v>
+        <v>53.9</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>2.04</v>
+        <v>0.85</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2.066</v>
+        <v>0.61</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1682,39 +1682,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>0.0133</v>
+        <v>1.4</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>-0.021</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>2282000</v>
+        <v>3190200</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.32</v>
+        <v>0.27</v>
       </c>
       <c r="H27" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>20.45</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.372</v>
+        <v>1.622</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.37</v>
+        <v>1.902</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1727,39 +1727,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.995</v>
+        <v>0.43</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>0.0311</v>
+        <v>0.0118</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1915100</v>
+        <v>3014600</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="H28" t="n">
-        <v>46.38</v>
-      </c>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.36</v>
+      </c>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1.028</v>
+        <v>0.4</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.974</v>
+        <v>0.381</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1772,39 +1772,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.43</v>
+        <v>0.375</v>
       </c>
       <c r="E29" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1888600</v>
+        <v>2933300</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.05</v>
+        <v>0.41</v>
       </c>
       <c r="H29" t="n">
-        <v>37.99</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.91</v>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.464</v>
+        <v>0.372</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.478</v>
+        <v>0.37</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1817,28 +1817,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.63</v>
+        <v>0.865</v>
       </c>
       <c r="E30" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>1693500</v>
+        <v>2924300</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="H30" t="n">
-        <v>58.13</v>
+        <v>46.09</v>
       </c>
       <c r="I30" s="16" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.621</v>
+        <v>0.868</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.617</v>
+        <v>0.869</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1862,39 +1862,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.435</v>
+        <v>0.91</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>0.0235</v>
+        <v>0.0282</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>1638600</v>
+        <v>2741200</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.14</v>
+        <v>1.55</v>
       </c>
       <c r="H31" t="n">
-        <v>62.51</v>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.73</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.4</v>
+        <v>0.911</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.382</v>
+        <v>0.886</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1907,39 +1907,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.38</v>
+        <v>0.63</v>
       </c>
       <c r="E32" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>1603300</v>
+        <v>2690100</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="H32" t="n">
-        <v>24.34</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.13</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.393</v>
+        <v>0.621</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.405</v>
+        <v>0.617</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1952,39 +1952,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>0</v>
+        <v>0.5</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1565200</v>
+        <v>2622900</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.08</v>
+        <v>0.92</v>
       </c>
       <c r="H33" t="n">
-        <v>52.07</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.63</v>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.572</v>
+        <v>0.436</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.545</v>
+        <v>0.435</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1997,28 +1997,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>3.37</v>
+        <v>1.99</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>0.003</v>
+        <v>0.0153</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>1553900</v>
+        <v>2551800</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
       <c r="H34" t="n">
-        <v>88.28</v>
+        <v>58.08</v>
       </c>
       <c r="I34" s="16" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>2.961</v>
+        <v>1.933</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>2.515</v>
+        <v>1.953</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2042,28 +2042,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.62</v>
+        <v>5.35</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0019</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1486600</v>
+        <v>2479000</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="H35" t="n">
-        <v>59.15</v>
+        <v>44.58</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.578</v>
+        <v>5.463</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.48</v>
+        <v>5.498</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2087,39 +2087,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>0.0163</v>
+        <v>0.265</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>-0.0364</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>1472400</v>
+        <v>2458900</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.33</v>
+        <v>0.23</v>
       </c>
       <c r="H36" t="n">
-        <v>70.66</v>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.76</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.535</v>
+        <v>0.29</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.48</v>
+        <v>0.28</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2132,39 +2132,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.24</v>
+        <v>2.56</v>
       </c>
       <c r="E37" s="17" t="n">
-        <v>-0.0204</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>1421000</v>
+        <v>2445800</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>1</v>
+        <v>0.13</v>
       </c>
       <c r="H37" t="n">
-        <v>76.79000000000001</v>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.42</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.216</v>
+        <v>2.623</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.211</v>
+        <v>2.561</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2177,28 +2177,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <v>0.008699999999999999</v>
+        <v>2.03</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1399700</v>
+        <v>2396300</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.13</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>39.44</v>
+        <v>46.02</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>7.116</v>
+        <v>2.041</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>7.541</v>
+        <v>2.067</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2222,28 +2222,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>0.011</v>
+        <v>0.82</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1385500</v>
+        <v>2268800</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="H39" t="n">
-        <v>58.23</v>
+        <v>55.59</v>
       </c>
       <c r="I39" s="16" t="inlineStr">
         <is>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.43</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.418</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2267,28 +2267,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <v>0</v>
+        <v>2.06</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>1336800</v>
+        <v>2240200</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="H40" t="n">
-        <v>48.56</v>
+        <v>39.63</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.769</v>
+        <v>2.123</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.771</v>
+        <v>2.235</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2312,38 +2312,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>0.0133</v>
+        <v>0.435</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>-0.0114</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1304600</v>
+        <v>2010900</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.23</v>
+        <v>0.1</v>
       </c>
       <c r="H41" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="I41" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.06</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="K41" s="9" t="n"/>
+        <v>0.427</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>0.378</v>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
     </row>
@@ -2355,40 +2357,38 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.365</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0267</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1260600</v>
+        <v>1992000</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
       <c r="H42" t="n">
-        <v>39.45</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.46</v>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.623</v>
-      </c>
-      <c r="K42" s="9" t="n">
-        <v>0.618</v>
-      </c>
+        <v>0.333</v>
+      </c>
+      <c r="K42" s="9" t="n"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
     </row>
@@ -2400,39 +2400,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>-0.0039</v>
+        <v>3.38</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>0.006</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1205800</v>
+        <v>1959500</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.61</v>
       </c>
       <c r="H43" t="n">
-        <v>47.03</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>88.44</v>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>2.624</v>
+        <v>2.962</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>2.561</v>
+        <v>2.515</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2445,39 +2445,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.87</v>
+        <v>6.92</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>0.0175</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1170700</v>
+        <v>1953000</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.34</v>
+        <v>0.18</v>
       </c>
       <c r="H44" t="n">
-        <v>35.11</v>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.44</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.9</v>
+        <v>7.116</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.964</v>
+        <v>7.541</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2490,28 +2490,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>0.014</v>
+        <v>0.325</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>-0.0299</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>1124200</v>
+        <v>1950000</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="H45" t="n">
-        <v>48.52</v>
+        <v>44.32</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.736</v>
+        <v>0.342</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.724</v>
+        <v>0.336</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2535,28 +2535,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>0</v>
+        <v>0.725</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>0.014</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>1060900</v>
+        <v>1888700</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.49</v>
+        <v>0.14</v>
       </c>
       <c r="H46" t="n">
-        <v>52.17</v>
+        <v>48.52</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.263</v>
+        <v>0.736</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.242</v>
+        <v>0.724</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2580,28 +2580,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.82</v>
+        <v>0.455</v>
       </c>
       <c r="E47" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1043800</v>
+        <v>1783700</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.06</v>
+        <v>0.26</v>
       </c>
       <c r="H47" t="n">
-        <v>55.59</v>
+        <v>57.28</v>
       </c>
       <c r="I47" s="16" t="inlineStr">
         <is>
@@ -2609,10 +2609,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.429</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.418</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2625,39 +2625,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0</v>
+        <v>0.62</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1037700</v>
+        <v>1730700</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="H48" t="n">
-        <v>68.73</v>
-      </c>
-      <c r="I48" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.15</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.801</v>
+        <v>0.578</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.776</v>
+        <v>0.48</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2670,28 +2670,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>-0.0179</v>
+        <v>0.575</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1034600</v>
+        <v>1655700</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>1.12</v>
+        <v>0.08</v>
       </c>
       <c r="H49" t="n">
-        <v>50.42</v>
+        <v>52.07</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.277</v>
+        <v>0.572</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.268</v>
+        <v>0.545</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2715,39 +2715,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ECOFIRS</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E50" s="17" t="n">
-        <v>-0.0313</v>
+        <v>0.62</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1008400</v>
+        <v>1632900</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.66</v>
+        <v>0.36</v>
       </c>
       <c r="H50" t="n">
-        <v>39.44</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.11</v>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.322</v>
+        <v>0.535</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.333</v>
+        <v>0.479</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2760,39 +2760,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>-0.008100000000000001</v>
+        <v>0.38</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>941400</v>
+        <v>1609400</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="H51" t="n">
-        <v>39.55</v>
-      </c>
-      <c r="I51" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.34</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>7.421</v>
+        <v>0.393</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>7.866</v>
+        <v>0.405</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2805,39 +2805,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>0</v>
+        <v>4.81</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>901500</v>
+        <v>1458300</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="H52" t="n">
-        <v>48.55</v>
-      </c>
-      <c r="I52" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.29</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>4.729</v>
+        <v>4.876</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>4.826</v>
+        <v>4.749</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2850,28 +2850,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>1.02</v>
+        <v>0.245</v>
       </c>
       <c r="E53" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>883600</v>
+        <v>1426100</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>57.63</v>
+        <v>84.81</v>
       </c>
       <c r="I53" s="16" t="inlineStr">
         <is>
@@ -2879,10 +2879,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>1.009</v>
+        <v>0.216</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.987</v>
+        <v>0.211</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2895,28 +2895,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.95</v>
+        <v>7.3</v>
       </c>
       <c r="E54" s="17" t="n">
-        <v>-0.0051</v>
+        <v>-0.0095</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>846500</v>
+        <v>1415600</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="H54" t="n">
-        <v>52.71</v>
+        <v>39.16</v>
       </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>1.929</v>
+        <v>7.42</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1.952</v>
+        <v>7.866</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2940,39 +2940,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>4.8</v>
+        <v>0.46</v>
       </c>
       <c r="E55" s="17" t="n">
-        <v>-0.0062</v>
+        <v>-0.0108</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>835400</v>
+        <v>1414300</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.03</v>
+        <v>0.19</v>
       </c>
       <c r="H55" t="n">
-        <v>46.79</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.23</v>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>4.875</v>
+        <v>0.487</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>4.749</v>
+        <v>0.545</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2985,28 +2985,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
         <v>0.765</v>
       </c>
-      <c r="E56" s="15" t="n">
-        <v>0.0132</v>
+      <c r="E56" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>796700</v>
+        <v>1395400</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="H56" t="n">
-        <v>55.78</v>
+        <v>48.56</v>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.744</v>
+        <v>0.769</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.771</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3030,33 +3030,40 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E57" s="17" t="n">
-        <v>-0.0129</v>
+        <v>0.87</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>0.0175</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>775600</v>
+        <v>1385000</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J57" s="9" t="n"/>
-      <c r="K57" s="9" t="n"/>
+        <v>0.4</v>
+      </c>
+      <c r="H57" t="n">
+        <v>35.11</v>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K57" s="9" t="n">
+        <v>0.964</v>
+      </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
     </row>
@@ -3068,28 +3075,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E58" s="15" t="n">
-        <v>0.0256</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>768500</v>
+        <v>1365100</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="H58" t="n">
-        <v>65.76000000000001</v>
+        <v>39.45</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -3097,10 +3104,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>1.084</v>
+        <v>0.623</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.945</v>
+        <v>0.618</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3113,39 +3120,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E59" s="15" t="n">
-        <v>0.0318</v>
+        <v>2.75</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>-0.0108</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>765100</v>
+        <v>1317300</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="H59" t="n">
-        <v>25.48</v>
-      </c>
-      <c r="I59" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.95</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.9</v>
+        <v>2.86</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>1.055</v>
+        <v>2.992</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3158,28 +3165,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>0.0327</v>
+        <v>0.465</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>-0.0106</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>749500</v>
+        <v>1305300</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="H60" t="n">
-        <v>56.96</v>
+        <v>43.22</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3187,10 +3194,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>3.97</v>
+        <v>0.505</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>3.608</v>
+        <v>0.467</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3203,28 +3210,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.865</v>
+        <v>0.825</v>
       </c>
       <c r="E61" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>748000</v>
+        <v>1298100</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.04</v>
+        <v>0.24</v>
       </c>
       <c r="H61" t="n">
-        <v>46.09</v>
+        <v>68.73</v>
       </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
@@ -3232,10 +3239,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.868</v>
+        <v>0.801</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.869</v>
+        <v>0.776</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3248,39 +3255,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>0</v>
+        <v>0.86</v>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>0.0238</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>711700</v>
+        <v>1260900</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="H62" t="n">
-        <v>75.20999999999999</v>
-      </c>
-      <c r="I62" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.19</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.6</v>
+        <v>0.905</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.538</v>
+        <v>0.855</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3293,28 +3300,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2.43</v>
+        <v>0.445</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>0.0083</v>
+        <v>0.0349</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>696600</v>
+        <v>1254200</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="H63" t="n">
-        <v>35.35</v>
+        <v>58.27</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3322,10 +3329,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>2.698</v>
+        <v>0.42</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>2.856</v>
+        <v>0.389</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3338,28 +3345,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>7.15</v>
+        <v>3.85</v>
       </c>
       <c r="E64" s="15" t="n">
-        <v>0.0014</v>
+        <v>0.0132</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>684900</v>
+        <v>1250800</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.04</v>
+        <v>0.17</v>
       </c>
       <c r="H64" t="n">
-        <v>33.24</v>
+        <v>58.12</v>
       </c>
       <c r="I64" s="13" t="inlineStr">
         <is>
@@ -3367,10 +3374,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>7.412</v>
+        <v>3.702</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>7.648</v>
+        <v>3.149</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3383,39 +3390,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.505</v>
+        <v>0.705</v>
       </c>
       <c r="E65" s="17" t="n">
-        <v>-0.0098</v>
+        <v>-0.014</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>651100</v>
+        <v>1232600</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="H65" t="n">
-        <v>29.82</v>
-      </c>
-      <c r="I65" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.29</v>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.534</v>
+        <v>0.717</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.778</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3428,39 +3435,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>647900</v>
+        <v>1194600</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.14</v>
+        <v>1.01</v>
       </c>
       <c r="H66" t="n">
-        <v>21.84</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.11</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>1.341</v>
+        <v>0.23</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>1.528</v>
+        <v>0.238</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3473,39 +3480,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>-0.0131</v>
+        <v>4.73</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>647100</v>
+        <v>1161700</v>
       </c>
       <c r="G67" s="12" t="n">
         <v>0.05</v>
       </c>
       <c r="H67" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.55</v>
+      </c>
+      <c r="I67" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>5.455</v>
+        <v>4.729</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>5.496</v>
+        <v>4.826</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3518,39 +3525,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E68" s="17" t="n">
-        <v>-0.0076</v>
+        <v>0.265</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>644200</v>
+        <v>1131900</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.3</v>
+        <v>0.52</v>
       </c>
       <c r="H68" t="n">
-        <v>58.18</v>
-      </c>
-      <c r="I68" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.17</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.639</v>
+        <v>0.263</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.626</v>
+        <v>0.242</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3563,28 +3570,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E69" s="15" t="n">
-        <v>0.0074</v>
+        <v>0.62</v>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>631900</v>
+        <v>1129900</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.31</v>
+        <v>0.14</v>
       </c>
       <c r="H69" t="n">
-        <v>53.13</v>
+        <v>40.2</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3592,10 +3599,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>1.363</v>
+        <v>0.663</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>1.343</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3608,40 +3615,33 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0478</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>NWE Resources Group Berhad</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>-0.0048</v>
+        <v>0.2</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>623800</v>
+        <v>1128400</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="H70" t="n">
-        <v>39.63</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J70" s="9" t="n">
-        <v>2.123</v>
-      </c>
-      <c r="K70" s="9" t="n">
-        <v>2.235</v>
-      </c>
+        <v>0.01</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n"/>
+      <c r="K70" s="9" t="n"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
     </row>
@@ -3653,28 +3653,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>2.77</v>
+        <v>1.18</v>
       </c>
       <c r="E71" s="17" t="n">
-        <v>-0.0036</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>614800</v>
+        <v>1096200</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="H71" t="n">
-        <v>41.09</v>
+        <v>21.27</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
@@ -3682,10 +3682,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>2.862</v>
+        <v>1.34</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>2.992</v>
+        <v>1.528</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3698,39 +3698,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.845</v>
+        <v>6.89</v>
       </c>
       <c r="E72" s="15" t="n">
-        <v>0.006</v>
+        <v>0.0177</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>596500</v>
+        <v>1084800</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="H72" t="n">
-        <v>41.89</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.62</v>
+      </c>
+      <c r="I72" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.904</v>
+        <v>6.769</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.855</v>
+        <v>6.82</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3743,28 +3743,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E73" s="17" t="n">
-        <v>-0.008</v>
+        <v>4.08</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>0.0277</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>593100</v>
+        <v>1084700</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="H73" t="n">
-        <v>40.2</v>
+        <v>56.37</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -3772,10 +3772,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.663</v>
+        <v>3.968</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.6870000000000001</v>
+        <v>3.607</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3788,39 +3788,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E74" s="17" t="n">
-        <v>-0.008500000000000001</v>
+        <v>1.19</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>0.0171</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>585200</v>
+        <v>1081800</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.08</v>
+        <v>0.23</v>
       </c>
       <c r="H74" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="I74" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.06</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.216</v>
+        <v>1.083</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1.304</v>
+        <v>0.944</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3833,39 +3833,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="E75" s="17" t="n">
-        <v>-0.0106</v>
+        <v>2.42</v>
+      </c>
+      <c r="E75" s="15" t="n">
+        <v>0.004099999999999999</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>581000</v>
+        <v>1049600</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
       <c r="H75" t="n">
-        <v>56.86</v>
-      </c>
-      <c r="I75" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.78</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>6.268</v>
+        <v>2.697</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>5.97</v>
+        <v>2.856</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3878,39 +3878,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="E76" s="15" t="n">
-        <v>0.0222</v>
+        <v>0.275</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>577600</v>
+        <v>1034600</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.13</v>
+        <v>1.12</v>
       </c>
       <c r="H76" t="n">
-        <v>61.32</v>
-      </c>
-      <c r="I76" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.42</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>6.772</v>
+        <v>0.277</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>6.821</v>
+        <v>0.268</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3923,28 +3923,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1.55</v>
+        <v>0.41</v>
       </c>
       <c r="E77" s="17" t="n">
-        <v>-0.0252</v>
+        <v>-0.012</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>561500</v>
+        <v>1023300</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="H77" t="n">
-        <v>32.95</v>
+        <v>43.27</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3952,10 +3952,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>1.68</v>
+        <v>0.43</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>1.752</v>
+        <v>0.438</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3968,28 +3968,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.34</v>
+        <v>0.765</v>
       </c>
       <c r="E78" s="15" t="n">
-        <v>0.0152</v>
+        <v>0.0132</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>539300</v>
+        <v>1022100</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="H78" t="n">
-        <v>58.51</v>
+        <v>55.78</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.274</v>
+        <v>0.744</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.183</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4013,28 +4013,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>ECOFIRS</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E79" s="15" t="n">
-        <v>0.006</v>
+        <v>0.31</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>538000</v>
+        <v>1008400</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.14</v>
+        <v>0.66</v>
       </c>
       <c r="H79" t="n">
-        <v>53.23</v>
+        <v>39.44</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.826</v>
+        <v>0.322</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.793</v>
+        <v>0.333</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4058,28 +4058,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>1.03</v>
+        <v>0.42</v>
       </c>
       <c r="E80" s="15" t="n">
-        <v>0.03</v>
+        <v>0.012</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>524700</v>
+        <v>1004300</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="H80" t="n">
-        <v>51.46</v>
+        <v>56.78</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>1.034</v>
+        <v>0.396</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.963</v>
+        <v>0.365</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4103,28 +4103,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>0.002</v>
+        <v>0.65</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>-0.0076</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>518100</v>
+        <v>973200</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.04</v>
+        <v>0.45</v>
       </c>
       <c r="H81" t="n">
-        <v>46.45</v>
+        <v>58.18</v>
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
@@ -4132,16 +4132,1314 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>9.99</v>
+        <v>0.639</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>10.121</v>
+        <v>0.626</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0477</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>ECOSYS</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>-0.0129</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>965700</v>
+      </c>
+      <c r="G82" s="12" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="n"/>
+      <c r="K82" s="9" t="n"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="14" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>5.69</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="F83" s="11" t="n">
+        <v>957700</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H83" t="n">
+        <v>35.83</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>5.843</v>
+      </c>
+      <c r="K83" s="9" t="n">
+        <v>6.125</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="14" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E84" s="17" t="n">
+        <v>-0.0103</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>954500</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H84" t="n">
+        <v>62.87</v>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>0.9370000000000001</v>
+      </c>
+      <c r="K84" s="9" t="n">
+        <v>0.886</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="14" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="F85" s="11" t="n">
+        <v>940900</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H85" t="n">
+        <v>56.09</v>
+      </c>
+      <c r="I85" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>1.364</v>
+      </c>
+      <c r="K85" s="9" t="n">
+        <v>1.343</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="14" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0239</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>ECOMATE</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>920000</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H86" t="n">
+        <v>51.47</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="K86" s="9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="14" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>0.0382</v>
+      </c>
+      <c r="F87" s="11" t="n">
+        <v>912500</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H87" t="n">
+        <v>26.81</v>
+      </c>
+      <c r="I87" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>1.055</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="14" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>RALCO</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>883600</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H88" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="I88" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="K88" s="9" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="14" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>1023</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>CIMB</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="E89" s="17" t="n">
+        <v>-0.0014</v>
+      </c>
+      <c r="F89" s="11" t="n">
+        <v>883500</v>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H89" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="K89" s="9" t="n">
+        <v>7.648</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="14" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E90" s="17" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F90" s="11" t="n">
+        <v>862900</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H90" t="n">
+        <v>72.95999999999999</v>
+      </c>
+      <c r="I90" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>0.599</v>
+      </c>
+      <c r="K90" s="9" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="14" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E91" s="17" t="n">
+        <v>-0.0169</v>
+      </c>
+      <c r="F91" s="11" t="n">
+        <v>852800</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H91" t="n">
+        <v>49.07</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>1.171</v>
+      </c>
+      <c r="K91" s="9" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="14" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>AXIATA</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>833800</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H92" t="n">
+        <v>50.39</v>
+      </c>
+      <c r="I92" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>1.627</v>
+      </c>
+      <c r="K92" s="9" t="n">
+        <v>1.682</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="14" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F93" s="11" t="n">
+        <v>811500</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H93" t="n">
+        <v>31.45</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="14" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>0.0152</v>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>806900</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H94" t="n">
+        <v>58.51</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>1.274</v>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>1.183</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="14" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="E95" s="17" t="n">
+        <v>-0.0181</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>793300</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H95" t="n">
+        <v>55.94</v>
+      </c>
+      <c r="I95" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>6.264</v>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>5.969</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="14" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>-0.0251</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>759300</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H96" t="n">
+        <v>30.99</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="n">
+        <v>2.498</v>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>2.672</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="14" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>-0.0152</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>742900</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H97" t="n">
+        <v>49.74</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>2.606</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>2.611</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="14" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="E98" s="17" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>741400</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H98" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="I98" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>1.216</v>
+      </c>
+      <c r="K98" s="9" t="n">
+        <v>1.304</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="14" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="E99" s="15" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>699200</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H99" t="n">
+        <v>47.16</v>
+      </c>
+      <c r="I99" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>9.991</v>
+      </c>
+      <c r="K99" s="9" t="n">
+        <v>10.122</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="14" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E100" s="17" t="n">
+        <v>-0.0252</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>698900</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H100" t="n">
+        <v>32.95</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>1.752</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="14" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>SUNMED</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="E101" s="17" t="n">
+        <v>-0.0048</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>685000</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H101" t="n">
+        <v>45.74</v>
+      </c>
+      <c r="I101" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>2.104</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="14" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5180</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>CLMT</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>660700</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H102" t="n">
+        <v>47.59</v>
+      </c>
+      <c r="I102" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="14" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E103" s="15" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>642900</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H103" t="n">
+        <v>53.23</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>0.826</v>
+      </c>
+      <c r="K103" s="9" t="n">
+        <v>0.793</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="14" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>623700</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H104" t="n">
+        <v>51.46</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>1.034</v>
+      </c>
+      <c r="K104" s="9" t="n">
+        <v>0.963</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="E105" s="17" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>587700</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H105" t="n">
+        <v>54.73</v>
+      </c>
+      <c r="I105" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>5.069</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>5.046</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="14" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>574800</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H106" t="n">
+        <v>52.83</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>1.105</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="14" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="E107" s="15" t="n">
+        <v>0.0129</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>569800</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H107" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="I107" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>2.257</v>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>2.191</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="14" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>7076</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>CBIP</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>531400</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H108" t="n">
+        <v>40.24</v>
+      </c>
+      <c r="I108" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>1.073</v>
+      </c>
+      <c r="K108" s="9" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="14" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>524700</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H109" t="n">
+        <v>55.48</v>
+      </c>
+      <c r="I109" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="14" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="E110" s="17" t="n">
+        <v>-0.004099999999999999</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>515100</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H110" t="n">
+        <v>48.95</v>
+      </c>
+      <c r="I110" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>2.445</v>
+      </c>
+      <c r="K110" s="9" t="n">
+        <v>2.404</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M81"/>
+  <autoFilter ref="A1:M110"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-22/bursa-report-2026-10-22.xlsx
+++ b/docs/downloads/2026-10-22/bursa-report-2026-10-22.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-22" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-22'!$A$1:$M$110</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-22'!$A$1:$M$132</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M110"/>
+  <dimension ref="A1:M132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.1074</v>
+        <v>0.0992</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>5318900</v>
+        <v>6219300</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>61.4</v>
+        <v>60.75</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.241</v>
+        <v>1.24</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>1.097</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 61.4未超买，现价高于50日均线约22%，技术面信号偏可靠。</t>
+          <t>SAR转多信号，RSI 60.75未超买，现价高于50日均线约21%，技术面信号偏可靠。</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>0.0294</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>30649900</v>
+        <v>31572800</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>57.97</v>
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.285</v>
+        <v>0.28</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>58205900</v>
+        <v>62794600</v>
       </c>
       <c r="G4" s="12" t="n"/>
       <c r="I4" s="13" t="inlineStr">
@@ -714,10 +714,10 @@
         <v>0.1</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>55913200</v>
+        <v>58363600</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="H5" t="n">
         <v>25.86</v>
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.09</v>
+        <v>0.095</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>0.2</v>
+        <v>0.2667</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>18671700</v>
+        <v>21934000</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>47.9</v>
+        <v>56.27</v>
       </c>
       <c r="H6" t="n">
-        <v>77.75</v>
+        <v>81.28</v>
       </c>
       <c r="I6" s="16" t="inlineStr">
         <is>
@@ -804,10 +804,10 @@
         <v>-0.0105</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>13328100</v>
+        <v>18297300</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.37</v>
+        <v>0.51</v>
       </c>
       <c r="H7" t="n">
         <v>79.78</v>
@@ -834,39 +834,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0069</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VINVEST</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>0.3333</v>
+        <v>0.345</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>13304800</v>
+        <v>18058300</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>35.04</v>
+        <v>0.22</v>
       </c>
       <c r="H8" t="n">
-        <v>58.17</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>67.47</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.016</v>
+        <v>0.314</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.017</v>
+        <v>0.263</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -879,28 +879,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0069</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>VINVEST</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0</v>
+        <v>0.02</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>0.3333</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>12314800</v>
+        <v>13504900</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.49</v>
+        <v>35.57</v>
       </c>
       <c r="H9" t="n">
-        <v>81.19</v>
+        <v>58.17</v>
       </c>
       <c r="I9" s="16" t="inlineStr">
         <is>
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.642</v>
+        <v>0.016</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.548</v>
+        <v>0.017</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -924,39 +924,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0</v>
+        <v>0.71</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>12299800</v>
+        <v>12338100</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.15</v>
+        <v>0.49</v>
       </c>
       <c r="H10" t="n">
-        <v>67.47</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.7</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.314</v>
+        <v>0.642</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.263</v>
+        <v>0.548</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -969,33 +969,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>-0.0588</v>
+        <v>0.18</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>8474000</v>
+        <v>10052100</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.39</v>
+        <v>0.48</v>
+      </c>
+      <c r="H11" t="n">
+        <v>44.12</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="9" t="n"/>
+      <c r="J11" s="9" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0.186</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
     </row>
@@ -1007,40 +1014,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>0.0048</v>
+        <v>0.24</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>-0.0588</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>8339800</v>
+        <v>9129200</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H12" t="n">
-        <v>60.83</v>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>1.962</v>
-      </c>
-      <c r="K12" s="9" t="n">
-        <v>1.777</v>
-      </c>
+        <v>0.42</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n"/>
+      <c r="K12" s="9" t="n"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
     </row>
@@ -1052,39 +1052,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>0.08699999999999999</v>
+        <v>2.07</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>7642300</v>
+        <v>9016800</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="H13" t="n">
-        <v>41.65</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.35</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.136</v>
+        <v>1.961</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.148</v>
+        <v>1.776</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1097,39 +1097,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0</v>
+        <v>0.895</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>6154700</v>
+        <v>8658400</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>3.35</v>
+        <v>0.12</v>
       </c>
       <c r="H14" t="n">
-        <v>33.05</v>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.96</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.837</v>
+        <v>0.847</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.858</v>
+        <v>0.753</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1142,28 +1142,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.295</v>
+        <v>0.155</v>
       </c>
       <c r="E15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>6114500</v>
+        <v>8605000</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1.81</v>
+        <v>0.24</v>
       </c>
       <c r="H15" t="n">
-        <v>49.23</v>
+        <v>48.42</v>
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.295</v>
+        <v>0.155</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.295</v>
+        <v>0.156</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1187,39 +1187,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.18</v>
+        <v>0.77</v>
       </c>
       <c r="E16" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>5646100</v>
+        <v>7993300</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.27</v>
+        <v>0.52</v>
       </c>
       <c r="H16" t="n">
-        <v>44.12</v>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.51</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.187</v>
+        <v>0.774</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.186</v>
+        <v>0.776</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1232,39 +1232,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>-0.0165</v>
+        <v>0.12</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>5455100</v>
+        <v>7767300</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="H17" t="n">
-        <v>62.96</v>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.37</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.847</v>
+        <v>0.136</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.753</v>
+        <v>0.148</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1277,39 +1277,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ZANTAT</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.17</v>
+        <v>0.305</v>
       </c>
       <c r="E18" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>5407900</v>
+        <v>6285400</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>22.13</v>
+        <v>0.32</v>
       </c>
       <c r="H18" t="n">
-        <v>64.15000000000001</v>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.42</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.156</v>
+        <v>0.308</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.156</v>
+        <v>0.301</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1322,39 +1322,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>4850000</v>
+        <v>6190100</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.31</v>
+        <v>3.37</v>
       </c>
       <c r="H19" t="n">
-        <v>50.43</v>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.05</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.774</v>
+        <v>0.837</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.776</v>
+        <v>0.858</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1367,28 +1367,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>0.0311</v>
+        <v>0.295</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>4361300</v>
+        <v>6114500</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.49</v>
+        <v>1.81</v>
       </c>
       <c r="H20" t="n">
-        <v>46.38</v>
+        <v>49.23</v>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
@@ -1396,10 +1396,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>1.028</v>
+        <v>0.295</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.974</v>
+        <v>0.295</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1412,39 +1412,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>ZANTAT</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0</v>
+        <v>0.165</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>-0.0294</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>3940000</v>
+        <v>5569600</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.2</v>
+        <v>22.79</v>
       </c>
       <c r="H21" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.87</v>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.308</v>
+        <v>0.156</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.301</v>
+        <v>0.156</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1457,28 +1457,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>-0.0116</v>
+        <v>0.98</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>0.0155</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>3827700</v>
+        <v>5154400</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.1</v>
+        <v>0.58</v>
       </c>
       <c r="H22" t="n">
-        <v>36.88</v>
+        <v>44.26</v>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.463</v>
+        <v>1.027</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.478</v>
+        <v>0.974</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1517,10 +1517,10 @@
         <v>-0.0192</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>3780100</v>
+        <v>4466500</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H23" t="n">
         <v>31</v>
@@ -1547,39 +1547,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>0.0333</v>
+        <v>0.865</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>3472100</v>
+        <v>4440600</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="H24" t="n">
-        <v>43.61</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.09</v>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.155</v>
+        <v>0.868</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.182</v>
+        <v>0.869</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1592,28 +1592,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.285</v>
+        <v>0.43</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>0.0179</v>
+        <v>0.0118</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>3276200</v>
+        <v>4067500</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.52</v>
+        <v>0.34</v>
       </c>
       <c r="H25" t="n">
-        <v>31.02</v>
+        <v>61.36</v>
       </c>
       <c r="I25" s="16" t="inlineStr">
         <is>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.318</v>
+        <v>0.4</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.363</v>
+        <v>0.381</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1637,28 +1637,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.85</v>
+        <v>0.42</v>
       </c>
       <c r="E26" s="17" t="n">
-        <v>-0.023</v>
+        <v>-0.0233</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>3248400</v>
+        <v>3984300</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.72</v>
+        <v>0.11</v>
       </c>
       <c r="H26" t="n">
-        <v>53.9</v>
+        <v>35.83</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1666,10 +1666,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.85</v>
+        <v>0.463</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.61</v>
+        <v>0.478</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1682,39 +1682,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E27" s="17" t="n">
-        <v>-0.021</v>
+        <v>0.82</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>3190200</v>
+        <v>3923100</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="H27" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.59</v>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>1.622</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>1.902</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1727,28 +1727,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.43</v>
+        <v>0.285</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>0.0118</v>
+        <v>0.0179</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>3014600</v>
+        <v>3824900</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.25</v>
+        <v>0.61</v>
       </c>
       <c r="H28" t="n">
-        <v>61.36</v>
+        <v>31.02</v>
       </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.4</v>
+        <v>0.318</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.381</v>
+        <v>0.363</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1772,39 +1772,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0</v>
+        <v>0.155</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>2933300</v>
+        <v>3565700</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.41</v>
+        <v>0.25</v>
       </c>
       <c r="H29" t="n">
-        <v>55.91</v>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.61</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.372</v>
+        <v>0.155</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.37</v>
+        <v>0.182</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1817,39 +1817,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0</v>
+        <v>0.83</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>-0.046</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>2924300</v>
+        <v>3527400</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.14</v>
+        <v>0.78</v>
       </c>
       <c r="H30" t="n">
-        <v>46.09</v>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.52</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.868</v>
+        <v>0.848</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.869</v>
+        <v>0.609</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1862,39 +1862,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>0.0282</v>
+        <v>0.63</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2741200</v>
+        <v>3522100</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>1.55</v>
+        <v>0.33</v>
       </c>
       <c r="H31" t="n">
-        <v>50.73</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.13</v>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.911</v>
+        <v>0.621</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.886</v>
+        <v>0.617</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1907,39 +1907,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0</v>
+        <v>1.41</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>-0.014</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2690100</v>
+        <v>3426200</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="H32" t="n">
-        <v>58.13</v>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>20.85</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.621</v>
+        <v>1.623</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.617</v>
+        <v>1.903</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1952,39 +1952,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.5</v>
+        <v>2.54</v>
       </c>
       <c r="E33" s="17" t="n">
-        <v>-0.009899999999999999</v>
+        <v>-0.0155</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>2622900</v>
+        <v>3313000</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.92</v>
+        <v>0.18</v>
       </c>
       <c r="H33" t="n">
-        <v>75.63</v>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.26</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.436</v>
+        <v>2.621</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.435</v>
+        <v>2.561</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1997,39 +1997,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>1.99</v>
+        <v>5.35</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>0.0153</v>
+        <v>0.0019</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>2551800</v>
+        <v>3186700</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.42</v>
+        <v>0.24</v>
       </c>
       <c r="H34" t="n">
-        <v>58.08</v>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.58</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>1.933</v>
+        <v>5.463</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1.953</v>
+        <v>5.498</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2042,28 +2042,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>0.0019</v>
+        <v>0.575</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>2479000</v>
+        <v>3137900</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.19</v>
+        <v>0.15</v>
       </c>
       <c r="H35" t="n">
-        <v>44.58</v>
+        <v>52.07</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2071,10 +2071,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>5.463</v>
+        <v>0.572</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>5.498</v>
+        <v>0.545</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2087,39 +2087,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>-0.0364</v>
+        <v>2</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>2458900</v>
+        <v>3062500</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.23</v>
+        <v>0.5</v>
       </c>
       <c r="H36" t="n">
-        <v>39.76</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.21</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.29</v>
+        <v>1.934</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.28</v>
+        <v>1.953</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2132,39 +2132,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.38</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>2445800</v>
+        <v>3033300</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.13</v>
+        <v>0.42</v>
       </c>
       <c r="H37" t="n">
-        <v>46.42</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.3</v>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>2.623</v>
+        <v>0.372</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>2.561</v>
+        <v>0.37</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2177,28 +2177,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0</v>
+        <v>0.89</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>0.005600000000000001</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>2396300</v>
+        <v>2824100</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="H38" t="n">
-        <v>46.02</v>
+        <v>47.43</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>2.041</v>
+        <v>0.909</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>2.067</v>
+        <v>0.886</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2222,39 +2222,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0</v>
+        <v>0.27</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>2268800</v>
+        <v>2715500</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="H39" t="n">
-        <v>55.59</v>
-      </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.4</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.291</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.28</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2276,19 +2276,19 @@
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>-0.0048</v>
+        <v>2.07</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>2240200</v>
+        <v>2713800</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="H40" t="n">
-        <v>39.63</v>
+        <v>40.57</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>2.123</v>
+        <v>2.124</v>
       </c>
       <c r="K40" s="9" t="n">
         <v>2.235</v>
@@ -2312,39 +2312,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>-0.009899999999999999</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>2663300</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H41" t="n">
+        <v>75.63</v>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="K41" s="9" t="n">
         <v>0.435</v>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>-0.0114</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>2010900</v>
-      </c>
-      <c r="G41" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H41" t="n">
-        <v>55.06</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J41" s="9" t="n">
-        <v>0.427</v>
-      </c>
-      <c r="K41" s="9" t="n">
-        <v>0.378</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2357,38 +2357,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.365</v>
+        <v>2.02</v>
       </c>
       <c r="E42" s="17" t="n">
-        <v>-0.0267</v>
+        <v>-0.0049</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1992000</v>
+        <v>2552100</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.35</v>
+        <v>0.74</v>
       </c>
       <c r="H42" t="n">
-        <v>61.46</v>
-      </c>
-      <c r="I42" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.07</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="K42" s="9" t="n"/>
+        <v>2.04</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>2.066</v>
+      </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
     </row>
@@ -2400,28 +2402,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>0.006</v>
+        <v>0.45</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>-0.011</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1959500</v>
+        <v>2301200</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.61</v>
+        <v>0.33</v>
       </c>
       <c r="H43" t="n">
-        <v>88.44</v>
+        <v>56</v>
       </c>
       <c r="I43" s="16" t="inlineStr">
         <is>
@@ -2429,10 +2431,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>2.962</v>
+        <v>0.429</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>2.515</v>
+        <v>0.418</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2445,28 +2447,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.435</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>-0.0114</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1953000</v>
+        <v>2289000</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.18</v>
+        <v>0.11</v>
       </c>
       <c r="H44" t="n">
-        <v>39.44</v>
+        <v>55.06</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
@@ -2474,10 +2476,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>7.116</v>
+        <v>0.427</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>7.541</v>
+        <v>0.378</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2490,28 +2492,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="E45" s="17" t="n">
-        <v>-0.0299</v>
+        <v>6.9</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>0.0058</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>1950000</v>
+        <v>2278000</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="H45" t="n">
-        <v>44.32</v>
+        <v>38.61</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
@@ -2519,10 +2521,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.342</v>
+        <v>7.114</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.336</v>
+        <v>7.54</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2535,40 +2537,38 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>0.014</v>
+        <v>0.375</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>1888700</v>
+        <v>2249400</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.14</v>
+        <v>0.4</v>
       </c>
       <c r="H46" t="n">
-        <v>48.52</v>
-      </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.42</v>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="K46" s="9" t="n">
-        <v>0.724</v>
-      </c>
+        <v>0.334</v>
+      </c>
+      <c r="K46" s="9" t="n"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
     </row>
@@ -2580,39 +2580,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0</v>
+        <v>1.15</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>-0.0171</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1783700</v>
+        <v>2164000</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="H47" t="n">
-        <v>57.28</v>
-      </c>
-      <c r="I47" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.86</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.429</v>
+        <v>1.215</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.418</v>
+        <v>1.303</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2625,28 +2625,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="E48" s="15" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.035</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1730700</v>
+        <v>2163100</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="H48" t="n">
-        <v>59.15</v>
+        <v>50.52</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.578</v>
+        <v>0.737</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.48</v>
+        <v>0.724</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2670,28 +2670,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>0</v>
+        <v>0.325</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>-0.0299</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1655700</v>
+        <v>2049300</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.08</v>
+        <v>0.21</v>
       </c>
       <c r="H49" t="n">
-        <v>52.07</v>
+        <v>44.32</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -2699,10 +2699,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.572</v>
+        <v>0.342</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.545</v>
+        <v>0.336</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2715,28 +2715,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v>0.008100000000000001</v>
+        <v>7.3</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>-0.0095</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1632900</v>
+        <v>2020800</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.36</v>
+        <v>0.19</v>
       </c>
       <c r="H50" t="n">
-        <v>70.11</v>
+        <v>39.16</v>
       </c>
       <c r="I50" s="16" t="inlineStr">
         <is>
@@ -2744,10 +2744,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.535</v>
+        <v>7.42</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.479</v>
+        <v>7.866</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2760,39 +2760,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>0</v>
+        <v>3.38</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>0.006</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1609400</v>
+        <v>2005900</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.18</v>
+        <v>0.63</v>
       </c>
       <c r="H51" t="n">
-        <v>24.34</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>88.44</v>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.393</v>
+        <v>2.962</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.405</v>
+        <v>2.515</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2805,39 +2805,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.62</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1458300</v>
+        <v>1973500</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.06</v>
+        <v>0.44</v>
       </c>
       <c r="H52" t="n">
-        <v>47.29</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.11</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>4.876</v>
+        <v>0.535</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>4.749</v>
+        <v>0.479</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2850,39 +2850,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.245</v>
+        <v>0.615</v>
       </c>
       <c r="E53" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1426100</v>
+        <v>1930600</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1</v>
+        <v>0.31</v>
       </c>
       <c r="H53" t="n">
-        <v>84.81</v>
-      </c>
-      <c r="I53" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.6</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.216</v>
+        <v>0.578</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.211</v>
+        <v>0.48</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2895,39 +2895,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="E54" s="17" t="n">
-        <v>-0.0095</v>
+        <v>4.03</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>0.0151</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1415600</v>
+        <v>1900400</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="H54" t="n">
-        <v>39.16</v>
-      </c>
-      <c r="I54" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.82</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>7.42</v>
+        <v>3.963</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>7.866</v>
+        <v>3.606</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2940,39 +2940,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.46</v>
+        <v>4.82</v>
       </c>
       <c r="E55" s="17" t="n">
-        <v>-0.0108</v>
+        <v>-0.0021</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1414300</v>
+        <v>1789600</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>34.23</v>
-      </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.81</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.487</v>
+        <v>4.877</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.545</v>
+        <v>4.75</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2985,39 +2985,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.765</v>
+        <v>0.245</v>
       </c>
       <c r="E56" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1395400</v>
+        <v>1784000</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.17</v>
+        <v>1.25</v>
       </c>
       <c r="H56" t="n">
-        <v>48.56</v>
-      </c>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.81</v>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.769</v>
+        <v>0.216</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.771</v>
+        <v>0.211</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3030,28 +3030,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="E57" s="15" t="n">
-        <v>0.0175</v>
+        <v>0.23</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1385000</v>
+        <v>1716200</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.4</v>
+        <v>1.46</v>
       </c>
       <c r="H57" t="n">
-        <v>35.11</v>
+        <v>48.11</v>
       </c>
       <c r="I57" s="16" t="inlineStr">
         <is>
@@ -3059,10 +3059,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.9</v>
+        <v>0.23</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.964</v>
+        <v>0.238</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3075,28 +3075,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.46</v>
       </c>
       <c r="E58" s="17" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0213</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1365100</v>
+        <v>1697700</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="H58" t="n">
-        <v>39.45</v>
+        <v>42.44</v>
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
@@ -3104,10 +3104,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.623</v>
+        <v>0.504</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.618</v>
+        <v>0.467</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3120,28 +3120,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E59" s="17" t="n">
-        <v>-0.0108</v>
+        <v>3.87</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>0.0184</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1317300</v>
+        <v>1685200</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.38</v>
+        <v>0.22</v>
       </c>
       <c r="H59" t="n">
-        <v>39.95</v>
+        <v>58.62</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>2.86</v>
+        <v>3.704</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>2.992</v>
+        <v>3.15</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3165,28 +3165,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.465</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E60" s="17" t="n">
-        <v>-0.0106</v>
+        <v>-0.0175</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1305300</v>
+        <v>1653100</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="H60" t="n">
-        <v>43.22</v>
+        <v>38.82</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.505</v>
+        <v>0.623</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.467</v>
+        <v>0.618</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3210,39 +3210,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E61" s="10" t="n">
-        <v>0</v>
+        <v>7.15</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>0.0014</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1298100</v>
+        <v>1615400</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.24</v>
+        <v>0.1</v>
       </c>
       <c r="H61" t="n">
-        <v>68.73</v>
-      </c>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.24</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.801</v>
+        <v>7.412</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.776</v>
+        <v>7.648</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3264,19 +3264,19 @@
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.86</v>
+        <v>0.845</v>
       </c>
       <c r="E62" s="15" t="n">
-        <v>0.0238</v>
+        <v>0.006</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1260900</v>
+        <v>1613800</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="H62" t="n">
-        <v>44.19</v>
+        <v>41.89</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3284,7 +3284,7 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.905</v>
+        <v>0.904</v>
       </c>
       <c r="K62" s="9" t="n">
         <v>0.855</v>
@@ -3300,28 +3300,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E63" s="15" t="n">
-        <v>0.0349</v>
+        <v>0.38</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1254200</v>
+        <v>1609400</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.32</v>
+        <v>0.18</v>
       </c>
       <c r="H63" t="n">
-        <v>58.27</v>
+        <v>24.34</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.42</v>
+        <v>0.393</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.389</v>
+        <v>0.405</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3345,39 +3345,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="E64" s="15" t="n">
-        <v>0.0132</v>
+        <v>0.705</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>-0.014</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1250800</v>
+        <v>1575500</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H64" t="n">
-        <v>58.12</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.29</v>
+      </c>
+      <c r="I64" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>3.702</v>
+        <v>0.717</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>3.149</v>
+        <v>0.778</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3390,39 +3390,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.705</v>
+        <v>2.39</v>
       </c>
       <c r="E65" s="17" t="n">
-        <v>-0.014</v>
+        <v>-0.0083</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1232600</v>
+        <v>1561200</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.19</v>
+        <v>0.29</v>
       </c>
       <c r="H65" t="n">
-        <v>42.29</v>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.58</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.717</v>
+        <v>2.694</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.778</v>
+        <v>2.855</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3435,39 +3435,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.23</v>
+        <v>2.75</v>
       </c>
       <c r="E66" s="17" t="n">
-        <v>-0.0213</v>
+        <v>-0.0108</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1194600</v>
+        <v>1554500</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>1.01</v>
+        <v>0.45</v>
       </c>
       <c r="H66" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="I66" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.95</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.23</v>
+        <v>2.86</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.238</v>
+        <v>2.992</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3480,39 +3480,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0</v>
+        <v>1.42</v>
+      </c>
+      <c r="E67" s="15" t="n">
+        <v>0.0071</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1161700</v>
+        <v>1525700</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="H67" t="n">
-        <v>48.55</v>
-      </c>
-      <c r="I67" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.53</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>4.729</v>
+        <v>1.441</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>4.826</v>
+        <v>1.46</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3525,28 +3525,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>0</v>
+        <v>0.44</v>
+      </c>
+      <c r="E68" s="15" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1131900</v>
+        <v>1491700</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.52</v>
+        <v>0.39</v>
       </c>
       <c r="H68" t="n">
-        <v>52.17</v>
+        <v>57.25</v>
       </c>
       <c r="I68" s="13" t="inlineStr">
         <is>
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.263</v>
+        <v>0.419</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.242</v>
+        <v>0.389</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3570,39 +3570,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>-0.008</v>
+        <v>0.865</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>0.0117</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1129900</v>
+        <v>1476700</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.14</v>
+        <v>0.43</v>
       </c>
       <c r="H69" t="n">
-        <v>40.2</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.08</v>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.663</v>
+        <v>0.899</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.963</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3615,33 +3615,40 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NWE Resources Group Berhad</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>-0.0108</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>1460700</v>
+      </c>
+      <c r="G70" s="12" t="n">
         <v>0.2</v>
       </c>
-      <c r="E70" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="11" t="n">
-        <v>1128400</v>
-      </c>
-      <c r="G70" s="12" t="n">
-        <v>0.01</v>
+      <c r="H70" t="n">
+        <v>34.23</v>
       </c>
       <c r="I70" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J70" s="9" t="n"/>
-      <c r="K70" s="9" t="n"/>
+      <c r="J70" s="9" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>0.545</v>
+      </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
     </row>
@@ -3653,40 +3660,33 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>1.18</v>
+        <v>0.755</v>
       </c>
       <c r="E71" s="17" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0258</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1096200</v>
+        <v>1452600</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="H71" t="n">
-        <v>21.27</v>
+        <v>0.03</v>
       </c>
       <c r="I71" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J71" s="9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="K71" s="9" t="n">
-        <v>1.528</v>
-      </c>
+      <c r="J71" s="9" t="n"/>
+      <c r="K71" s="9" t="n"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
     </row>
@@ -3698,39 +3698,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>0.0177</v>
+        <v>0.765</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1084800</v>
+        <v>1400400</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.25</v>
+        <v>0.17</v>
       </c>
       <c r="H72" t="n">
-        <v>59.62</v>
-      </c>
-      <c r="I72" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.56</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>6.769</v>
+        <v>0.769</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>6.82</v>
+        <v>0.771</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3743,39 +3743,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="E73" s="15" t="n">
-        <v>0.0277</v>
+        <v>4.73</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1084700</v>
+        <v>1396500</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H73" t="n">
-        <v>56.37</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.55</v>
+      </c>
+      <c r="I73" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>3.968</v>
+        <v>4.729</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>3.607</v>
+        <v>4.826</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3788,28 +3788,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E74" s="15" t="n">
-        <v>0.0171</v>
+        <v>0.615</v>
+      </c>
+      <c r="E74" s="17" t="n">
+        <v>-0.016</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1081800</v>
+        <v>1348200</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="H74" t="n">
-        <v>65.06</v>
+        <v>39.44</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -3817,10 +3817,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.083</v>
+        <v>0.662</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.944</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3833,39 +3833,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.42</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E75" s="15" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.0382</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1049600</v>
+        <v>1343200</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.19</v>
+        <v>0.6</v>
       </c>
       <c r="H75" t="n">
-        <v>34.78</v>
-      </c>
-      <c r="I75" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>26.81</v>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>2.697</v>
+        <v>0.901</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>2.856</v>
+        <v>1.055</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3878,39 +3878,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>-0.0179</v>
+        <v>6.91</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>0.0207</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1034600</v>
+        <v>1315400</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>1.12</v>
+        <v>0.3</v>
       </c>
       <c r="H76" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.77</v>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.277</v>
+        <v>6.771</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.268</v>
+        <v>6.82</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3923,39 +3923,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E77" s="17" t="n">
-        <v>-0.012</v>
+        <v>0.825</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1023300</v>
+        <v>1296100</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="H77" t="n">
-        <v>43.27</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.73</v>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.43</v>
+        <v>0.801</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.438</v>
+        <v>0.776</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3977,19 +3977,19 @@
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>0.0132</v>
+        <v>0.755</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1022100</v>
+        <v>1295200</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="H78" t="n">
-        <v>55.78</v>
+        <v>54.29</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="K78" s="9" t="n">
         <v>0.6850000000000001</v>
@@ -4013,28 +4013,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>0348</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ECOFIRS</t>
+          <t>CLITE</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.31</v>
+        <v>0.205</v>
       </c>
       <c r="E79" s="17" t="n">
-        <v>-0.0313</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1008400</v>
+        <v>1294800</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.66</v>
+        <v>1.09</v>
       </c>
       <c r="H79" t="n">
-        <v>39.44</v>
+        <v>35.59</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4042,10 +4042,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.322</v>
+        <v>0.229</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.333</v>
+        <v>0.215</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4058,28 +4058,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E80" s="15" t="n">
-        <v>0.012</v>
+        <v>0.865</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1004300</v>
+        <v>1272800</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.17</v>
+        <v>0.44</v>
       </c>
       <c r="H80" t="n">
-        <v>56.78</v>
+        <v>51.47</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.396</v>
+        <v>0.865</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.365</v>
+        <v>0.86</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4103,39 +4103,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E81" s="17" t="n">
-        <v>-0.0076</v>
+        <v>1.18</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>973200</v>
+        <v>1270400</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.45</v>
+        <v>0.27</v>
       </c>
       <c r="H81" t="n">
-        <v>58.18</v>
-      </c>
-      <c r="I81" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>64.34</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.639</v>
+        <v>1.082</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.626</v>
+        <v>0.944</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4148,33 +4148,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E82" s="17" t="n">
-        <v>-0.0129</v>
+        <v>5.69</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>0.0035</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>965700</v>
+        <v>1250800</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.02</v>
+        <v>0.16</v>
+      </c>
+      <c r="H82" t="n">
+        <v>35.83</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J82" s="9" t="n"/>
-      <c r="K82" s="9" t="n"/>
+      <c r="J82" s="9" t="n">
+        <v>5.843</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>6.125</v>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
     </row>
@@ -4186,39 +4193,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>5.69</v>
-      </c>
-      <c r="E83" s="15" t="n">
-        <v>0.0035</v>
+        <v>0.95</v>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>957700</v>
+        <v>1218000</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="H83" t="n">
-        <v>35.83</v>
-      </c>
-      <c r="I83" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.47</v>
+      </c>
+      <c r="I83" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>5.843</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>6.125</v>
+        <v>0.885</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4231,39 +4238,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.965</v>
+        <v>1.18</v>
       </c>
       <c r="E84" s="17" t="n">
-        <v>-0.0103</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>954500</v>
+        <v>1213300</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.16</v>
+        <v>0.26</v>
       </c>
       <c r="H84" t="n">
-        <v>62.87</v>
-      </c>
-      <c r="I84" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.27</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.9370000000000001</v>
+        <v>1.34</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.886</v>
+        <v>1.528</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4276,28 +4283,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E85" s="15" t="n">
-        <v>0.0147</v>
+        <v>0.4</v>
+      </c>
+      <c r="E85" s="17" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>940900</v>
+        <v>1179000</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.46</v>
+        <v>0.11</v>
       </c>
       <c r="H85" t="n">
-        <v>56.09</v>
+        <v>29.9</v>
       </c>
       <c r="I85" s="16" t="inlineStr">
         <is>
@@ -4305,10 +4312,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>1.364</v>
+        <v>0.491</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1.343</v>
+        <v>0.596</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4321,28 +4328,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.865</v>
+        <v>0.265</v>
       </c>
       <c r="E86" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>920000</v>
+        <v>1131900</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.32</v>
+        <v>0.52</v>
       </c>
       <c r="H86" t="n">
-        <v>51.47</v>
+        <v>52.17</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4350,10 +4357,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.865</v>
+        <v>0.263</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.86</v>
+        <v>0.242</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4366,39 +4373,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E87" s="15" t="n">
-        <v>0.0382</v>
+        <v>0.41</v>
+      </c>
+      <c r="E87" s="17" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>912500</v>
+        <v>1101500</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.41</v>
+        <v>0.12</v>
       </c>
       <c r="H87" t="n">
-        <v>26.81</v>
-      </c>
-      <c r="I87" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.27</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.901</v>
+        <v>0.43</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1.055</v>
+        <v>0.438</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4411,39 +4418,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>0</v>
+        <v>1.17</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>883600</v>
+        <v>1100400</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>1.41</v>
+        <v>0.16</v>
       </c>
       <c r="H88" t="n">
-        <v>57.63</v>
-      </c>
-      <c r="I88" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.55</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>1.009</v>
+        <v>1.172</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.987</v>
+        <v>1.146</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4456,28 +4463,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>-0.0014</v>
+        <v>1.33</v>
+      </c>
+      <c r="E89" s="15" t="n">
+        <v>0.0076</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>883500</v>
+        <v>1063300</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.05</v>
+        <v>0.43</v>
       </c>
       <c r="H89" t="n">
-        <v>32.26</v>
+        <v>57.76</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -4485,10 +4492,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>7.41</v>
+        <v>1.273</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>7.648</v>
+        <v>1.183</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4501,39 +4508,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.655</v>
+        <v>2.42</v>
       </c>
       <c r="E90" s="17" t="n">
-        <v>-0.0076</v>
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>862900</v>
+        <v>1062700</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.67</v>
+        <v>0.1</v>
       </c>
       <c r="H90" t="n">
-        <v>72.95999999999999</v>
-      </c>
-      <c r="I90" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.63</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.599</v>
+        <v>2.444</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.538</v>
+        <v>2.404</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4546,28 +4553,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1.16</v>
+        <v>2.33</v>
       </c>
       <c r="E91" s="17" t="n">
-        <v>-0.0169</v>
+        <v>-0.0251</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>852800</v>
+        <v>1048700</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.13</v>
+        <v>0.24</v>
       </c>
       <c r="H91" t="n">
-        <v>49.07</v>
+        <v>30.99</v>
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
@@ -4575,10 +4582,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>1.171</v>
+        <v>2.498</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1.145</v>
+        <v>2.672</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4591,39 +4598,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>0</v>
+        <v>0.275</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>833800</v>
+        <v>1034600</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.11</v>
+        <v>1.12</v>
       </c>
       <c r="H92" t="n">
-        <v>50.39</v>
-      </c>
-      <c r="I92" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.42</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>1.627</v>
+        <v>0.277</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>1.682</v>
+        <v>0.268</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4636,28 +4643,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>0</v>
+        <v>0.42</v>
+      </c>
+      <c r="E93" s="15" t="n">
+        <v>0.012</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>811500</v>
+        <v>1023300</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.29</v>
+        <v>0.17</v>
       </c>
       <c r="H93" t="n">
-        <v>31.45</v>
+        <v>56.78</v>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
@@ -4665,10 +4672,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.535</v>
+        <v>0.396</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.365</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4681,39 +4688,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>0.0152</v>
+        <v>0.65</v>
+      </c>
+      <c r="E94" s="17" t="n">
+        <v>-0.0076</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>806900</v>
+        <v>1023200</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.32</v>
+        <v>0.47</v>
       </c>
       <c r="H94" t="n">
-        <v>58.51</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.18</v>
+      </c>
+      <c r="I94" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.274</v>
+        <v>0.639</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.183</v>
+        <v>0.626</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4726,39 +4733,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>ECOFIRS</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>6.51</v>
+        <v>0.31</v>
       </c>
       <c r="E95" s="17" t="n">
-        <v>-0.0181</v>
+        <v>-0.0313</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>793300</v>
+        <v>1008400</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.13</v>
+        <v>0.66</v>
       </c>
       <c r="H95" t="n">
-        <v>55.94</v>
-      </c>
-      <c r="I95" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.44</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>6.264</v>
+        <v>0.322</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>5.969</v>
+        <v>0.333</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4771,28 +4778,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>-0.0251</v>
+        <v>0.46</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>759300</v>
+        <v>1003500</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.17</v>
+        <v>0.55</v>
       </c>
       <c r="H96" t="n">
-        <v>30.99</v>
+        <v>47.19</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -4800,10 +4807,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>2.498</v>
+        <v>0.461</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>2.672</v>
+        <v>0.462</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4816,28 +4823,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E97" s="17" t="n">
-        <v>-0.0152</v>
+        <v>0.51</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>742900</v>
+        <v>974600</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.12</v>
+        <v>0.34</v>
       </c>
       <c r="H97" t="n">
-        <v>49.74</v>
+        <v>31.45</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -4845,10 +4852,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>2.606</v>
+        <v>0.535</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>2.611</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4861,28 +4868,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E98" s="17" t="n">
-        <v>-0.008500000000000001</v>
+        <v>1.38</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>741400</v>
+        <v>960900</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.1</v>
+        <v>0.47</v>
       </c>
       <c r="H98" t="n">
-        <v>35.1</v>
+        <v>56.09</v>
       </c>
       <c r="I98" s="16" t="inlineStr">
         <is>
@@ -4890,10 +4897,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.216</v>
+        <v>1.364</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.304</v>
+        <v>1.343</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4906,28 +4913,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="E99" s="15" t="n">
-        <v>0.003</v>
+        <v>6.53</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <v>-0.0151</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>699200</v>
+        <v>951400</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="H99" t="n">
-        <v>47.16</v>
+        <v>56.31</v>
       </c>
       <c r="I99" s="16" t="inlineStr">
         <is>
@@ -4935,10 +4942,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>9.991</v>
+        <v>6.266</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>10.122</v>
+        <v>5.97</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4951,39 +4958,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E100" s="17" t="n">
-        <v>-0.0252</v>
+        <v>9.98</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>0.003</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>698900</v>
+        <v>889700</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.12</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H100" t="n">
-        <v>32.95</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.16</v>
+      </c>
+      <c r="I100" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>1.68</v>
+        <v>9.991</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>1.752</v>
+        <v>10.122</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4996,28 +5003,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E101" s="17" t="n">
-        <v>-0.0048</v>
+        <v>0.66</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>685000</v>
+        <v>887400</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.05</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H101" t="n">
-        <v>45.74</v>
+        <v>75.20999999999999</v>
       </c>
       <c r="I101" s="16" t="inlineStr">
         <is>
@@ -5025,10 +5032,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>2.102</v>
+        <v>0.6</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>2.104</v>
+        <v>0.538</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5041,28 +5048,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="E102" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>660700</v>
+        <v>883600</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.4</v>
+        <v>1.41</v>
       </c>
       <c r="H102" t="n">
-        <v>47.59</v>
+        <v>57.63</v>
       </c>
       <c r="I102" s="16" t="inlineStr">
         <is>
@@ -5070,10 +5077,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.009</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.576</v>
+        <v>0.987</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5086,39 +5093,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E103" s="15" t="n">
-        <v>0.006</v>
+        <v>1.64</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>642900</v>
+        <v>881900</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="H103" t="n">
-        <v>53.23</v>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.39</v>
+      </c>
+      <c r="I103" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.826</v>
+        <v>1.627</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.793</v>
+        <v>1.682</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5131,39 +5138,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>1.03</v>
+        <v>2.37</v>
       </c>
       <c r="E104" s="15" t="n">
-        <v>0.03</v>
+        <v>0.0172</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>623700</v>
+        <v>866400</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="H104" t="n">
-        <v>51.46</v>
-      </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.52</v>
+      </c>
+      <c r="I104" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>1.034</v>
+        <v>2.258</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.963</v>
+        <v>2.192</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5191,10 +5198,10 @@
         <v>-0.009599999999999999</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>587700</v>
+        <v>861000</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="H105" t="n">
         <v>54.73</v>
@@ -5221,28 +5228,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E106" s="15" t="n">
-        <v>0.0185</v>
+        <v>2.58</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>574800</v>
+        <v>831400</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="H106" t="n">
-        <v>52.83</v>
+        <v>48.14</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5250,10 +5257,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>1.105</v>
+        <v>2.604</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.911</v>
+        <v>2.611</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5266,28 +5273,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="E107" s="15" t="n">
-        <v>0.0129</v>
+        <v>0.555</v>
+      </c>
+      <c r="E107" s="17" t="n">
+        <v>-0.0089</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>569800</v>
+        <v>823700</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.17</v>
+        <v>0.5</v>
       </c>
       <c r="H107" t="n">
-        <v>60.88</v>
+        <v>44.46</v>
       </c>
       <c r="I107" s="16" t="inlineStr">
         <is>
@@ -5295,10 +5302,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>2.257</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>2.191</v>
+        <v>0.576</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5311,28 +5318,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>CBIP</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>1.06</v>
+        <v>2.09</v>
       </c>
       <c r="E108" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>531400</v>
+        <v>808200</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>17.5</v>
+        <v>0.06</v>
       </c>
       <c r="H108" t="n">
-        <v>40.24</v>
+        <v>47.56</v>
       </c>
       <c r="I108" s="16" t="inlineStr">
         <is>
@@ -5340,10 +5347,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>1.073</v>
+        <v>2.103</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>1.113</v>
+        <v>2.104</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5356,39 +5363,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E109" s="17" t="n">
-        <v>-0.0192</v>
+        <v>1.02</v>
+      </c>
+      <c r="E109" s="15" t="n">
+        <v>0.02</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>524700</v>
+        <v>788800</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="H109" t="n">
-        <v>55.48</v>
-      </c>
-      <c r="I109" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.11</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.745</v>
+        <v>1.033</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.707</v>
+        <v>0.962</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5401,28 +5408,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="E110" s="17" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.83</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>515100</v>
+        <v>782900</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.05</v>
+        <v>0.21</v>
       </c>
       <c r="H110" t="n">
-        <v>48.95</v>
+        <v>52.35</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -5430,16 +5437,1006 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>2.445</v>
+        <v>0.826</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>2.404</v>
+        <v>0.792</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>-0.0314</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>763900</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H111" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>1.679</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>1.752</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="14" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>TIMECOM</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>735300</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H112" t="n">
+        <v>32.64</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>5.508</v>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>5.766</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>708200</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H113" t="n">
+        <v>51.92</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>2.795</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>2.683</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="14" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0056</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>NCT</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>685800</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H114" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="I114" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="14" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>675700</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H115" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>5.483</v>
+      </c>
+      <c r="K115" s="9" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="14" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="E116" s="17" t="n">
+        <v>-0.0123</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>654100</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H116" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>7.303</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>6.926</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>639100</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H117" t="n">
+        <v>33.97</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>4.356</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="14" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>630800</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H118" t="n">
+        <v>57.35</v>
+      </c>
+      <c r="I118" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="K118" s="9" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>0.009300000000000001</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>619800</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H119" t="n">
+        <v>51.92</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>1.104</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>0.911</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="14" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>602200</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H120" t="n">
+        <v>50.36</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n">
+        <v>3.825</v>
+      </c>
+      <c r="K120" s="9" t="n">
+        <v>3.726</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="14" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>597600</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H121" t="n">
+        <v>56.43</v>
+      </c>
+      <c r="I121" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>0.746</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>0.708</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="14" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="E122" s="15" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>586600</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H122" t="n">
+        <v>52.47</v>
+      </c>
+      <c r="I122" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="n">
+        <v>4.379</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>4.433</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>584700</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H123" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>1.365</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>1.447</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="14" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E124" s="17" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>584500</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H124" t="n">
+        <v>29</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="K124" s="9" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="14" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="E125" s="17" t="n">
+        <v>-0.005600000000000001</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>559400</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H125" t="n">
+        <v>56.15</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>10.448</v>
+      </c>
+      <c r="K125" s="9" t="n">
+        <v>9.831</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="14" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="E126" s="17" t="n">
+        <v>-0.0315</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>558100</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H126" t="n">
+        <v>31.89</v>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="n">
+        <v>0.698</v>
+      </c>
+      <c r="K126" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>8583</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>MAHSING</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E127" s="17" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>542600</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H127" t="n">
+        <v>25.71</v>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>0.956</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="14" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>538900</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H128" t="n">
+        <v>59.69</v>
+      </c>
+      <c r="I128" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="n">
+        <v>2.715</v>
+      </c>
+      <c r="K128" s="9" t="n">
+        <v>2.323</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="14" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>7076</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>CBIP</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>533400</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="H129" t="n">
+        <v>40.24</v>
+      </c>
+      <c r="I129" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="n">
+        <v>1.073</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="14" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>7195</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>BNASTRA</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E130" s="17" t="n">
+        <v>-0.0179</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>528900</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H130" t="n">
+        <v>68.58</v>
+      </c>
+      <c r="I130" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="n">
+        <v>2.645</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>2.466</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>509100</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H131" t="n">
+        <v>48.48</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="14" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E132" s="17" t="n">
+        <v>-0.0183</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>500300</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H132" t="n">
+        <v>47.29</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>0.522</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M110"/>
+  <autoFilter ref="A1:M132"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-22/bursa-report-2026-10-22.xlsx
+++ b/docs/downloads/2026-10-22/bursa-report-2026-10-22.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-22" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-22'!$A$1:$M$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-22'!$A$1:$M$170</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -82,8 +82,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M158"/>
+  <dimension ref="A1:M170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,7 +558,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>65785600</v>
+        <v>69387300</v>
       </c>
       <c r="G2" s="5" t="n"/>
       <c r="I2" s="6" t="inlineStr">
@@ -588,19 +588,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>62388500</v>
+        <v>63878100</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>0.17</v>
       </c>
       <c r="H3" t="n">
-        <v>25.86</v>
+        <v>23.85</v>
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.105</v>
+        <v>0.104</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.284</v>
@@ -639,15 +639,15 @@
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>31754000</v>
+        <v>32516200</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="H4" t="n">
         <v>56.15</v>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -678,21 +678,21 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0.2</v>
+        <v>0.095</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>0.2667</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>22761400</v>
+        <v>23953600</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>58.39</v>
+        <v>61.45</v>
       </c>
       <c r="H5" t="n">
-        <v>77.75</v>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
+        <v>81.28</v>
+      </c>
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -729,10 +729,10 @@
         <v>-0.0145</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>19182400</v>
+        <v>20228800</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.23</v>
+        <v>0.25</v>
       </c>
       <c r="H6" t="n">
         <v>64.98999999999999</v>
@@ -768,21 +768,21 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.47</v>
+        <v>0.465</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>-0.0105</v>
+        <v>-0.0211</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>19016600</v>
+        <v>19169600</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="H7" t="n">
-        <v>79.78</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
+        <v>77.25</v>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -804,39 +804,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0069</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VINVEST</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="E8" s="8" t="n">
-        <v>0.3333</v>
+        <v>0.715</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>13548500</v>
+        <v>18065100</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>35.69</v>
+        <v>0.71</v>
       </c>
       <c r="H8" t="n">
-        <v>58.17</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
+        <v>81.19</v>
+      </c>
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.016</v>
+        <v>0.642</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.017</v>
+        <v>0.548</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -849,39 +849,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0069</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>VINVEST</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0.3333</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>12912700</v>
+        <v>13650400</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.51</v>
+        <v>35.95</v>
       </c>
       <c r="H9" t="n">
-        <v>81.19</v>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
+        <v>58.17</v>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.642</v>
+        <v>0.016</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.548</v>
+        <v>0.017</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -903,16 +903,16 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.225</v>
+        <v>0.23</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>-0.1176</v>
+        <v>-0.098</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>12264600</v>
+        <v>13131100</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -941,21 +941,21 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.77</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10528900</v>
+        <v>10980700</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
       <c r="H11" t="n">
-        <v>50.43</v>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
+        <v>46.51</v>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -977,39 +977,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>-0.0097</v>
+        <v>0.305</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10184200</v>
+        <v>10915400</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.36</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>58.9</v>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.42</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.959</v>
+        <v>0.308</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>1.776</v>
+        <v>0.301</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1022,39 +1022,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0.0278</v>
+        <v>0.895</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>10097000</v>
+        <v>10608000</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.48</v>
+        <v>0.14</v>
       </c>
       <c r="H13" t="n">
-        <v>48.09</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.96</v>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.187</v>
+        <v>0.847</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.186</v>
+        <v>0.753</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1067,39 +1067,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>-0.0165</v>
+        <v>0.18</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10003300</v>
+        <v>10507400</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="H14" t="n">
-        <v>62.96</v>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.12</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.847</v>
+        <v>0.187</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.753</v>
+        <v>0.186</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1112,39 +1112,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>0</v>
+        <v>2.05</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8645400</v>
+        <v>10476700</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="H15" t="n">
-        <v>47.42</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.9</v>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.308</v>
+        <v>1.959</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.301</v>
+        <v>1.776</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1157,39 +1157,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.155</v>
+        <v>0.865</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>8605000</v>
+        <v>9619800</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.24</v>
+        <v>0.47</v>
       </c>
       <c r="H16" t="n">
-        <v>48.42</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.09</v>
+      </c>
+      <c r="I16" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.155</v>
+        <v>0.868</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.156</v>
+        <v>0.869</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1202,28 +1202,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>0.0435</v>
+        <v>0.155</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>7827300</v>
+        <v>9255000</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.4</v>
+        <v>0.26</v>
       </c>
       <c r="H17" t="n">
-        <v>38.37</v>
+        <v>48.42</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.136</v>
+        <v>0.155</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.148</v>
+        <v>0.156</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1247,39 +1247,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>0</v>
+        <v>0.12</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>7234600</v>
+        <v>7917300</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="H18" t="n">
-        <v>46.09</v>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.37</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.868</v>
+        <v>0.136</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.869</v>
+        <v>0.148</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1292,39 +1292,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>0.08259999999999999</v>
+        <v>0.98</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>0.0155</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6739200</v>
+        <v>7504700</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>2.15</v>
+        <v>0.85</v>
       </c>
       <c r="H19" t="n">
-        <v>59.38</v>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.26</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.238</v>
+        <v>1.027</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1.096</v>
+        <v>0.974</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1337,39 +1337,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>0.0207</v>
+        <v>1.3</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>0.07440000000000001</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6656800</v>
+        <v>6882200</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.75</v>
+        <v>2.2</v>
       </c>
       <c r="H20" t="n">
-        <v>44.98</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.66</v>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.028</v>
+        <v>1.237</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.974</v>
+        <v>1.096</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1382,39 +1382,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>0.43</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>0.0118</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>6241100</v>
+        <v>6615300</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>3.4</v>
+        <v>0.55</v>
       </c>
       <c r="H21" t="n">
-        <v>33.05</v>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.36</v>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.837</v>
+        <v>0.4</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.858</v>
+        <v>0.381</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1427,28 +1427,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6114500</v>
+        <v>6277300</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>1.81</v>
+        <v>3.42</v>
       </c>
       <c r="H22" t="n">
-        <v>49.23</v>
+        <v>31.21</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.295</v>
+        <v>0.836</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.295</v>
+        <v>0.858</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1472,39 +1472,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ZANTAT</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>-0.0294</v>
+        <v>0.295</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>5638600</v>
+        <v>6114500</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>23.08</v>
+        <v>1.81</v>
       </c>
       <c r="H23" t="n">
-        <v>58.87</v>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.23</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.156</v>
+        <v>0.295</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.156</v>
+        <v>0.295</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1517,39 +1517,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>-0.0233</v>
+        <v>0.82</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>5469700</v>
+        <v>5937300</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.15</v>
+        <v>0.36</v>
       </c>
       <c r="H24" t="n">
-        <v>35.83</v>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.59</v>
+      </c>
+      <c r="I24" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.463</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.478</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1562,39 +1562,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="E25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5079100</v>
+        <v>5845400</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.31</v>
+        <v>0.55</v>
       </c>
       <c r="H25" t="n">
-        <v>55.59</v>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
+        <v>58.13</v>
+      </c>
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.621</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.617</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1607,39 +1607,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>ZANTAT</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>0.0118</v>
+        <v>0.165</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>-0.0294</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4947400</v>
+        <v>5638600</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.41</v>
+        <v>23.08</v>
       </c>
       <c r="H26" t="n">
-        <v>61.36</v>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
+        <v>58.87</v>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4</v>
+        <v>0.156</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.381</v>
+        <v>0.156</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1652,39 +1652,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>0</v>
+        <v>0.42</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4812100</v>
+        <v>5604700</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="H27" t="n">
-        <v>58.13</v>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.83</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.621</v>
+        <v>0.463</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.617</v>
+        <v>0.478</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1697,28 +1697,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>8338</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>DATAPRP</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>-0.0192</v>
+        <v>0.065</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <v>0.0833</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4602200</v>
+        <v>5414400</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H28" t="n">
-        <v>31</v>
+        <v>49.57</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.271</v>
+        <v>0.064</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.296</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1742,28 +1742,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>-0.0182</v>
+        <v>7.16</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <v>0.0028</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4165900</v>
+        <v>4859100</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.39</v>
+        <v>0.29</v>
       </c>
       <c r="H29" t="n">
-        <v>41.4</v>
+        <v>33.88</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
@@ -1771,10 +1771,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.291</v>
+        <v>7.413</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.28</v>
+        <v>7.648</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1787,28 +1787,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2.52</v>
+        <v>1.4</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>-0.0233</v>
+        <v>-0.021</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>4017100</v>
+        <v>4774300</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.22</v>
+        <v>0.41</v>
       </c>
       <c r="H30" t="n">
-        <v>44.15</v>
+        <v>20.45</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2.62</v>
+        <v>1.622</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2.56</v>
+        <v>1.902</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1832,39 +1832,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>0.0255</v>
+        <v>5.31</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3983100</v>
+        <v>4757800</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.65</v>
+        <v>0.36</v>
       </c>
       <c r="H31" t="n">
-        <v>60.28</v>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.99</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.935</v>
+        <v>5.459</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1.953</v>
+        <v>5.497</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1877,39 +1877,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>0.0357</v>
+        <v>0.255</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3930000</v>
+        <v>4757300</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.63</v>
+        <v>0.59</v>
       </c>
       <c r="H32" t="n">
-        <v>33.67</v>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.319</v>
+        <v>0.271</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.363</v>
+        <v>0.296</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1922,28 +1922,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>0.0019</v>
+        <v>0.27</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3775400</v>
+        <v>4495900</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="H33" t="n">
-        <v>44.58</v>
+        <v>41.4</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>5.463</v>
+        <v>0.291</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>5.498</v>
+        <v>0.28</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1967,28 +1967,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.825</v>
+        <v>2.52</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>-0.0517</v>
+        <v>-0.0233</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3708400</v>
+        <v>4456800</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.82</v>
+        <v>0.24</v>
       </c>
       <c r="H34" t="n">
-        <v>52.18</v>
+        <v>44.15</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.847</v>
+        <v>2.62</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.609</v>
+        <v>2.56</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2012,39 +2012,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>0.0333</v>
+        <v>0.29</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3695800</v>
+        <v>4445100</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.25</v>
+        <v>0.71</v>
       </c>
       <c r="H35" t="n">
-        <v>43.61</v>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.67</v>
+      </c>
+      <c r="I35" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.155</v>
+        <v>0.319</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.182</v>
+        <v>0.363</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2057,39 +2057,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>1.4</v>
+        <v>0.38</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>-0.021</v>
+        <v>-0.0732</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3671100</v>
+        <v>4358200</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="H36" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>28.09</v>
+      </c>
+      <c r="I36" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.622</v>
+        <v>0.489</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>1.902</v>
+        <v>0.595</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2102,39 +2102,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>0</v>
+        <v>2.01</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>0.0255</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>3348600</v>
+        <v>4208600</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.16</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>56.58</v>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.28</v>
+      </c>
+      <c r="I37" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.427</v>
+        <v>1.935</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.378</v>
+        <v>1.953</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2147,39 +2147,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.57</v>
+        <v>7.3</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0095</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3329900</v>
+        <v>4104200</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.16</v>
+        <v>0.38</v>
       </c>
       <c r="H38" t="n">
-        <v>51.02</v>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.16</v>
+      </c>
+      <c r="I38" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.572</v>
+        <v>7.42</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.545</v>
+        <v>7.866</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2192,39 +2192,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>-0.0095</v>
+        <v>4.75</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <v>0.0042</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>3311100</v>
+        <v>4043800</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.31</v>
+        <v>0.19</v>
       </c>
       <c r="H39" t="n">
-        <v>39.16</v>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
+        <v>50.39</v>
+      </c>
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>7.42</v>
+        <v>4.731</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>7.866</v>
+        <v>4.826</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2237,39 +2237,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>0.0133</v>
+        <v>0.15</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>3243200</v>
+        <v>3826300</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.45</v>
+        <v>0.26</v>
       </c>
       <c r="H40" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.8</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.372</v>
+        <v>0.154</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.37</v>
+        <v>0.182</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2282,28 +2282,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>0.0102</v>
+        <v>0.825</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>-0.0517</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>3074500</v>
+        <v>3793200</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.29</v>
+        <v>0.84</v>
       </c>
       <c r="H41" t="n">
-        <v>39.85</v>
+        <v>52.18</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
@@ -2311,10 +2311,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>7.117</v>
+        <v>0.847</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>7.541</v>
+        <v>0.609</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2327,28 +2327,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>0.0042</v>
+        <v>0.57</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>3056900</v>
+        <v>3751000</v>
       </c>
       <c r="G42" s="5" t="n">
         <v>0.18</v>
       </c>
       <c r="H42" t="n">
-        <v>34.52</v>
+        <v>51.02</v>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>7.414</v>
+        <v>0.572</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>7.648</v>
+        <v>0.545</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2372,28 +2372,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>0</v>
+        <v>0.19</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>2932300</v>
+        <v>3715500</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.85</v>
+        <v>0.17</v>
       </c>
       <c r="H43" t="n">
-        <v>46.02</v>
+        <v>33.78</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>2.041</v>
+        <v>0.212</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2.067</v>
+        <v>0.232</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>-0.061</v>
+        <v>2.03</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2906700</v>
+        <v>3638600</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.27</v>
+        <v>1.05</v>
       </c>
       <c r="H44" t="n">
-        <v>28.52</v>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.02</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.49</v>
+        <v>2.041</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.595</v>
+        <v>2.067</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2462,28 +2462,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>-0.0171</v>
+        <v>6.92</v>
+      </c>
+      <c r="E45" s="9" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2872900</v>
+        <v>3637500</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="H45" t="n">
-        <v>33.86</v>
+        <v>39.44</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.215</v>
+        <v>7.116</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1.303</v>
+        <v>7.541</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2507,28 +2507,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>0</v>
+        <v>0.435</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>-0.0114</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2860300</v>
+        <v>3359100</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="H46" t="n">
-        <v>40.57</v>
+        <v>55.06</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
@@ -2536,10 +2536,10 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2.124</v>
+        <v>0.427</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2.235</v>
+        <v>0.378</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2552,39 +2552,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E47" s="9" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2833500</v>
+        <v>3343200</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>1</v>
+        <v>0.46</v>
       </c>
       <c r="H47" t="n">
-        <v>78.48</v>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
+        <v>61.3</v>
+      </c>
+      <c r="I47" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.437</v>
+        <v>0.372</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.435</v>
+        <v>0.37</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2597,28 +2597,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>0.005600000000000001</v>
+        <v>2.07</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2824100</v>
+        <v>3319300</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>1.6</v>
+        <v>0.29</v>
       </c>
       <c r="H48" t="n">
-        <v>47.43</v>
+        <v>40.57</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.909</v>
+        <v>2.124</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.886</v>
+        <v>2.235</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2642,28 +2642,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>5.68</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>0.0018</v>
+        <v>2.41</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>2763300</v>
+        <v>3242600</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.36</v>
+        <v>0.29</v>
       </c>
       <c r="H49" t="n">
-        <v>35.02</v>
+        <v>46.38</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>5.842</v>
+        <v>2.443</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>6.125</v>
+        <v>2.404</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2687,28 +2687,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>0.004500000000000001</v>
+        <v>5.69</v>
+      </c>
+      <c r="E50" s="9" t="n">
+        <v>0.0035</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>2753700</v>
+        <v>3107500</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="H50" t="n">
-        <v>38.96</v>
+        <v>35.83</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>4.579</v>
+        <v>5.843</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>4.64</v>
+        <v>6.125</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2732,28 +2732,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>0.035</v>
+        <v>1.15</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>-0.0171</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>2732800</v>
+        <v>3065400</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.21</v>
+        <v>0.4</v>
       </c>
       <c r="H51" t="n">
-        <v>50.52</v>
+        <v>33.86</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.737</v>
+        <v>1.215</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.724</v>
+        <v>1.303</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2777,38 +2777,40 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>-0.0133</v>
+        <v>0.735</v>
+      </c>
+      <c r="E52" s="9" t="n">
+        <v>0.028</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2458900</v>
+        <v>3028700</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.44</v>
+        <v>0.23</v>
       </c>
       <c r="H52" t="n">
-        <v>63.38</v>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.87</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.334</v>
-      </c>
-      <c r="K52" s="2" t="n"/>
+        <v>0.737</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0.724</v>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
     </row>
@@ -2820,39 +2822,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>-0.011</v>
+        <v>0.885</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2399200</v>
+        <v>2905400</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.34</v>
+        <v>1.64</v>
       </c>
       <c r="H53" t="n">
-        <v>56</v>
-      </c>
-      <c r="I53" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.54</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.429</v>
+        <v>0.909</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.418</v>
+        <v>0.886</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2865,39 +2867,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>-0.0244</v>
+        <v>0.51</v>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2332900</v>
+        <v>2856800</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.38</v>
+        <v>1.01</v>
       </c>
       <c r="H54" t="n">
-        <v>56.33</v>
-      </c>
-      <c r="I54" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>79.26000000000001</v>
+      </c>
+      <c r="I54" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.576</v>
+        <v>0.437</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.48</v>
+        <v>0.435</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2910,39 +2912,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>0</v>
+        <v>4.48</v>
+      </c>
+      <c r="E55" s="9" t="n">
+        <v>0.004500000000000001</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2198500</v>
+        <v>2776600</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.1</v>
+        <v>0.31</v>
       </c>
       <c r="H55" t="n">
-        <v>48.55</v>
-      </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.96</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>4.729</v>
+        <v>4.579</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>4.826</v>
+        <v>4.64</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2964,19 +2966,19 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>0.0202</v>
+        <v>4.03</v>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>0.0151</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2165700</v>
+        <v>2626100</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="H56" t="n">
-        <v>55.45</v>
+        <v>54.82</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
@@ -2984,10 +2986,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>3.965</v>
+        <v>3.963</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>3.607</v>
+        <v>3.606</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3000,40 +3002,38 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="E57" s="10" t="n">
-        <v>-0.0149</v>
+        <v>-0.0133</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2108800</v>
+        <v>2579300</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.21</v>
+        <v>0.46</v>
       </c>
       <c r="H57" t="n">
-        <v>46.02</v>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.38</v>
+      </c>
+      <c r="I57" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.342</v>
-      </c>
-      <c r="K57" s="2" t="n">
-        <v>0.336</v>
-      </c>
+        <v>0.334</v>
+      </c>
+      <c r="K57" s="2" t="n"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
     </row>
@@ -3045,39 +3045,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="E58" s="8" t="n">
-        <v>0.0089</v>
+        <v>3.88</v>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>0.0211</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2057900</v>
+        <v>2567600</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.64</v>
+        <v>0.34</v>
       </c>
       <c r="H58" t="n">
-        <v>88.59</v>
-      </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.87</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>2.963</v>
+        <v>3.705</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>2.516</v>
+        <v>3.15</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3090,39 +3090,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E59" s="9" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2052000</v>
+        <v>2536400</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="H59" t="n">
-        <v>84.81</v>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
+        <v>51.98</v>
+      </c>
+      <c r="I59" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.216</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.211</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3135,39 +3135,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="E60" s="8" t="n">
-        <v>0.0211</v>
+        <v>0.625</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2044900</v>
+        <v>2514700</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.27</v>
+        <v>0.72</v>
       </c>
       <c r="H60" t="n">
-        <v>58.87</v>
-      </c>
-      <c r="I60" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.66</v>
+      </c>
+      <c r="I60" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>3.705</v>
+        <v>0.619</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>3.15</v>
+        <v>0.609</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3180,39 +3180,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.465</v>
+        <v>0.45</v>
       </c>
       <c r="E61" s="10" t="n">
-        <v>-0.0106</v>
+        <v>-0.011</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>2028900</v>
+        <v>2450800</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.21</v>
+        <v>0.35</v>
       </c>
       <c r="H61" t="n">
-        <v>43.22</v>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56</v>
+      </c>
+      <c r="I61" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.505</v>
+        <v>0.429</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.467</v>
+        <v>0.418</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3225,39 +3225,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.6</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2027500</v>
+        <v>2414100</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="H62" t="n">
-        <v>70.11</v>
-      </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.33</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.535</v>
+        <v>0.576</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.479</v>
+        <v>0.48</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3270,28 +3270,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>0</v>
+        <v>1.42</v>
+      </c>
+      <c r="E63" s="9" t="n">
+        <v>0.0071</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1914100</v>
+        <v>2324400</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.08</v>
+        <v>0.61</v>
       </c>
       <c r="H63" t="n">
-        <v>48.34</v>
+        <v>40.53</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3299,10 +3299,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>4.878</v>
+        <v>1.441</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>4.75</v>
+        <v>1.46</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3315,39 +3315,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>-0.006</v>
+        <v>0.245</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1912400</v>
+        <v>2283900</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.29</v>
+        <v>1.6</v>
       </c>
       <c r="H64" t="n">
-        <v>40.52</v>
-      </c>
-      <c r="I64" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.81</v>
+      </c>
+      <c r="I64" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.903</v>
+        <v>0.216</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.855</v>
+        <v>0.211</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3360,28 +3360,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>2.39</v>
+        <v>0.325</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>-0.0083</v>
+        <v>-0.0299</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1858100</v>
+        <v>2161300</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.34</v>
+        <v>0.22</v>
       </c>
       <c r="H65" t="n">
-        <v>33.58</v>
+        <v>44.32</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3389,10 +3389,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2.694</v>
+        <v>0.342</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2.855</v>
+        <v>0.336</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3405,33 +3405,40 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.745</v>
+        <v>0.825</v>
       </c>
       <c r="E66" s="10" t="n">
-        <v>-0.0387</v>
+        <v>-0.0179</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1836300</v>
+        <v>2155800</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.04</v>
+        <v>0.33</v>
+      </c>
+      <c r="H66" t="n">
+        <v>39.44</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J66" s="2" t="n"/>
-      <c r="K66" s="2" t="n"/>
+      <c r="J66" s="2" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0.855</v>
+      </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
     </row>
@@ -3443,39 +3450,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.705</v>
+        <v>4.81</v>
       </c>
       <c r="E67" s="10" t="n">
-        <v>-0.014</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1798300</v>
+        <v>2154900</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.28</v>
+        <v>0.09</v>
       </c>
       <c r="H67" t="n">
-        <v>42.29</v>
-      </c>
-      <c r="I67" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.29</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.717</v>
+        <v>4.876</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.778</v>
+        <v>4.749</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3488,39 +3495,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>-0.0108</v>
+        <v>0.62</v>
+      </c>
+      <c r="E68" s="9" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1773300</v>
+        <v>2105600</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="H68" t="n">
-        <v>39.95</v>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.11</v>
+      </c>
+      <c r="I68" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2.86</v>
+        <v>0.535</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>2.992</v>
+        <v>0.479</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3533,39 +3540,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E69" s="8" t="n">
-        <v>0.0234</v>
+        <v>3.39</v>
+      </c>
+      <c r="E69" s="9" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1764000</v>
+        <v>2070500</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.51</v>
+        <v>0.65</v>
       </c>
       <c r="H69" t="n">
-        <v>37.03</v>
-      </c>
-      <c r="I69" s="9" t="inlineStr">
+        <v>88.59</v>
+      </c>
+      <c r="I69" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.9</v>
+        <v>2.963</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.964</v>
+        <v>2.516</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3578,39 +3585,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.46</v>
+        <v>0.705</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>-0.0108</v>
+        <v>-0.014</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1761800</v>
+        <v>2064400</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="H70" t="n">
-        <v>34.23</v>
-      </c>
-      <c r="I70" s="9" t="inlineStr">
+        <v>42.29</v>
+      </c>
+      <c r="I70" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.487</v>
+        <v>0.717</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.545</v>
+        <v>0.778</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3623,28 +3630,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.39</v>
       </c>
       <c r="E71" s="10" t="n">
-        <v>-0.0175</v>
+        <v>-0.0083</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1738600</v>
+        <v>2063200</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.2</v>
+        <v>0.38</v>
       </c>
       <c r="H71" t="n">
-        <v>38.82</v>
+        <v>33.58</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3652,10 +3659,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.623</v>
+        <v>2.694</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.618</v>
+        <v>2.855</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3668,39 +3675,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>-0.0213</v>
+        <v>0.875</v>
+      </c>
+      <c r="E72" s="9" t="n">
+        <v>0.0234</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1716200</v>
+        <v>2061200</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>1.46</v>
+        <v>0.6</v>
       </c>
       <c r="H72" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="I72" s="9" t="inlineStr">
+        <v>37.03</v>
+      </c>
+      <c r="I72" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.23</v>
+        <v>0.9</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.238</v>
+        <v>0.964</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3713,28 +3720,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.75</v>
+        <v>0.46</v>
       </c>
       <c r="E73" s="10" t="n">
-        <v>-0.0066</v>
+        <v>-0.0213</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1695300</v>
+        <v>2038900</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.29</v>
+        <v>0.21</v>
       </c>
       <c r="H73" t="n">
-        <v>53.38</v>
+        <v>42.44</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
@@ -3742,10 +3749,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.742</v>
+        <v>0.504</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.467</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3767,27 +3774,27 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>0.0177</v>
+        <v>6.9</v>
+      </c>
+      <c r="E74" s="9" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1694800</v>
+        <v>2024700</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.39</v>
+        <v>0.46</v>
       </c>
       <c r="H74" t="n">
-        <v>59.62</v>
-      </c>
-      <c r="I74" s="9" t="inlineStr">
+        <v>60.21</v>
+      </c>
+      <c r="I74" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>6.769</v>
+        <v>6.77</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>6.82</v>
@@ -3803,28 +3810,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>0</v>
+        <v>2.37</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1609400</v>
+        <v>1917100</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.18</v>
+        <v>0.44</v>
       </c>
       <c r="H75" t="n">
-        <v>24.34</v>
+        <v>33.25</v>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
@@ -3832,10 +3839,10 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.393</v>
+        <v>2.502</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.405</v>
+        <v>2.673</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3848,28 +3855,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E76" s="8" t="n">
-        <v>0.0071</v>
+        <v>0.745</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1556700</v>
+        <v>1913900</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.41</v>
+        <v>0.32</v>
       </c>
       <c r="H76" t="n">
-        <v>40.53</v>
+        <v>52.51</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
@@ -3877,10 +3884,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.441</v>
+        <v>0.742</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1.46</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3893,40 +3900,33 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>0</v>
+        <v>0.75</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1551400</v>
+        <v>1910300</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="H77" t="n">
-        <v>48.48</v>
-      </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="K77" s="2" t="n">
-        <v>0.5620000000000001</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n"/>
+      <c r="K77" s="2" t="n"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
     </row>
@@ -3938,28 +3938,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0348</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CLITE</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.205</v>
+        <v>2.76</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>-0.04650000000000001</v>
+        <v>-0.0072</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1519800</v>
+        <v>1871700</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>1.28</v>
+        <v>0.54</v>
       </c>
       <c r="H78" t="n">
-        <v>35.59</v>
+        <v>40.51</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3967,10 +3967,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.229</v>
+        <v>2.861</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.215</v>
+        <v>2.992</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3983,39 +3983,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>0</v>
+        <v>2.6</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1506900</v>
+        <v>1857200</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.43</v>
+        <v>0.31</v>
       </c>
       <c r="H79" t="n">
-        <v>75.12</v>
-      </c>
-      <c r="I79" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.74</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.62</v>
+        <v>2.606</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.609</v>
+        <v>2.611</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4028,39 +4028,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E80" s="8" t="n">
-        <v>0.0233</v>
+        <v>2.1</v>
+      </c>
+      <c r="E80" s="9" t="n">
+        <v>0.0048</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1501700</v>
+        <v>1844800</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.39</v>
+        <v>0.14</v>
       </c>
       <c r="H80" t="n">
-        <v>57.25</v>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.56</v>
+      </c>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.419</v>
+        <v>2.104</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.389</v>
+        <v>2.104</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4073,39 +4073,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E81" s="8" t="n">
-        <v>0.051</v>
+        <v>0.38</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1454800</v>
+        <v>1764100</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.66</v>
+        <v>0.2</v>
       </c>
       <c r="H81" t="n">
-        <v>29.31</v>
-      </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.34</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.902</v>
+        <v>0.393</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1.056</v>
+        <v>0.405</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4118,39 +4118,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>0</v>
+        <v>0.455</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>-0.0215</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1452400</v>
+        <v>1761900</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="H82" t="n">
-        <v>48.56</v>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33</v>
+      </c>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.769</v>
+        <v>0.487</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.771</v>
+        <v>0.545</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4163,39 +4163,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1436900</v>
+        <v>1758300</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.3</v>
+        <v>1.49</v>
       </c>
       <c r="H83" t="n">
-        <v>21.84</v>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.11</v>
+      </c>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.341</v>
+        <v>0.23</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1.528</v>
+        <v>0.238</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4208,39 +4208,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1434200</v>
+        <v>1738600</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="H84" t="n">
-        <v>68.73</v>
-      </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.82</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.801</v>
+        <v>0.623</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.776</v>
+        <v>0.618</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4253,39 +4253,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>TMK</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>0</v>
+        <v>2.9</v>
+      </c>
+      <c r="E85" s="9" t="n">
+        <v>0.0507</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1427600</v>
+        <v>1714400</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.11</v>
+        <v>1.72</v>
       </c>
       <c r="H85" t="n">
-        <v>47.56</v>
-      </c>
-      <c r="I85" s="9" t="inlineStr">
+        <v>56.98</v>
+      </c>
+      <c r="I85" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>2.103</v>
+        <v>2.78</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>2.104</v>
+        <v>2.836</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4298,28 +4298,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.61</v>
+        <v>1.18</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>-0.024</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1409600</v>
+        <v>1705200</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="H86" t="n">
-        <v>38.7</v>
+        <v>21.27</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4327,10 +4327,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.662</v>
+        <v>1.34</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.6870000000000001</v>
+        <v>1.528</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4343,28 +4343,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>-0.0137</v>
+        <v>0.44</v>
+      </c>
+      <c r="E87" s="9" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1391300</v>
+        <v>1691400</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.31</v>
+        <v>0.44</v>
       </c>
       <c r="H87" t="n">
-        <v>49.46</v>
+        <v>57.25</v>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>7.302</v>
+        <v>0.419</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>6.926</v>
+        <v>0.389</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4388,28 +4388,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E88" s="8" t="n">
-        <v>0.008500000000000001</v>
+        <v>5.59</v>
+      </c>
+      <c r="E88" s="9" t="n">
+        <v>0.0257</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1363000</v>
+        <v>1666500</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.29</v>
+        <v>0.43</v>
       </c>
       <c r="H88" t="n">
-        <v>64.34</v>
+        <v>53.1</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4417,10 +4417,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.082</v>
+        <v>5.494</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.944</v>
+        <v>5.383</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4433,39 +4433,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E89" s="10" t="n">
-        <v>-0.0103</v>
+        <v>0.445</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1343600</v>
+        <v>1653700</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.23</v>
+        <v>0.09</v>
       </c>
       <c r="H89" t="n">
-        <v>62.87</v>
-      </c>
-      <c r="I89" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.56</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.491</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.886</v>
+        <v>0.642</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4478,39 +4478,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E90" s="8" t="n">
-        <v>0.0217</v>
+        <v>0.61</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>-0.024</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1328200</v>
+        <v>1636400</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>1.34</v>
+        <v>0.2</v>
       </c>
       <c r="H90" t="n">
-        <v>52.67</v>
-      </c>
-      <c r="I90" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.7</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>2.773</v>
+        <v>0.662</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>2.834</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4523,39 +4523,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>-0.0385</v>
+        <v>0.825</v>
+      </c>
+      <c r="E91" s="9" t="n">
+        <v>0.051</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1327500</v>
+        <v>1623300</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.21</v>
+        <v>0.73</v>
       </c>
       <c r="H91" t="n">
-        <v>40.31</v>
-      </c>
-      <c r="I91" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>29.31</v>
+      </c>
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.268</v>
+        <v>0.902</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.288</v>
+        <v>1.056</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4568,39 +4568,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>-0.0123</v>
+        <v>0.825</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1325300</v>
+        <v>1584700</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="H92" t="n">
-        <v>46.38</v>
-      </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.73</v>
+      </c>
+      <c r="I92" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>2.443</v>
+        <v>0.801</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>2.404</v>
+        <v>0.776</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4613,28 +4613,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0348</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>CLITE</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1.31</v>
+        <v>0.2</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>-0.0076</v>
+        <v>-0.0698</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1313800</v>
+        <v>1569800</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.53</v>
+        <v>1.32</v>
       </c>
       <c r="H93" t="n">
-        <v>55.94</v>
+        <v>33.52</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
@@ -4642,10 +4642,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.271</v>
+        <v>0.228</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1.182</v>
+        <v>0.215</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4658,28 +4658,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E94" s="3" t="n">
-        <v>0</v>
+        <v>7.19</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>-0.0151</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1272800</v>
+        <v>1549100</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.44</v>
+        <v>0.34</v>
       </c>
       <c r="H94" t="n">
-        <v>51.47</v>
+        <v>49.26</v>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
@@ -4687,10 +4687,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.865</v>
+        <v>7.301</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0.86</v>
+        <v>6.926</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4703,39 +4703,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>-0.0293</v>
+        <v>1.3</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1266100</v>
+        <v>1526700</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.29</v>
+        <v>0.22</v>
       </c>
       <c r="H95" t="n">
-        <v>30.47</v>
-      </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.98</v>
+      </c>
+      <c r="I95" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>2.497</v>
+        <v>1.222</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>2.672</v>
+        <v>1.201</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4748,39 +4748,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.65</v>
+        <v>3.75</v>
       </c>
       <c r="E96" s="10" t="n">
-        <v>-0.0152</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1251600</v>
+        <v>1520100</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.98</v>
+        <v>0.47</v>
       </c>
       <c r="H96" t="n">
-        <v>70.83</v>
-      </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.79</v>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.599</v>
+        <v>3.819</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.538</v>
+        <v>3.724</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4793,39 +4793,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="E97" s="8" t="n">
-        <v>0.0129</v>
+        <v>0.41</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>-0.012</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1240700</v>
+        <v>1497200</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="H97" t="n">
-        <v>60.88</v>
-      </c>
-      <c r="I97" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.86</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>2.257</v>
+        <v>0.395</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>2.191</v>
+        <v>0.364</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4838,39 +4838,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>ECOFIRS</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>6.51</v>
+        <v>0.31</v>
       </c>
       <c r="E98" s="10" t="n">
-        <v>-0.0181</v>
+        <v>-0.0313</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1220800</v>
+        <v>1486500</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.2</v>
+        <v>0.97</v>
       </c>
       <c r="H98" t="n">
-        <v>55.94</v>
-      </c>
-      <c r="I98" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.44</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>6.264</v>
+        <v>0.322</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>5.969</v>
+        <v>0.333</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4883,39 +4883,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>-0.008</v>
+        <v>9.98</v>
+      </c>
+      <c r="E99" s="9" t="n">
+        <v>0.003</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1211300</v>
+        <v>1456300</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.14</v>
+        <v>0.11</v>
       </c>
       <c r="H99" t="n">
-        <v>41.72</v>
-      </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.16</v>
+      </c>
+      <c r="I99" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.282</v>
+        <v>9.991</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1.316</v>
+        <v>10.122</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4928,28 +4928,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>-0.0169</v>
+        <v>0.765</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1143500</v>
+        <v>1452400</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H100" t="n">
-        <v>49.07</v>
+        <v>48.56</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4957,10 +4957,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>1.171</v>
+        <v>0.769</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>1.145</v>
+        <v>0.771</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4973,28 +4973,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E101" s="8" t="n">
-        <v>0.0112</v>
+        <v>1.16</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1139000</v>
+        <v>1417400</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
       </c>
       <c r="H101" t="n">
-        <v>29.46</v>
+        <v>62.28</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.491</v>
+        <v>1.08</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.642</v>
+        <v>0.944</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5018,39 +5018,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>-0.0241</v>
+        <v>2.37</v>
+      </c>
+      <c r="E102" s="9" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1138500</v>
+        <v>1404000</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.13</v>
+        <v>0.42</v>
       </c>
       <c r="H102" t="n">
-        <v>42.07</v>
-      </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.52</v>
+      </c>
+      <c r="I102" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.43</v>
+        <v>2.258</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.438</v>
+        <v>2.192</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5063,39 +5063,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>6.51</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>-0.0181</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1132000</v>
+        <v>1400000</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.62</v>
+        <v>0.23</v>
       </c>
       <c r="H103" t="n">
-        <v>47.19</v>
-      </c>
-      <c r="I103" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.94</v>
+      </c>
+      <c r="I103" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.461</v>
+        <v>6.264</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.462</v>
+        <v>5.969</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5108,28 +5108,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>0</v>
+        <v>6.21</v>
+      </c>
+      <c r="E104" s="9" t="n">
+        <v>0.0016</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1131900</v>
+        <v>1386200</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.52</v>
+        <v>0.21</v>
       </c>
       <c r="H104" t="n">
-        <v>52.17</v>
+        <v>38.12</v>
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.263</v>
+        <v>6.343</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.242</v>
+        <v>6.686</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5153,39 +5153,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E105" s="3" t="n">
-        <v>0</v>
+        <v>0.635</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>-0.0379</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1088400</v>
+        <v>1364400</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.16</v>
+        <v>1.06</v>
       </c>
       <c r="H105" t="n">
-        <v>63.98</v>
-      </c>
-      <c r="I105" s="9" t="inlineStr">
+        <v>65.13</v>
+      </c>
+      <c r="I105" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.222</v>
+        <v>0.597</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1.201</v>
+        <v>0.538</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5198,39 +5198,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="E106" s="8" t="n">
-        <v>0.003</v>
+        <v>0.965</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1080500</v>
+        <v>1358600</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.09</v>
+        <v>0.23</v>
       </c>
       <c r="H106" t="n">
-        <v>47.16</v>
-      </c>
-      <c r="I106" s="9" t="inlineStr">
+        <v>62.87</v>
+      </c>
+      <c r="I106" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>9.991</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>10.122</v>
+        <v>0.886</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5243,28 +5243,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ECOFIRS</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.305</v>
+        <v>1.3</v>
       </c>
       <c r="E107" s="10" t="n">
-        <v>-0.0469</v>
+        <v>-0.0152</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1078200</v>
+        <v>1357600</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="H107" t="n">
-        <v>36.98</v>
+        <v>54.94</v>
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
@@ -5272,10 +5272,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.322</v>
+        <v>1.27</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.333</v>
+        <v>1.182</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5288,28 +5288,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="E108" s="8" t="n">
-        <v>0.0165</v>
+        <v>1.24</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1073400</v>
+        <v>1345100</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.28</v>
+        <v>0.16</v>
       </c>
       <c r="H108" t="n">
-        <v>51.98</v>
+        <v>41.72</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>5.489</v>
+        <v>1.282</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>5.382</v>
+        <v>1.316</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5333,39 +5333,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E109" s="10" t="n">
-        <v>-0.0182</v>
+        <v>8</v>
+      </c>
+      <c r="E109" s="9" t="n">
+        <v>0.0076</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1061900</v>
+        <v>1332400</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.12</v>
+        <v>0.38</v>
       </c>
       <c r="H109" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="I109" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.37</v>
+      </c>
+      <c r="I109" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.082</v>
+        <v>7.921</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1.052</v>
+        <v>7.949</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5378,39 +5378,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.65</v>
+        <v>0.25</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>-0.0076</v>
+        <v>-0.0385</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1061500</v>
+        <v>1327500</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.49</v>
+        <v>0.21</v>
       </c>
       <c r="H110" t="n">
-        <v>58.18</v>
-      </c>
-      <c r="I110" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.31</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.639</v>
+        <v>0.268</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.626</v>
+        <v>0.288</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5423,28 +5423,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>0.415</v>
+        <v>0.865</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1047600</v>
+        <v>1291200</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.18</v>
+        <v>0.44</v>
       </c>
       <c r="H111" t="n">
-        <v>55.93</v>
+        <v>51.47</v>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
@@ -5452,10 +5452,10 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.396</v>
+        <v>0.865</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0.364</v>
+        <v>0.86</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5468,39 +5468,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E112" s="10" t="n">
-        <v>-0.0061</v>
+        <v>0.46</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1039400</v>
+        <v>1279000</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.13</v>
+        <v>0.7</v>
       </c>
       <c r="H112" t="n">
-        <v>49.02</v>
-      </c>
-      <c r="I112" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.19</v>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.626</v>
+        <v>0.461</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>1.682</v>
+        <v>0.462</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5513,28 +5513,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>2.58</v>
+        <v>0.405</v>
       </c>
       <c r="E113" s="10" t="n">
-        <v>-0.0227</v>
+        <v>-0.0241</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1035600</v>
+        <v>1253200</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="H113" t="n">
-        <v>48.14</v>
+        <v>42.07</v>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
@@ -5542,10 +5542,10 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>2.604</v>
+        <v>0.43</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>2.611</v>
+        <v>0.438</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5558,28 +5558,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.275</v>
+        <v>0.82</v>
       </c>
       <c r="E114" s="10" t="n">
-        <v>-0.0179</v>
+        <v>-0.012</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1034600</v>
+        <v>1197700</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>1.12</v>
+        <v>0.32</v>
       </c>
       <c r="H114" t="n">
-        <v>50.42</v>
+        <v>50.45</v>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
@@ -5587,10 +5587,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.277</v>
+        <v>0.825</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.268</v>
+        <v>0.792</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5603,28 +5603,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>3.06</v>
+      </c>
+      <c r="E115" s="9" t="n">
+        <v>0.0033</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1024500</v>
+        <v>1195100</v>
       </c>
       <c r="G115" s="5" t="n">
         <v>0.36</v>
       </c>
       <c r="H115" t="n">
-        <v>31.45</v>
+        <v>39.07</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5632,10 +5632,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.535</v>
+        <v>3.131</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>3.291</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5648,28 +5648,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MULPHA</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>2.6</v>
+        <v>1.09</v>
       </c>
       <c r="E116" s="10" t="n">
-        <v>-0.0114</v>
+        <v>-0.0091</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1010200</v>
+        <v>1189900</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>9.050000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="H116" t="n">
-        <v>39.25</v>
+        <v>52.02</v>
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>2.691</v>
+        <v>1.083</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>2.793</v>
+        <v>1.052</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5693,39 +5693,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>-0.0116</v>
+        <v>1.64</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>991500</v>
+        <v>1165000</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.24</v>
+        <v>0.15</v>
       </c>
       <c r="H117" t="n">
-        <v>54.14</v>
-      </c>
-      <c r="I117" s="9" t="inlineStr">
+        <v>50.39</v>
+      </c>
+      <c r="I117" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>5.068</v>
+        <v>1.627</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>5.046</v>
+        <v>1.682</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5738,28 +5738,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="E118" s="8" t="n">
-        <v>0.01</v>
+        <v>1.17</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>984000</v>
+        <v>1157900</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="H118" t="n">
-        <v>48.67</v>
+        <v>50.55</v>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
@@ -5767,10 +5767,10 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.032</v>
+        <v>1.172</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0.962</v>
+        <v>1.146</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5783,39 +5783,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E119" s="8" t="n">
-        <v>0.0147</v>
+        <v>2.78</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>-0.0071</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>970900</v>
+        <v>1156700</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.47</v>
+        <v>0.13</v>
       </c>
       <c r="H119" t="n">
-        <v>56.09</v>
-      </c>
-      <c r="I119" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.68</v>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.364</v>
+        <v>2.793</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>1.343</v>
+        <v>2.683</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5828,28 +5828,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TIMECOM</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="E120" s="8" t="n">
-        <v>0.0019</v>
+        <v>0.89</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>-0.0111</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>923300</v>
+        <v>1139100</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.44</v>
+        <v>0.71</v>
       </c>
       <c r="H120" t="n">
-        <v>33.44</v>
+        <v>29</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5857,10 +5857,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>5.509</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>5.766</v>
+        <v>0.992</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5873,28 +5873,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>-0.0314</v>
+        <v>0.265</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>911900</v>
+        <v>1131900</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.15</v>
+        <v>0.52</v>
       </c>
       <c r="H121" t="n">
-        <v>32.26</v>
+        <v>52.17</v>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
@@ -5902,10 +5902,10 @@
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.679</v>
+        <v>0.263</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>1.752</v>
+        <v>0.242</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5918,39 +5918,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="E122" s="8" t="n">
-        <v>0.0053</v>
+        <v>5.13</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>-0.0116</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>897900</v>
+        <v>1113600</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="H122" t="n">
-        <v>49.94</v>
-      </c>
-      <c r="I122" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.14</v>
+      </c>
+      <c r="I122" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>3.824</v>
+        <v>5.068</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>3.725</v>
+        <v>5.046</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5963,40 +5963,36 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>1.02</v>
+        <v>0.205</v>
       </c>
       <c r="E123" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>883600</v>
+        <v>1085200</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>1.41</v>
+        <v>0.12</v>
       </c>
       <c r="H123" t="n">
-        <v>57.63</v>
-      </c>
-      <c r="I123" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J123" s="2" t="n">
-        <v>1.009</v>
-      </c>
-      <c r="K123" s="2" t="n">
-        <v>0.987</v>
-      </c>
+        <v>86.33</v>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="n"/>
+      <c r="K123" s="2" t="n"/>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
     </row>
@@ -6008,28 +6004,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>0.885</v>
+        <v>0.505</v>
       </c>
       <c r="E124" s="10" t="n">
-        <v>-0.0167</v>
+        <v>-0.0098</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>866100</v>
+        <v>1082400</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.54</v>
+        <v>0.38</v>
       </c>
       <c r="H124" t="n">
-        <v>28</v>
+        <v>29.82</v>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
@@ -6037,10 +6033,10 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.534</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0.992</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6053,39 +6049,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>-0.0024</v>
+        <v>0.655</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>862400</v>
+        <v>1081100</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.21</v>
+        <v>0.5</v>
       </c>
       <c r="H125" t="n">
-        <v>34.89</v>
-      </c>
-      <c r="I125" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.54</v>
+      </c>
+      <c r="I125" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>4.358</v>
+        <v>0.64</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>4.661</v>
+        <v>0.627</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6098,39 +6094,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>TOYOVEN</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E126" s="10" t="n">
-        <v>-0.006</v>
+        <v>0.24</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>842400</v>
+        <v>1054700</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.22</v>
+        <v>0.96</v>
       </c>
       <c r="H126" t="n">
-        <v>51.38</v>
-      </c>
-      <c r="I126" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.09</v>
+      </c>
+      <c r="I126" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.825</v>
+        <v>0.226</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.792</v>
+        <v>0.212</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6143,39 +6139,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>0</v>
+        <v>0.76</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>831200</v>
+        <v>1044100</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.09</v>
+        <v>0.37</v>
       </c>
       <c r="H127" t="n">
-        <v>51.92</v>
-      </c>
-      <c r="I127" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.56</v>
+      </c>
+      <c r="I127" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>2.795</v>
+        <v>0.745</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>2.683</v>
+        <v>0.707</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6188,39 +6184,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>MULPHA</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>0.555</v>
+        <v>2.6</v>
       </c>
       <c r="E128" s="10" t="n">
-        <v>-0.0089</v>
+        <v>-0.0114</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>823700</v>
+        <v>1035200</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.5</v>
+        <v>9.27</v>
       </c>
       <c r="H128" t="n">
-        <v>44.46</v>
-      </c>
-      <c r="I128" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.25</v>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.5590000000000001</v>
+        <v>2.691</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0.576</v>
+        <v>2.793</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6233,39 +6229,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="E129" s="8" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.275</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>802800</v>
+        <v>1034600</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.16</v>
+        <v>1.12</v>
       </c>
       <c r="H129" t="n">
-        <v>51.32</v>
-      </c>
-      <c r="I129" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.42</v>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>4.376</v>
+        <v>0.277</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>4.432</v>
+        <v>0.268</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6278,39 +6274,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="E130" s="8" t="n">
-        <v>0.005</v>
+        <v>1.01</v>
+      </c>
+      <c r="E130" s="9" t="n">
+        <v>0.01</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>773500</v>
+        <v>1021000</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="H130" t="n">
-        <v>54.17</v>
-      </c>
-      <c r="I130" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.67</v>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>7.919</v>
+        <v>1.032</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>7.949</v>
+        <v>0.962</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6323,28 +6319,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>10.6</v>
+        <v>1.54</v>
       </c>
       <c r="E131" s="10" t="n">
-        <v>-0.0075</v>
+        <v>-0.0314</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>736400</v>
+        <v>997100</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="H131" t="n">
-        <v>55.74</v>
+        <v>32.26</v>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
@@ -6352,10 +6348,10 @@
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>10.446</v>
+        <v>1.679</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>9.83</v>
+        <v>1.752</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6368,39 +6364,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E132" s="3" t="n">
-        <v>0</v>
+        <v>1.38</v>
+      </c>
+      <c r="E132" s="9" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>731800</v>
+        <v>970900</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.23</v>
+        <v>0.47</v>
       </c>
       <c r="H132" t="n">
-        <v>33.03</v>
-      </c>
-      <c r="I132" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.09</v>
+      </c>
+      <c r="I132" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.879</v>
+        <v>1.364</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0.9409999999999999</v>
+        <v>1.343</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6413,39 +6409,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>0</v>
+        <v>0.61</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>-0.0394</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>728700</v>
+        <v>966000</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="H133" t="n">
-        <v>54.56</v>
-      </c>
-      <c r="I133" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.33</v>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>2.114</v>
+        <v>0.697</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>2.074</v>
+        <v>0.74</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6458,39 +6454,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>TIMECOM</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E134" s="10" t="n">
-        <v>-0.0224</v>
+        <v>5.31</v>
+      </c>
+      <c r="E134" s="9" t="n">
+        <v>0.0019</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>688700</v>
+        <v>964700</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="H134" t="n">
-        <v>54.78</v>
-      </c>
-      <c r="I134" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.44</v>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.65</v>
+        <v>5.509</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0.569</v>
+        <v>5.766</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6503,39 +6499,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>0.765</v>
+        <v>4.2</v>
       </c>
       <c r="E135" s="10" t="n">
-        <v>-0.0192</v>
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>674100</v>
+        <v>959600</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="H135" t="n">
-        <v>55.48</v>
-      </c>
-      <c r="I135" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.42</v>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.745</v>
+        <v>4.357</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>0.707</v>
+        <v>4.661</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6548,28 +6544,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>MAXIS</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>0.58</v>
+        <v>3.52</v>
       </c>
       <c r="E136" s="10" t="n">
-        <v>-0.0333</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>666700</v>
+        <v>936200</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.17</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H136" t="n">
-        <v>47.52</v>
+        <v>48.35</v>
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
@@ -6577,10 +6573,10 @@
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.594</v>
+        <v>3.527</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>0.586</v>
+        <v>3.58</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6593,39 +6589,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>6.21</v>
-      </c>
-      <c r="E137" s="8" t="n">
-        <v>0.0016</v>
+        <v>4.41</v>
+      </c>
+      <c r="E137" s="9" t="n">
+        <v>0.0023</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>666400</v>
+        <v>921500</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H137" t="n">
-        <v>38.12</v>
-      </c>
-      <c r="I137" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.93</v>
+      </c>
+      <c r="I137" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>6.343</v>
+        <v>4.375</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>6.686</v>
+        <v>4.432</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6638,28 +6634,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0.615</v>
+        <v>10.62</v>
       </c>
       <c r="E138" s="10" t="n">
-        <v>-0.0315</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>665200</v>
+        <v>895600</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="H138" t="n">
-        <v>31.89</v>
+        <v>56.15</v>
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
@@ -6667,10 +6663,10 @@
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.698</v>
+        <v>10.448</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0.74</v>
+        <v>9.831</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6683,39 +6679,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="E139" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>660000</v>
+        <v>883600</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.11</v>
+        <v>1.41</v>
       </c>
       <c r="H139" t="n">
-        <v>50.96</v>
-      </c>
-      <c r="I139" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.63</v>
+      </c>
+      <c r="I139" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>1.103</v>
+        <v>1.009</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0.911</v>
+        <v>0.987</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6728,39 +6724,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="E140" s="8" t="n">
-        <v>0.0068</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>657600</v>
+        <v>849500</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.24</v>
+        <v>0.52</v>
       </c>
       <c r="H140" t="n">
-        <v>50.12</v>
-      </c>
-      <c r="I140" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.59</v>
+      </c>
+      <c r="I140" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>3.007</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>2.861</v>
+        <v>0.576</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6773,39 +6769,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>-0.0143</v>
+        <v>2.13</v>
+      </c>
+      <c r="E141" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>629500</v>
+        <v>841400</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="H141" t="n">
-        <v>70.19</v>
-      </c>
-      <c r="I141" s="9" t="inlineStr">
+        <v>54.56</v>
+      </c>
+      <c r="I141" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>2.646</v>
+        <v>2.114</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>2.466</v>
+        <v>2.074</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6818,39 +6814,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E142" s="10" t="n">
-        <v>-0.0183</v>
+        <v>1.78</v>
+      </c>
+      <c r="E142" s="9" t="n">
+        <v>0.023</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>626600</v>
+        <v>798600</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="H142" t="n">
-        <v>47.29</v>
-      </c>
-      <c r="I142" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.42</v>
+      </c>
+      <c r="I142" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.553</v>
+        <v>1.809</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>0.522</v>
+        <v>1.938</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6863,28 +6859,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E143" s="3" t="n">
-        <v>0</v>
+        <v>2.72</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>-0.0037</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>617300</v>
+        <v>786200</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.14</v>
+        <v>0.06</v>
       </c>
       <c r="H143" t="n">
-        <v>26.8</v>
+        <v>47.89</v>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
@@ -6892,10 +6888,10 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.957</v>
+        <v>2.748</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>1.04</v>
+        <v>2.746</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6908,28 +6904,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E144" s="10" t="n">
-        <v>-0.009000000000000001</v>
+        <v>0.835</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>616000</v>
+        <v>775600</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="H144" t="n">
-        <v>44.85</v>
+        <v>33.03</v>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
@@ -6937,10 +6933,10 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>1.14</v>
+        <v>0.879</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>1.108</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6953,39 +6949,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E145" s="8" t="n">
-        <v>0.008</v>
+        <v>13.06</v>
+      </c>
+      <c r="E145" s="9" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>608700</v>
+        <v>775600</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.33</v>
+        <v>0.12</v>
       </c>
       <c r="H145" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I145" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.34</v>
+      </c>
+      <c r="I145" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>1.366</v>
+        <v>13.02</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>1.447</v>
+        <v>13.348</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -6998,39 +6994,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="E146" s="8" t="n">
-        <v>0.0077</v>
+        <v>2.97</v>
+      </c>
+      <c r="E146" s="9" t="n">
+        <v>0.0034</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>602100</v>
+        <v>749500</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.09</v>
+        <v>0.28</v>
       </c>
       <c r="H146" t="n">
-        <v>50.35</v>
-      </c>
-      <c r="I146" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.66</v>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>13.022</v>
+        <v>3.006</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>13.348</v>
+        <v>2.861</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7043,39 +7039,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E147" s="8" t="n">
-        <v>0.0071</v>
+        <v>0.53</v>
+      </c>
+      <c r="E147" s="10" t="n">
+        <v>-0.0275</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>572900</v>
+        <v>697500</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="H147" t="n">
-        <v>59.69</v>
-      </c>
-      <c r="I147" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.28</v>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>2.715</v>
+        <v>0.553</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>2.323</v>
+        <v>0.522</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7088,28 +7084,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E148" s="10" t="n">
-        <v>-0.0146</v>
+        <v>1.08</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>565600</v>
+        <v>693000</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="H148" t="n">
-        <v>42.26</v>
+        <v>50.96</v>
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
@@ -7117,10 +7113,10 @@
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.736</v>
+        <v>1.103</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.911</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7133,39 +7129,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="E149" s="8" t="n">
-        <v>0.0105</v>
+        <v>0.655</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>-0.0224</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>564600</v>
+        <v>688700</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="H149" t="n">
-        <v>58.56</v>
-      </c>
-      <c r="I149" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.78</v>
+      </c>
+      <c r="I149" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>2.808</v>
+        <v>0.65</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>2.294</v>
+        <v>0.569</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7178,28 +7174,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E150" s="8" t="n">
-        <v>0.0051</v>
+        <v>0.58</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>564200</v>
+        <v>671500</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.22</v>
+        <v>0.17</v>
       </c>
       <c r="H150" t="n">
-        <v>45.26</v>
+        <v>47.52</v>
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
@@ -7207,10 +7203,10 @@
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>2.072</v>
+        <v>0.594</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>1.993</v>
+        <v>0.586</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7223,39 +7219,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E151" s="8" t="n">
-        <v>0.0161</v>
+        <v>2.8</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>-0.0036</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>545600</v>
+        <v>668900</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.26</v>
+        <v>0.2</v>
       </c>
       <c r="H151" t="n">
-        <v>45.31</v>
-      </c>
-      <c r="I151" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.33</v>
+      </c>
+      <c r="I151" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>1.302</v>
+        <v>2.712</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>1.296</v>
+        <v>2.323</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7268,39 +7264,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>CBIP</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E152" s="3" t="n">
-        <v>0</v>
+        <v>2.75</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>533400</v>
+        <v>660500</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>17.56</v>
+        <v>0.45</v>
       </c>
       <c r="H152" t="n">
-        <v>40.24</v>
-      </c>
-      <c r="I152" s="9" t="inlineStr">
+        <v>68.58</v>
+      </c>
+      <c r="I152" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>1.073</v>
+        <v>2.645</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>1.113</v>
+        <v>2.466</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7313,39 +7309,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="E153" s="3" t="n">
-        <v>0</v>
+        <v>1.1</v>
+      </c>
+      <c r="E153" s="10" t="n">
+        <v>-0.009000000000000001</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>525300</v>
+        <v>648100</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.41</v>
+        <v>0.19</v>
       </c>
       <c r="H153" t="n">
-        <v>48.09</v>
-      </c>
-      <c r="I153" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.85</v>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>2.117</v>
+        <v>1.14</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>2.255</v>
+        <v>1.108</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
@@ -7358,28 +7354,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E154" s="10" t="n">
-        <v>-0.0037</v>
+        <v>2.87</v>
+      </c>
+      <c r="E154" s="9" t="n">
+        <v>0.0035</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>524400</v>
+        <v>646500</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="H154" t="n">
-        <v>47.89</v>
+        <v>57.8</v>
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
@@ -7387,10 +7383,10 @@
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>2.748</v>
+        <v>2.806</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>2.746</v>
+        <v>2.293</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7403,28 +7399,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="E155" s="8" t="n">
-        <v>0.0033</v>
+        <v>0.915</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>-0.0054</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>519600</v>
+        <v>636000</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="H155" t="n">
-        <v>39.07</v>
+        <v>25.71</v>
       </c>
       <c r="I155" s="6" t="inlineStr">
         <is>
@@ -7432,10 +7428,10 @@
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>3.131</v>
+        <v>0.956</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>3.291</v>
+        <v>1.04</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7448,39 +7444,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>0.635</v>
+        <v>1.25</v>
       </c>
       <c r="E156" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>515000</v>
+        <v>635700</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.48</v>
+        <v>0.35</v>
       </c>
       <c r="H156" t="n">
-        <v>55.02</v>
-      </c>
-      <c r="I156" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.15</v>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.633</v>
+        <v>1.365</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>0.632</v>
+        <v>1.447</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7508,15 +7504,15 @@
         <v>-0.004</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>506900</v>
+        <v>599400</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="H157" t="n">
         <v>46.1</v>
       </c>
-      <c r="I157" s="9" t="inlineStr">
+      <c r="I157" s="8" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
@@ -7538,45 +7534,585 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="E158" s="8" t="n">
-        <v>0.0172</v>
+        <v>0.67</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>-0.0219</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>503700</v>
+        <v>591300</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="H158" t="n">
-        <v>39.74</v>
-      </c>
-      <c r="I158" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.71</v>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>1.808</v>
+        <v>0.735</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>1.937</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
     </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>MCEMENT</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E159" s="9" t="n">
+        <v>0.0115</v>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v>585600</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H159" t="n">
+        <v>38.44</v>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>5.427</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>5.757</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="7" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>583700</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H160" t="n">
+        <v>44.64</v>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>2.071</v>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>1.993</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="7" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SIMEPROP</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F161" s="4" t="n">
+        <v>572500</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H161" t="n">
+        <v>54.14</v>
+      </c>
+      <c r="I161" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>1.264</v>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="7" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>565000</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H162" t="n">
+        <v>55.02</v>
+      </c>
+      <c r="I162" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="7" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E163" s="9" t="n">
+        <v>0.0161</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>550500</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H163" t="n">
+        <v>45.31</v>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>1.302</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>1.296</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="7" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>7076</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>CBIP</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" s="4" t="n">
+        <v>536400</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="H164" t="n">
+        <v>40.24</v>
+      </c>
+      <c r="I164" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>1.073</v>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="7" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>5401</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>TROP</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E165" s="9" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v>535300</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H165" t="n">
+        <v>48.65</v>
+      </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>1.185</v>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>1.188</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="7" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="E166" s="9" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F166" s="4" t="n">
+        <v>531300</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H166" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="I166" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>3.338</v>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>3.571</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="7" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>6971</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>KOBAY</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F167" s="4" t="n">
+        <v>526300</v>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H167" t="n">
+        <v>48.09</v>
+      </c>
+      <c r="I167" s="8" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>2.117</v>
+      </c>
+      <c r="K167" s="2" t="n">
+        <v>2.255</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="7" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>0376</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>IAB</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F168" s="4" t="n">
+        <v>525300</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H168" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K168" s="2" t="n">
+        <v>1.271</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="7" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>7163</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>PJBUMI</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F169" s="4" t="n">
+        <v>518800</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H169" t="n">
+        <v>61.36</v>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>4.168</v>
+      </c>
+      <c r="K169" s="2" t="n">
+        <v>4.024</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="7" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>0293</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>KJTS</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E170" s="9" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="F170" s="4" t="n">
+        <v>502300</v>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H170" t="n">
+        <v>38.43</v>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>0.927</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>1.015</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M158"/>
+  <autoFilter ref="A1:M170"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-22/bursa-report-2026-10-22.xlsx
+++ b/docs/downloads/2026-10-22/bursa-report-2026-10-22.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-22" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-22'!$A$1:$M$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-22'!$A$1:$M$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M189"/>
+  <dimension ref="A1:M192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.1074</v>
+        <v>0.1322</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>7194900</v>
+        <v>7395000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>61.4</v>
+        <v>63.23</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>1.241</v>
+        <v>1.244</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1.097</v>
+        <v>1.098</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -598,62 +598,45 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 61.4未超买，现价高于50日均线约22%，技术面信号偏可靠。</t>
+          <t>SAR转多信号，RSI 63.23未超买，现价高于50日均线约25%，技术面信号可靠性较高。</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>信号</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>4723</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>JAKS</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0.0294</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>33203300</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>57.97</v>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>🎯 SAR 转多</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr">
-        <is>
-          <t>SAR转多信号，RSI 57.97未超买，现价高于50日均线约21.5%，技术面信号较为可靠。</t>
-        </is>
-      </c>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0479</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0479.KL</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>75234900</v>
+      </c>
+      <c r="G3" s="12" t="n"/>
+      <c r="I3" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J3" s="9" t="n"/>
+      <c r="K3" s="9" t="n"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" s="14" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -663,31 +646,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0479.KL</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>0</v>
+        <v>0.055</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>0.1</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>71973100</v>
-      </c>
-      <c r="G4" s="12" t="n"/>
+        <v>67677900</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H4" t="n">
+        <v>25.86</v>
+      </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>0.284</v>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
     </row>
@@ -699,39 +691,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
       <c r="E5" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>65484000</v>
+        <v>33500500</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.18</v>
+        <v>0.55</v>
       </c>
       <c r="H5" t="n">
-        <v>23.85</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.15</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.104</v>
+        <v>0.159</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.284</v>
+        <v>0.144</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -753,19 +745,19 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.095</v>
+        <v>0.09</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>0.2667</v>
+        <v>0.2</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>24736600</v>
+        <v>25231100</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>63.46</v>
+        <v>64.73</v>
       </c>
       <c r="H6" t="n">
-        <v>81.28</v>
+        <v>77.75</v>
       </c>
       <c r="I6" s="16" t="inlineStr">
         <is>
@@ -804,7 +796,7 @@
         <v>-0.0145</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>21650900</v>
+        <v>21718600</v>
       </c>
       <c r="G7" s="12" t="n">
         <v>0.26</v>
@@ -843,19 +835,19 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.47</v>
+        <v>0.465</v>
       </c>
       <c r="E8" s="17" t="n">
-        <v>-0.0105</v>
+        <v>-0.0211</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>19563600</v>
+        <v>19563700</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>0.55</v>
       </c>
       <c r="H8" t="n">
-        <v>79.78</v>
+        <v>77.25</v>
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
@@ -933,19 +925,19 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0</v>
+        <v>0.71</v>
+      </c>
+      <c r="E10" s="17" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>18091900</v>
+        <v>18092000</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>0.71</v>
       </c>
       <c r="H10" t="n">
-        <v>81.19</v>
+        <v>78.7</v>
       </c>
       <c r="I10" s="16" t="inlineStr">
         <is>
@@ -978,13 +970,13 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.23</v>
+        <v>0.225</v>
       </c>
       <c r="E11" s="17" t="n">
-        <v>-0.098</v>
+        <v>-0.1176</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>17660000</v>
+        <v>17690000</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>0.8100000000000001</v>
@@ -1022,10 +1014,10 @@
         <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>14559400</v>
+        <v>14659400</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="H12" t="n">
         <v>47.42</v>
@@ -1067,7 +1059,7 @@
         <v>0.3333</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>13661900</v>
+        <v>13662000</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>35.99</v>
@@ -1112,10 +1104,10 @@
         <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>13091100</v>
+        <v>13262100</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H14" t="n">
         <v>46.09</v>
@@ -1142,39 +1134,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7209</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CHEETAH</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>0.0417</v>
+        <v>2.03</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>-0.0193</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>12025000</v>
+        <v>12291500</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>20.5</v>
+        <v>0.44</v>
       </c>
       <c r="H15" t="n">
-        <v>56.11</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.52</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.118</v>
+        <v>1.957</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.117</v>
+        <v>1.776</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1187,39 +1179,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>7209</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>CHEETAH</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>-0.0588</v>
+        <v>0.125</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>11691500</v>
+        <v>12025000</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.97</v>
+        <v>20.5</v>
       </c>
       <c r="H16" t="n">
-        <v>51.97</v>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.11</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.397</v>
+        <v>0.118</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.381</v>
+        <v>0.117</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1232,28 +1224,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>2.03</v>
+        <v>0.4</v>
       </c>
       <c r="E17" s="17" t="n">
-        <v>-0.0193</v>
+        <v>-0.0588</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>11673400</v>
+        <v>11788700</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.42</v>
+        <v>0.98</v>
       </c>
       <c r="H17" t="n">
-        <v>57.52</v>
+        <v>51.97</v>
       </c>
       <c r="I17" s="16" t="inlineStr">
         <is>
@@ -1261,10 +1253,10 @@
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1.957</v>
+        <v>0.397</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>1.776</v>
+        <v>0.381</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1292,7 +1284,7 @@
         <v>0.006500000000000001</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>11595600</v>
+        <v>11596200</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>0.75</v>
@@ -1337,7 +1329,7 @@
         <v>-0.0165</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>11330900</v>
+        <v>11380100</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>0.15</v>
@@ -1376,19 +1368,19 @@
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0</v>
+        <v>0.185</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>0.0278</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>11038500</v>
+        <v>11124400</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>0.53</v>
       </c>
       <c r="H20" t="n">
-        <v>44.12</v>
+        <v>48.09</v>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
@@ -1421,19 +1413,19 @@
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.98</v>
+        <v>0.975</v>
       </c>
       <c r="E21" s="15" t="n">
-        <v>0.0155</v>
+        <v>0.0104</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>8028100</v>
+        <v>8106200</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="H21" t="n">
-        <v>44.26</v>
+        <v>43.51</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -1472,7 +1464,7 @@
         <v>0.0435</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>7967300</v>
+        <v>7967400</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>0.4</v>
@@ -1502,39 +1494,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.63</v>
+        <v>0.15</v>
       </c>
       <c r="E23" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>7558000</v>
+        <v>7623400</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.71</v>
+        <v>0.52</v>
       </c>
       <c r="H23" t="n">
-        <v>58.13</v>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.8</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.621</v>
+        <v>0.154</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.617</v>
+        <v>0.182</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1547,39 +1539,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.15</v>
+        <v>0.63</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>7532800</v>
+        <v>7558000</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.52</v>
+        <v>0.71</v>
       </c>
       <c r="H24" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.13</v>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.154</v>
+        <v>0.621</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.182</v>
+        <v>0.617</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1607,10 +1599,10 @@
         <v>0.0833</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>7285700</v>
+        <v>7335700</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="H25" t="n">
         <v>49.57</v>
@@ -1652,7 +1644,7 @@
         <v>-0.0116</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>6973500</v>
+        <v>7013500</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>0.19</v>
@@ -1691,19 +1683,19 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>7.31</v>
+        <v>7.32</v>
       </c>
       <c r="E27" s="17" t="n">
-        <v>-0.008100000000000001</v>
+        <v>-0.0068</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>6724300</v>
+        <v>6734900</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>0.63</v>
       </c>
       <c r="H27" t="n">
-        <v>39.55</v>
+        <v>39.94</v>
       </c>
       <c r="I27" s="16" t="inlineStr">
         <is>
@@ -1711,7 +1703,7 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>7.421</v>
+        <v>7.422</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>7.866</v>
@@ -1742,7 +1734,7 @@
         <v>0.0021</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>6501900</v>
+        <v>6543800</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>0.31</v>
@@ -1787,10 +1779,10 @@
         <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>6360800</v>
+        <v>6460800</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>3.46</v>
+        <v>3.52</v>
       </c>
       <c r="H29" t="n">
         <v>33.05</v>
@@ -1817,28 +1809,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5259</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AVANGAAD</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.29</v>
+        <v>2.5</v>
       </c>
       <c r="E30" s="17" t="n">
-        <v>-0.0169</v>
+        <v>-0.031</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>6163000</v>
+        <v>6253200</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>1.83</v>
+        <v>0.34</v>
       </c>
       <c r="H30" t="n">
-        <v>24.93</v>
+        <v>43.09</v>
       </c>
       <c r="I30" s="13" t="inlineStr">
         <is>
@@ -1846,10 +1838,10 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.295</v>
+        <v>2.618</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.295</v>
+        <v>2.56</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1862,39 +1854,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>AVANGAAD</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0</v>
+        <v>0.29</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>-0.0169</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>5967300</v>
+        <v>6163000</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.36</v>
+        <v>1.83</v>
       </c>
       <c r="H31" t="n">
-        <v>55.59</v>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.93</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.295</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.295</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1922,10 +1914,10 @@
         <v>0.0014</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>5966000</v>
+        <v>6048900</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H32" t="n">
         <v>33.24</v>
@@ -1952,39 +1944,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>-0.0271</v>
+        <v>0.82</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>5665000</v>
+        <v>5973400</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="H33" t="n">
-        <v>43.61</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.59</v>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>2.619</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>2.56</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1997,39 +1989,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0301</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ZANTAT</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.165</v>
+        <v>0.19</v>
       </c>
       <c r="E34" s="17" t="n">
-        <v>-0.0294</v>
+        <v>-0.0256</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>5664800</v>
+        <v>5780800</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>23.18</v>
+        <v>0.27</v>
       </c>
       <c r="H34" t="n">
-        <v>58.87</v>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.78</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.156</v>
+        <v>0.212</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.156</v>
+        <v>0.232</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2042,28 +2034,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0301</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>ZANTAT</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.38</v>
+        <v>0.165</v>
       </c>
       <c r="E35" s="17" t="n">
-        <v>-0.0732</v>
+        <v>-0.0294</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5513700</v>
+        <v>5669500</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.51</v>
+        <v>23.2</v>
       </c>
       <c r="H35" t="n">
-        <v>28.09</v>
+        <v>58.87</v>
       </c>
       <c r="I35" s="16" t="inlineStr">
         <is>
@@ -2071,10 +2063,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.489</v>
+        <v>0.156</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.595</v>
+        <v>0.156</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2087,39 +2079,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.185</v>
+        <v>0.38</v>
       </c>
       <c r="E36" s="17" t="n">
-        <v>-0.0513</v>
+        <v>-0.0732</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5508000</v>
+        <v>5563800</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.26</v>
+        <v>0.52</v>
       </c>
       <c r="H36" t="n">
-        <v>31.94</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>28.09</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.212</v>
+        <v>0.489</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.232</v>
+        <v>0.595</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2147,10 +2139,10 @@
         <v>-0.021</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5449200</v>
+        <v>5506300</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="H37" t="n">
         <v>20.45</v>
@@ -2186,19 +2178,19 @@
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>5.32</v>
+        <v>5.3</v>
       </c>
       <c r="E38" s="17" t="n">
-        <v>-0.0037</v>
+        <v>-0.0075</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5382600</v>
+        <v>5469200</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="H38" t="n">
-        <v>43.36</v>
+        <v>42.64</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2206,7 +2198,7 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>5.46</v>
+        <v>5.458</v>
       </c>
       <c r="K38" s="9" t="n">
         <v>5.497</v>
@@ -2222,28 +2214,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SINARAN</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>-0.04</v>
+        <v>0.055</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>5030500</v>
+        <v>5120800</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>1.65</v>
+        <v>0.8</v>
       </c>
       <c r="H39" t="n">
-        <v>53.31</v>
+        <v>60.5</v>
       </c>
       <c r="I39" s="16" t="inlineStr">
         <is>
@@ -2251,10 +2243,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.117</v>
+        <v>0.049</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.109</v>
+        <v>0.047</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2267,39 +2259,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>SINARAN</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="E40" s="17" t="n">
-        <v>-0.0385</v>
+        <v>-0.04</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4835200</v>
+        <v>5030500</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.6</v>
+        <v>1.65</v>
       </c>
       <c r="H40" t="n">
-        <v>28.63</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.31</v>
+      </c>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.271</v>
+        <v>0.117</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.296</v>
+        <v>0.109</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2312,39 +2304,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>0.0357</v>
+        <v>0.255</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>4585400</v>
+        <v>4855600</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.73</v>
+        <v>0.6</v>
       </c>
       <c r="H41" t="n">
-        <v>33.67</v>
-      </c>
-      <c r="I41" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.319</v>
+        <v>0.271</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.363</v>
+        <v>0.296</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2357,39 +2349,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>-0.0364</v>
+        <v>0.29</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>4576700</v>
+        <v>4600500</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.43</v>
+        <v>0.74</v>
       </c>
       <c r="H42" t="n">
-        <v>39.76</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.67</v>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.29</v>
+        <v>0.319</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.28</v>
+        <v>0.363</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2402,39 +2394,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>0.0255</v>
+        <v>0.265</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>-0.0364</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>4518900</v>
+        <v>4576700</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.74</v>
+        <v>0.43</v>
       </c>
       <c r="H43" t="n">
-        <v>60.28</v>
-      </c>
-      <c r="I43" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.76</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>1.935</v>
+        <v>0.29</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>1.953</v>
+        <v>0.28</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2447,39 +2439,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>-0.0123</v>
+        <v>2.02</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>0.0306</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>4373000</v>
+        <v>4523100</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.4</v>
+        <v>0.74</v>
       </c>
       <c r="H44" t="n">
-        <v>46.38</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.29</v>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>2.443</v>
+        <v>1.936</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>2.404</v>
+        <v>1.954</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2492,28 +2484,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>0</v>
+        <v>2.4</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>-0.0164</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>4114300</v>
+        <v>4398900</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="H45" t="n">
-        <v>40.57</v>
+        <v>45.19</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
@@ -2521,10 +2513,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>2.124</v>
+        <v>2.442</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>2.235</v>
+        <v>2.404</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2537,28 +2529,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.435</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E46" s="17" t="n">
-        <v>-0.0114</v>
+        <v>-0.0174</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>4023200</v>
+        <v>4220300</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="H46" t="n">
-        <v>55.06</v>
+        <v>50.01</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2566,10 +2558,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.427</v>
+        <v>0.571</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.378</v>
+        <v>0.545</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2582,28 +2574,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E47" s="17" t="n">
-        <v>-0.04019999999999999</v>
+        <v>2.07</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3977900</v>
+        <v>4181700</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.88</v>
+        <v>0.36</v>
       </c>
       <c r="H47" t="n">
-        <v>52.86</v>
+        <v>40.57</v>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
@@ -2611,10 +2603,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.848</v>
+        <v>2.124</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.61</v>
+        <v>2.235</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2627,28 +2619,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>6.92</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.44</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3939400</v>
+        <v>4024400</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.37</v>
+        <v>0.19</v>
       </c>
       <c r="H48" t="n">
-        <v>39.44</v>
+        <v>56.58</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2656,10 +2648,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>7.116</v>
+        <v>0.427</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>7.541</v>
+        <v>0.378</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2672,28 +2664,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.825</v>
       </c>
       <c r="E49" s="17" t="n">
-        <v>-0.0174</v>
+        <v>-0.0517</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3922600</v>
+        <v>3995300</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.19</v>
+        <v>0.89</v>
       </c>
       <c r="H49" t="n">
-        <v>50.01</v>
+        <v>52.18</v>
       </c>
       <c r="I49" s="13" t="inlineStr">
         <is>
@@ -2701,10 +2693,10 @@
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.571</v>
+        <v>0.847</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.545</v>
+        <v>0.609</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2717,28 +2709,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>0</v>
+        <v>6.92</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3781300</v>
+        <v>3954600</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1.09</v>
+        <v>0.37</v>
       </c>
       <c r="H50" t="n">
-        <v>46.02</v>
+        <v>39.44</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2746,10 +2738,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>2.041</v>
+        <v>7.116</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>2.067</v>
+        <v>7.541</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2762,28 +2754,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>-0.0171</v>
+        <v>2.03</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3460100</v>
+        <v>3832700</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.45</v>
+        <v>1.11</v>
       </c>
       <c r="H51" t="n">
-        <v>33.86</v>
+        <v>46.02</v>
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
@@ -2791,10 +2783,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>1.215</v>
+        <v>2.041</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>1.303</v>
+        <v>2.067</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2807,28 +2799,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>5.69</v>
-      </c>
-      <c r="E52" s="15" t="n">
-        <v>0.0035</v>
+        <v>1.15</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>-0.0171</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3430000</v>
+        <v>3508200</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="H52" t="n">
-        <v>35.83</v>
+        <v>33.86</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2836,10 +2828,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>5.843</v>
+        <v>1.215</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>6.125</v>
+        <v>1.303</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2852,39 +2844,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.38</v>
+        <v>5.69</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>0.0133</v>
+        <v>0.0035</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>3343400</v>
+        <v>3463600</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="H53" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="I53" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.83</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.372</v>
+        <v>5.843</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.37</v>
+        <v>6.125</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2912,10 +2904,10 @@
         <v>0.035</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>3342900</v>
+        <v>3389600</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="H54" t="n">
         <v>50.52</v>
@@ -2942,28 +2934,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>-0.0417</v>
+        <v>3.91</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>0.0289</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>3246700</v>
+        <v>3378900</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="H55" t="n">
-        <v>48.41</v>
+        <v>59.59</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2971,10 +2963,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.352</v>
+        <v>3.708</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.329</v>
+        <v>3.15</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2987,39 +2979,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>3.99</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>0.005</v>
+        <v>0.375</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>3231200</v>
+        <v>3349800</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="H56" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.91</v>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>3.959</v>
+        <v>0.372</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>3.605</v>
+        <v>0.37</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3032,28 +3024,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>0.0076</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3120500</v>
+        <v>3256100</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>1.76</v>
+        <v>0.34</v>
       </c>
       <c r="H57" t="n">
-        <v>46.54</v>
+        <v>53.84</v>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
@@ -3061,10 +3053,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.909</v>
+        <v>3.96</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.886</v>
+        <v>3.606</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3077,38 +3069,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.365</v>
+        <v>0.345</v>
       </c>
       <c r="E58" s="17" t="n">
-        <v>-0.0267</v>
+        <v>-0.0417</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2982600</v>
+        <v>3251700</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.53</v>
+        <v>0.42</v>
       </c>
       <c r="H58" t="n">
-        <v>61.46</v>
-      </c>
-      <c r="I58" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.41</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="K58" s="9" t="n"/>
+        <v>0.352</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>0.329</v>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
     </row>
@@ -3120,28 +3114,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>4.48</v>
-      </c>
-      <c r="E59" s="15" t="n">
-        <v>0.004500000000000001</v>
+        <v>0.885</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2910500</v>
+        <v>3120500</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.33</v>
+        <v>1.76</v>
       </c>
       <c r="H59" t="n">
-        <v>38.96</v>
+        <v>46.54</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3149,10 +3143,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>4.579</v>
+        <v>0.909</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>4.64</v>
+        <v>0.886</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3165,28 +3159,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.6</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2856800</v>
+        <v>3015500</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>1.01</v>
+        <v>0.67</v>
       </c>
       <c r="H60" t="n">
-        <v>79.26000000000001</v>
+        <v>65.84</v>
       </c>
       <c r="I60" s="16" t="inlineStr">
         <is>
@@ -3194,10 +3188,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.437</v>
+        <v>0.533</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.435</v>
+        <v>0.479</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3210,40 +3204,38 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>0.0211</v>
+        <v>0.365</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>-0.0267</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2837300</v>
+        <v>2996600</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="H61" t="n">
-        <v>58.87</v>
-      </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.46</v>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>3.705</v>
-      </c>
-      <c r="K61" s="9" t="n">
-        <v>3.15</v>
-      </c>
+        <v>0.333</v>
+      </c>
+      <c r="K61" s="9" t="n"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
     </row>
@@ -3255,28 +3247,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>3.07</v>
+        <v>4.48</v>
       </c>
       <c r="E62" s="15" t="n">
-        <v>0.0066</v>
+        <v>0.004500000000000001</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2794600</v>
+        <v>2913500</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.84</v>
+        <v>0.33</v>
       </c>
       <c r="H62" t="n">
-        <v>40.25</v>
+        <v>38.96</v>
       </c>
       <c r="I62" s="13" t="inlineStr">
         <is>
@@ -3284,10 +3276,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>3.132</v>
+        <v>4.579</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>3.291</v>
+        <v>4.64</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3300,39 +3292,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.6</v>
+        <v>0.44</v>
       </c>
       <c r="E63" s="17" t="n">
-        <v>-0.0244</v>
+        <v>-0.0112</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2723000</v>
+        <v>2912100</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.61</v>
+        <v>0.16</v>
       </c>
       <c r="H63" t="n">
-        <v>65.84</v>
-      </c>
-      <c r="I63" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.83</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.533</v>
+        <v>0.49</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.479</v>
+        <v>0.642</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3345,28 +3337,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E64" s="17" t="n">
-        <v>-0.011</v>
+        <v>0.505</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2633700</v>
+        <v>2872500</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.38</v>
+        <v>1.01</v>
       </c>
       <c r="H64" t="n">
-        <v>56</v>
+        <v>78.48</v>
       </c>
       <c r="I64" s="16" t="inlineStr">
         <is>
@@ -3374,10 +3366,10 @@
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.429</v>
+        <v>0.437</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.418</v>
+        <v>0.435</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3390,28 +3382,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E65" s="15" t="n">
-        <v>0.0192</v>
+        <v>0.235</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2627300</v>
+        <v>2827200</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="H65" t="n">
-        <v>60.21</v>
+        <v>53.18</v>
       </c>
       <c r="I65" s="16" t="inlineStr">
         <is>
@@ -3419,10 +3411,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>6.77</v>
+        <v>0.231</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>6.82</v>
+        <v>0.238</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3435,39 +3427,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E66" s="17" t="n">
-        <v>-0.014</v>
+        <v>3.07</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2618300</v>
+        <v>2797200</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.41</v>
+        <v>0.84</v>
       </c>
       <c r="H66" t="n">
-        <v>42.29</v>
-      </c>
-      <c r="I66" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.25</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.717</v>
+        <v>3.132</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.778</v>
+        <v>3.291</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3480,28 +3472,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0</v>
+        <v>6.94</v>
+      </c>
+      <c r="E67" s="15" t="n">
+        <v>0.0251</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2560000</v>
+        <v>2755900</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>1.8</v>
+        <v>0.63</v>
       </c>
       <c r="H67" t="n">
-        <v>84.81</v>
+        <v>62.38</v>
       </c>
       <c r="I67" s="16" t="inlineStr">
         <is>
@@ -3509,10 +3501,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.216</v>
+        <v>6.774</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.211</v>
+        <v>6.821</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3525,28 +3517,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.5649999999999999</v>
-      </c>
-      <c r="E68" s="15" t="n">
-        <v>0.0089</v>
+        <v>0.24</v>
+      </c>
+      <c r="E68" s="17" t="n">
+        <v>-0.0204</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2536400</v>
+        <v>2720500</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>1.48</v>
+        <v>1.91</v>
       </c>
       <c r="H68" t="n">
-        <v>51.98</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
@@ -3554,10 +3546,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.216</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.211</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3570,39 +3562,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.625</v>
+        <v>0.455</v>
       </c>
       <c r="E69" s="17" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0319</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2514700</v>
+        <v>2718800</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.72</v>
+        <v>0.28</v>
       </c>
       <c r="H69" t="n">
-        <v>63.66</v>
-      </c>
-      <c r="I69" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.69</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.619</v>
+        <v>0.504</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.609</v>
+        <v>0.467</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3615,39 +3607,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>-0.0179</v>
+        <v>0.455</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2463800</v>
+        <v>2642100</v>
       </c>
       <c r="G70" s="12" t="n">
         <v>0.38</v>
       </c>
       <c r="H70" t="n">
-        <v>39.44</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.28</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.902</v>
+        <v>0.429</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.855</v>
+        <v>0.418</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3660,39 +3652,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.595</v>
+        <v>0.705</v>
       </c>
       <c r="E71" s="17" t="n">
-        <v>-0.0325</v>
+        <v>-0.014</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2437500</v>
+        <v>2618300</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="H71" t="n">
-        <v>55.61</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.29</v>
+      </c>
+      <c r="I71" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.576</v>
+        <v>0.717</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.48</v>
+        <v>0.778</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3705,39 +3697,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E72" s="17" t="n">
-        <v>-0.0149</v>
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2418700</v>
+        <v>2536400</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.24</v>
+        <v>1.48</v>
       </c>
       <c r="H72" t="n">
-        <v>46.02</v>
-      </c>
-      <c r="I72" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.98</v>
+      </c>
+      <c r="I72" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.342</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.336</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3750,28 +3742,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0</v>
+        <v>0.625</v>
+      </c>
+      <c r="E73" s="17" t="n">
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2388800</v>
+        <v>2514700</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.44</v>
+        <v>0.72</v>
       </c>
       <c r="H73" t="n">
-        <v>68.73</v>
+        <v>63.66</v>
       </c>
       <c r="I73" s="16" t="inlineStr">
         <is>
@@ -3779,10 +3771,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.801</v>
+        <v>0.619</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.776</v>
+        <v>0.609</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3795,28 +3787,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.735</v>
+        <v>0.325</v>
       </c>
       <c r="E74" s="17" t="n">
-        <v>-0.0265</v>
+        <v>-0.0299</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2385600</v>
+        <v>2505400</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="H74" t="n">
-        <v>50.84</v>
+        <v>44.32</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -3824,10 +3816,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.741</v>
+        <v>0.342</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.336</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3840,39 +3832,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E75" s="15" t="n">
-        <v>0.0234</v>
+        <v>0.59</v>
+      </c>
+      <c r="E75" s="17" t="n">
+        <v>-0.0407</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2385400</v>
+        <v>2500600</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.41</v>
       </c>
       <c r="H75" t="n">
-        <v>37.03</v>
-      </c>
-      <c r="I75" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.91</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.9</v>
+        <v>0.575</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.964</v>
+        <v>0.48</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3885,28 +3877,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5337</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ECOSHOP</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E76" s="15" t="n">
-        <v>0.0071</v>
+        <v>0.82</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2366900</v>
+        <v>2500400</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.62</v>
+        <v>0.38</v>
       </c>
       <c r="H76" t="n">
-        <v>40.53</v>
+        <v>38.92</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -3914,10 +3906,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>1.441</v>
+        <v>0.901</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>1.46</v>
+        <v>0.855</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3930,28 +3922,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>2.4</v>
+        <v>0.545</v>
       </c>
       <c r="E77" s="17" t="n">
-        <v>-0.004099999999999999</v>
+        <v>-0.04389999999999999</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2365400</v>
+        <v>2485500</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.43</v>
+        <v>0.28</v>
       </c>
       <c r="H77" t="n">
-        <v>33.88</v>
+        <v>37.06</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3959,10 +3951,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>2.695</v>
+        <v>0.621</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>2.855</v>
+        <v>0.618</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3975,39 +3967,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E78" s="17" t="n">
-        <v>-0.0351</v>
+        <v>0.875</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>0.0234</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2355700</v>
+        <v>2472000</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.26</v>
+        <v>0.72</v>
       </c>
       <c r="H78" t="n">
-        <v>37.63</v>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.03</v>
+      </c>
+      <c r="I78" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.622</v>
+        <v>0.9</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.618</v>
+        <v>0.964</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4020,28 +4012,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="E79" s="17" t="n">
-        <v>-0.04</v>
+        <v>-0.0331</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2275700</v>
+        <v>2469600</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.27</v>
+        <v>0.42</v>
       </c>
       <c r="H79" t="n">
-        <v>37.3</v>
+        <v>50.05</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4049,10 +4041,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.661</v>
+        <v>0.741</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4065,33 +4057,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.755</v>
+        <v>2.39</v>
       </c>
       <c r="E80" s="17" t="n">
-        <v>-0.0258</v>
+        <v>-0.0083</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2268300</v>
+        <v>2427700</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.05</v>
+        <v>0.44</v>
+      </c>
+      <c r="H80" t="n">
+        <v>33.58</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J80" s="9" t="n"/>
-      <c r="K80" s="9" t="n"/>
+      <c r="J80" s="9" t="n">
+        <v>2.694</v>
+      </c>
+      <c r="K80" s="9" t="n">
+        <v>2.855</v>
+      </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
     </row>
@@ -4103,28 +4102,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>2.38</v>
+        <v>2.57</v>
       </c>
       <c r="E81" s="17" t="n">
-        <v>-0.0042</v>
+        <v>-0.0265</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2264500</v>
+        <v>2402100</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
       <c r="H81" t="n">
-        <v>33.86</v>
+        <v>47.38</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
@@ -4132,10 +4131,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>2.503</v>
+        <v>2.603</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>2.673</v>
+        <v>2.611</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4148,39 +4147,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="E82" s="17" t="n">
-        <v>-0.0189</v>
+        <v>0.825</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2231600</v>
+        <v>2388800</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.37</v>
+        <v>0.44</v>
       </c>
       <c r="H82" t="n">
-        <v>48.93</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.73</v>
+      </c>
+      <c r="I82" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>2.605</v>
+        <v>0.801</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>2.611</v>
+        <v>0.776</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4193,28 +4192,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.46</v>
+        <v>0.6</v>
       </c>
       <c r="E83" s="17" t="n">
-        <v>-0.0213</v>
+        <v>-0.04</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2210500</v>
+        <v>2381000</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="H83" t="n">
-        <v>42.44</v>
+        <v>37.3</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4222,10 +4221,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.504</v>
+        <v>0.661</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.467</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4238,28 +4237,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>ECOSHOP</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="E84" s="17" t="n">
-        <v>-0.0021</v>
+        <v>1.43</v>
+      </c>
+      <c r="E84" s="15" t="n">
+        <v>0.0142</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2198300</v>
+        <v>2371500</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.09</v>
+        <v>0.62</v>
       </c>
       <c r="H84" t="n">
-        <v>47.81</v>
+        <v>44.43</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -4267,10 +4266,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>4.877</v>
+        <v>1.442</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>4.75</v>
+        <v>1.46</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4283,39 +4282,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="E85" s="15" t="n">
-        <v>0.0089</v>
+        <v>2.38</v>
+      </c>
+      <c r="E85" s="17" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2086700</v>
+        <v>2309400</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.65</v>
+        <v>0.53</v>
       </c>
       <c r="H85" t="n">
-        <v>88.59</v>
-      </c>
-      <c r="I85" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.86</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>2.963</v>
+        <v>2.503</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>2.516</v>
+        <v>2.673</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4328,40 +4327,33 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="E86" s="15" t="n">
-        <v>0.022</v>
+        <v>0.75</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>-0.0323</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2075400</v>
+        <v>2292400</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="H86" t="n">
-        <v>52.66</v>
+        <v>0.05</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J86" s="9" t="n">
-        <v>5.492</v>
-      </c>
-      <c r="K86" s="9" t="n">
-        <v>5.382</v>
-      </c>
+      <c r="J86" s="9" t="n"/>
+      <c r="K86" s="9" t="n"/>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
     </row>
@@ -4373,39 +4365,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="E87" s="15" t="n">
-        <v>0.004</v>
+        <v>4.83</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2050400</v>
+        <v>2289300</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="H87" t="n">
-        <v>47.85</v>
-      </c>
-      <c r="I87" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.34</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>9.992000000000001</v>
+        <v>4.878</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>10.122</v>
+        <v>4.75</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4418,28 +4410,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>6.22</v>
+        <v>5.58</v>
       </c>
       <c r="E88" s="15" t="n">
-        <v>0.0032</v>
+        <v>0.0239</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2041200</v>
+        <v>2132000</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.31</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H88" t="n">
-        <v>38.83</v>
+        <v>52.88</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -4447,10 +4439,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>6.344</v>
+        <v>5.493</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>6.686</v>
+        <v>5.382</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4463,39 +4455,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E89" s="17" t="n">
-        <v>-0.012</v>
+        <v>9.99</v>
+      </c>
+      <c r="E89" s="15" t="n">
+        <v>0.004</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2031300</v>
+        <v>2111200</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.34</v>
+        <v>0.17</v>
       </c>
       <c r="H89" t="n">
-        <v>54.86</v>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.85</v>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.395</v>
+        <v>9.992000000000001</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.364</v>
+        <v>10.122</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4508,39 +4500,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="E90" s="17" t="n">
-        <v>-0.0219</v>
+        <v>3.39</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>0.0089</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1988000</v>
+        <v>2089200</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.44</v>
+        <v>0.65</v>
       </c>
       <c r="H90" t="n">
-        <v>48.29</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>88.59</v>
+      </c>
+      <c r="I90" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>7.296</v>
+        <v>2.963</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>6.925</v>
+        <v>2.516</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4553,39 +4545,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="E91" s="17" t="n">
-        <v>-0.0108</v>
+        <v>-0.012</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1940800</v>
+        <v>2071000</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="H91" t="n">
-        <v>34.23</v>
-      </c>
-      <c r="I91" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.86</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.487</v>
+        <v>0.395</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.545</v>
+        <v>0.364</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4598,28 +4590,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="E92" s="17" t="n">
-        <v>-0.0072</v>
+        <v>6.22</v>
+      </c>
+      <c r="E92" s="15" t="n">
+        <v>0.0032</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1934000</v>
+        <v>2043300</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.55</v>
+        <v>0.31</v>
       </c>
       <c r="H92" t="n">
-        <v>40.51</v>
+        <v>38.83</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -4627,10 +4619,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>2.861</v>
+        <v>6.344</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>2.992</v>
+        <v>6.686</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4643,39 +4635,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E93" s="15" t="n">
-        <v>0.0048</v>
+        <v>7.12</v>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>-0.0247</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1909600</v>
+        <v>2015700</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="H93" t="n">
-        <v>49.56</v>
-      </c>
-      <c r="I93" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.91</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>2.104</v>
+        <v>7.294</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>2.104</v>
+        <v>6.925</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4688,39 +4680,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>0.0507</v>
+        <v>2.76</v>
+      </c>
+      <c r="E94" s="17" t="n">
+        <v>-0.0072</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1842300</v>
+        <v>1943300</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>1.85</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H94" t="n">
-        <v>56.98</v>
-      </c>
-      <c r="I94" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.51</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>2.78</v>
+        <v>2.861</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>2.836</v>
+        <v>2.992</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4733,39 +4725,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E95" s="17" t="n">
-        <v>-0.0213</v>
+        <v>1.19</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1827200</v>
+        <v>1942500</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>1.55</v>
+        <v>0.41</v>
       </c>
       <c r="H95" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="I95" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.84</v>
+      </c>
+      <c r="I95" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.23</v>
+        <v>1.341</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.238</v>
+        <v>1.528</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4778,39 +4770,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>1.18</v>
+        <v>0.46</v>
       </c>
       <c r="E96" s="17" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0108</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1800400</v>
+        <v>1940900</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.38</v>
+        <v>0.26</v>
       </c>
       <c r="H96" t="n">
-        <v>21.27</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.23</v>
+      </c>
+      <c r="I96" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>1.34</v>
+        <v>0.487</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>1.528</v>
+        <v>0.545</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4823,39 +4815,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0353</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>WESTRVR</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.435</v>
+        <v>2.1</v>
       </c>
       <c r="E97" s="15" t="n">
-        <v>0.0116</v>
+        <v>0.0048</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1788300</v>
+        <v>1939500</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.46</v>
+        <v>0.15</v>
       </c>
       <c r="H97" t="n">
-        <v>56.19</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.56</v>
+      </c>
+      <c r="I97" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.419</v>
+        <v>2.104</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.389</v>
+        <v>2.104</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4868,28 +4860,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>TMK</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="E98" s="17" t="n">
-        <v>-0.0256</v>
+        <v>2.9</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>0.0507</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1767400</v>
+        <v>1901200</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.29</v>
+        <v>1.91</v>
       </c>
       <c r="H98" t="n">
-        <v>55.05</v>
+        <v>56.98</v>
       </c>
       <c r="I98" s="16" t="inlineStr">
         <is>
@@ -4897,10 +4889,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>6.259</v>
+        <v>2.78</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>5.968</v>
+        <v>2.836</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4913,28 +4905,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0348</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>CLITE</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>0</v>
+        <v>0.2</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <v>-0.0698</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1764100</v>
+        <v>1805600</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.2</v>
+        <v>1.52</v>
       </c>
       <c r="H99" t="n">
-        <v>24.34</v>
+        <v>33.52</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -4942,10 +4934,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.393</v>
+        <v>0.228</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.405</v>
+        <v>0.215</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4958,28 +4950,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.75</v>
+        <v>6.42</v>
       </c>
       <c r="E100" s="17" t="n">
-        <v>-0.0385</v>
+        <v>-0.0317</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1731600</v>
+        <v>1804400</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.61</v>
+        <v>0.3</v>
       </c>
       <c r="H100" t="n">
-        <v>52.82</v>
+        <v>54.35</v>
       </c>
       <c r="I100" s="16" t="inlineStr">
         <is>
@@ -4987,10 +4979,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.744</v>
+        <v>6.255</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.707</v>
+        <v>5.968</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -5003,39 +4995,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0348</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CLITE</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.2</v>
+        <v>0.74</v>
       </c>
       <c r="E101" s="17" t="n">
-        <v>-0.0698</v>
+        <v>-0.0513</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1729800</v>
+        <v>1792000</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>1.46</v>
+        <v>0.63</v>
       </c>
       <c r="H101" t="n">
-        <v>33.52</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.18</v>
+      </c>
+      <c r="I101" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.228</v>
+        <v>0.743</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.215</v>
+        <v>0.707</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5048,39 +5040,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>0</v>
+        <v>0.435</v>
+      </c>
+      <c r="E102" s="15" t="n">
+        <v>0.0116</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1723000</v>
+        <v>1788900</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.25</v>
+        <v>0.46</v>
       </c>
       <c r="H102" t="n">
-        <v>63.98</v>
-      </c>
-      <c r="I102" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.19</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>1.222</v>
+        <v>0.419</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>1.201</v>
+        <v>0.389</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5093,28 +5085,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E103" s="17" t="n">
-        <v>-0.0112</v>
+        <v>0.38</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1715200</v>
+        <v>1764100</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H103" t="n">
-        <v>26.83</v>
+        <v>24.34</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -5122,10 +5114,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.49</v>
+        <v>0.393</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.642</v>
+        <v>0.405</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5138,28 +5130,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E104" s="15" t="n">
-        <v>0.0446</v>
+        <v>1.3</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1711100</v>
+        <v>1727300</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.77</v>
+        <v>0.25</v>
       </c>
       <c r="H104" t="n">
-        <v>28.08</v>
+        <v>63.98</v>
       </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
@@ -5167,10 +5159,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.901</v>
+        <v>1.222</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>1.056</v>
+        <v>1.201</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5183,39 +5175,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="E105" s="17" t="n">
-        <v>-0.0106</v>
+        <v>0.82</v>
+      </c>
+      <c r="E105" s="15" t="n">
+        <v>0.0446</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1614700</v>
+        <v>1724100</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="H105" t="n">
-        <v>47.39</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>28.08</v>
+      </c>
+      <c r="I105" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>3.818</v>
+        <v>0.901</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>3.724</v>
+        <v>1.056</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5228,28 +5220,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>1.16</v>
+        <v>0.25</v>
       </c>
       <c r="E106" s="17" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0385</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1608100</v>
+        <v>1707800</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="H106" t="n">
-        <v>62.28</v>
+        <v>40.31</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -5257,10 +5249,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>1.08</v>
+        <v>0.268</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.944</v>
+        <v>0.288</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5273,28 +5265,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.375</v>
+        <v>3.73</v>
       </c>
       <c r="E107" s="17" t="n">
-        <v>-0.026</v>
+        <v>-0.0132</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1582800</v>
+        <v>1661600</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.65</v>
+        <v>0.51</v>
       </c>
       <c r="H107" t="n">
-        <v>44.57</v>
+        <v>46.99</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -5302,10 +5294,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>0.386</v>
+        <v>3.817</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.39</v>
+        <v>3.724</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5318,28 +5310,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>IHH</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>7.98</v>
-      </c>
-      <c r="E108" s="15" t="n">
-        <v>0.005</v>
+        <v>5.1</v>
+      </c>
+      <c r="E108" s="17" t="n">
+        <v>-0.0173</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1574100</v>
+        <v>1615300</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.45</v>
+        <v>0.39</v>
       </c>
       <c r="H108" t="n">
-        <v>54.17</v>
+        <v>52.43</v>
       </c>
       <c r="I108" s="16" t="inlineStr">
         <is>
@@ -5347,10 +5339,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>7.919</v>
+        <v>5.065</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>7.949</v>
+        <v>5.046</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5363,28 +5355,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>5.09</v>
-      </c>
-      <c r="E109" s="17" t="n">
-        <v>-0.0193</v>
+        <v>2.37</v>
+      </c>
+      <c r="E109" s="15" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1571400</v>
+        <v>1614700</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
       <c r="H109" t="n">
-        <v>51.89</v>
+        <v>61.52</v>
       </c>
       <c r="I109" s="16" t="inlineStr">
         <is>
@@ -5392,10 +5384,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>5.064</v>
+        <v>2.258</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>5.045</v>
+        <v>2.192</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5408,28 +5400,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>TIMECOM</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E110" s="10" t="n">
-        <v>0</v>
+        <v>1.15</v>
+      </c>
+      <c r="E110" s="17" t="n">
+        <v>-0.0171</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1540300</v>
+        <v>1608500</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.73</v>
+        <v>0.34</v>
       </c>
       <c r="H110" t="n">
-        <v>32.64</v>
+        <v>61.02</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -5437,10 +5429,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>5.508</v>
+        <v>1.079</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>5.766</v>
+        <v>0.944</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5453,28 +5445,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3557</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ECOFIRS</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.31</v>
+        <v>0.375</v>
       </c>
       <c r="E111" s="17" t="n">
-        <v>-0.0313</v>
+        <v>-0.026</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1486500</v>
+        <v>1582900</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.97</v>
+        <v>0.65</v>
       </c>
       <c r="H111" t="n">
-        <v>39.44</v>
+        <v>44.57</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -5482,10 +5474,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.322</v>
+        <v>0.386</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.333</v>
+        <v>0.39</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5498,39 +5490,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>IHH</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E112" s="17" t="n">
-        <v>-0.0385</v>
+        <v>7.99</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>0.0063</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1477700</v>
+        <v>1582600</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.24</v>
+        <v>0.45</v>
       </c>
       <c r="H112" t="n">
-        <v>40.31</v>
-      </c>
-      <c r="I112" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.78</v>
+      </c>
+      <c r="I112" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.268</v>
+        <v>7.92</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.288</v>
+        <v>7.949</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5543,39 +5535,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>TIMECOM</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="E113" s="15" t="n">
-        <v>0.0129</v>
+        <v>5.29</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>-0.0019</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1465900</v>
+        <v>1569200</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.44</v>
+        <v>0.75</v>
       </c>
       <c r="H113" t="n">
-        <v>60.88</v>
-      </c>
-      <c r="I113" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.25</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>2.257</v>
+        <v>5.507</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>2.191</v>
+        <v>5.766</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5588,28 +5580,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>DXN</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E114" s="10" t="n">
-        <v>0</v>
+        <v>0.465</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>0.0109</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1455700</v>
+        <v>1542400</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.18</v>
+        <v>0.85</v>
       </c>
       <c r="H114" t="n">
-        <v>48.56</v>
+        <v>54.86</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -5617,10 +5609,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.769</v>
+        <v>0.462</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.771</v>
+        <v>0.462</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5633,39 +5625,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>ECOFIRS</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.65</v>
+        <v>0.31</v>
       </c>
       <c r="E115" s="17" t="n">
-        <v>-0.0152</v>
+        <v>-0.0313</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1451300</v>
+        <v>1486500</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>1.13</v>
+        <v>0.97</v>
       </c>
       <c r="H115" t="n">
-        <v>70.83</v>
-      </c>
-      <c r="I115" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.44</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.599</v>
+        <v>0.322</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.538</v>
+        <v>0.333</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5678,39 +5670,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AZAMJAYA</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.96</v>
+        <v>0.64</v>
       </c>
       <c r="E116" s="17" t="n">
-        <v>-0.0254</v>
+        <v>-0.0303</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1448300</v>
+        <v>1476200</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>6.12</v>
+        <v>1.15</v>
       </c>
       <c r="H116" t="n">
-        <v>47.51</v>
-      </c>
-      <c r="I116" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.93000000000001</v>
+      </c>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.971</v>
+        <v>0.598</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.976</v>
+        <v>0.538</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5723,28 +5715,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5318</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>DXN</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>0</v>
+        <v>1.52</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>-0.044</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1430500</v>
+        <v>1465700</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.79</v>
+        <v>0.24</v>
       </c>
       <c r="H117" t="n">
-        <v>47.19</v>
+        <v>30.97</v>
       </c>
       <c r="I117" s="13" t="inlineStr">
         <is>
@@ -5752,10 +5744,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.461</v>
+        <v>1.677</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.462</v>
+        <v>1.751</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5777,19 +5769,19 @@
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E118" s="10" t="n">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1427100</v>
+        <v>1459100</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="H118" t="n">
-        <v>56.98</v>
+        <v>54.94</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5797,7 +5789,7 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>1.272</v>
+        <v>1.27</v>
       </c>
       <c r="K118" s="9" t="n">
         <v>1.182</v>
@@ -5813,28 +5805,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>1.25</v>
+        <v>0.765</v>
       </c>
       <c r="E119" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1420100</v>
+        <v>1455700</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H119" t="n">
-        <v>43.04</v>
+        <v>48.56</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5842,10 +5834,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>1.283</v>
+        <v>0.769</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.316</v>
+        <v>0.771</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5858,39 +5850,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.97</v>
+        <v>1.24</v>
       </c>
       <c r="E120" s="17" t="n">
-        <v>-0.0051</v>
+        <v>-0.008</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1381100</v>
+        <v>1452700</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="H120" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="I120" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.72</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.9379999999999999</v>
+        <v>1.282</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.886</v>
+        <v>1.316</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5903,28 +5895,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>AZAMJAYA</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>2.77</v>
+        <v>0.96</v>
       </c>
       <c r="E121" s="17" t="n">
-        <v>-0.0107</v>
+        <v>-0.0254</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1380400</v>
+        <v>1448300</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.15</v>
+        <v>6.12</v>
       </c>
       <c r="H121" t="n">
-        <v>50.08</v>
+        <v>47.51</v>
       </c>
       <c r="I121" s="13" t="inlineStr">
         <is>
@@ -5932,10 +5924,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>2.792</v>
+        <v>0.971</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>2.683</v>
+        <v>0.976</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5948,28 +5940,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BJCORP</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E122" s="10" t="n">
-        <v>0</v>
+        <v>2.78</v>
+      </c>
+      <c r="E122" s="17" t="n">
+        <v>-0.0071</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1368100</v>
+        <v>1437600</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>1.34</v>
+        <v>0.16</v>
       </c>
       <c r="H122" t="n">
-        <v>51.15</v>
+        <v>50.68</v>
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
@@ -5977,10 +5969,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.25</v>
+        <v>2.793</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.25</v>
+        <v>2.683</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5993,39 +5985,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>0</v>
+        <v>0.405</v>
+      </c>
+      <c r="E123" s="17" t="n">
+        <v>-0.0241</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1361300</v>
+        <v>1398400</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="H123" t="n">
-        <v>50.39</v>
-      </c>
-      <c r="I123" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.07</v>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>1.627</v>
+        <v>0.43</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>1.682</v>
+        <v>0.438</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6038,39 +6030,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>1.52</v>
+        <v>0.97</v>
       </c>
       <c r="E124" s="17" t="n">
-        <v>-0.044</v>
+        <v>-0.0051</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1357200</v>
+        <v>1381100</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.22</v>
+        <v>0.24</v>
       </c>
       <c r="H124" t="n">
-        <v>30.97</v>
-      </c>
-      <c r="I124" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.90000000000001</v>
+      </c>
+      <c r="I124" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>1.677</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>1.751</v>
+        <v>0.886</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6083,28 +6075,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>BJCORP</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.41</v>
+        <v>0.245</v>
       </c>
       <c r="E125" s="17" t="n">
-        <v>-0.012</v>
+        <v>-0.02</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1348900</v>
+        <v>1369300</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.15</v>
+        <v>1.34</v>
       </c>
       <c r="H125" t="n">
-        <v>43.27</v>
+        <v>11.11</v>
       </c>
       <c r="I125" s="13" t="inlineStr">
         <is>
@@ -6112,10 +6104,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.43</v>
+        <v>0.249</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.438</v>
+        <v>0.25</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6128,33 +6120,40 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0478</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>NWE Resources Group Berhad</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.2</v>
+        <v>1.64</v>
       </c>
       <c r="E126" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1306700</v>
+        <v>1367700</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.01</v>
+        <v>0.17</v>
+      </c>
+      <c r="H126" t="n">
+        <v>50.39</v>
       </c>
       <c r="I126" s="16" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J126" s="9" t="n"/>
-      <c r="K126" s="9" t="n"/>
+      <c r="J126" s="9" t="n">
+        <v>1.627</v>
+      </c>
+      <c r="K126" s="9" t="n">
+        <v>1.682</v>
+      </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
     </row>
@@ -6166,28 +6165,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E127" s="10" t="n">
-        <v>0</v>
+        <v>4.2</v>
+      </c>
+      <c r="E127" s="17" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1291200</v>
+        <v>1346000</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="H127" t="n">
-        <v>51.47</v>
+        <v>34.42</v>
       </c>
       <c r="I127" s="13" t="inlineStr">
         <is>
@@ -6195,10 +6194,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.865</v>
+        <v>4.357</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.86</v>
+        <v>4.661</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6211,28 +6210,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>4.2</v>
+        <v>1.08</v>
       </c>
       <c r="E128" s="17" t="n">
-        <v>-0.004699999999999999</v>
+        <v>-0.0182</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1275200</v>
+        <v>1337100</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.31</v>
+        <v>0.15</v>
       </c>
       <c r="H128" t="n">
-        <v>34.42</v>
+        <v>50.4</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6240,10 +6239,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>4.357</v>
+        <v>1.082</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>4.661</v>
+        <v>1.052</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6256,28 +6255,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E129" s="17" t="n">
-        <v>-0.0181</v>
+        <v>0.865</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1259600</v>
+        <v>1291200</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="H129" t="n">
-        <v>49.55</v>
+        <v>51.47</v>
       </c>
       <c r="I129" s="13" t="inlineStr">
         <is>
@@ -6285,10 +6284,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.825</v>
+        <v>0.865</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.792</v>
+        <v>0.86</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6301,28 +6300,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>1.08</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E130" s="17" t="n">
-        <v>-0.0182</v>
+        <v>-0.0181</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1245600</v>
+        <v>1278700</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.14</v>
+        <v>0.34</v>
       </c>
       <c r="H130" t="n">
-        <v>50.4</v>
+        <v>49.55</v>
       </c>
       <c r="I130" s="13" t="inlineStr">
         <is>
@@ -6330,10 +6329,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>1.082</v>
+        <v>0.825</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>1.052</v>
+        <v>0.792</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6346,28 +6345,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="E131" s="17" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.027</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1224100</v>
+        <v>1278100</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.18</v>
+        <v>0.37</v>
       </c>
       <c r="H131" t="n">
-        <v>50.55</v>
+        <v>42.41</v>
       </c>
       <c r="I131" s="13" t="inlineStr">
         <is>
@@ -6375,10 +6374,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>1.172</v>
+        <v>1.138</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>1.146</v>
+        <v>1.108</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6391,28 +6390,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>1.01</v>
+        <v>0.295</v>
       </c>
       <c r="E132" s="15" t="n">
-        <v>0.01</v>
+        <v>0.0926</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1197700</v>
+        <v>1257500</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.29</v>
+        <v>1.2</v>
       </c>
       <c r="H132" t="n">
-        <v>48.67</v>
+        <v>47.27</v>
       </c>
       <c r="I132" s="13" t="inlineStr">
         <is>
@@ -6420,10 +6419,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>1.032</v>
+        <v>0.294</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.962</v>
+        <v>0.33</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6436,28 +6435,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E133" s="17" t="n">
-        <v>-0.0167</v>
+        <v>1.01</v>
+      </c>
+      <c r="E133" s="15" t="n">
+        <v>0.01</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1167500</v>
+        <v>1247300</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.73</v>
+        <v>0.3</v>
       </c>
       <c r="H133" t="n">
-        <v>28</v>
+        <v>48.67</v>
       </c>
       <c r="I133" s="13" t="inlineStr">
         <is>
@@ -6465,10 +6464,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.9320000000000001</v>
+        <v>1.032</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.992</v>
+        <v>0.962</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6481,28 +6480,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MAXIS</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>3.53</v>
+        <v>1.16</v>
       </c>
       <c r="E134" s="17" t="n">
-        <v>-0.0028</v>
+        <v>-0.0169</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1154100</v>
+        <v>1232100</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.85</v>
+        <v>0.18</v>
       </c>
       <c r="H134" t="n">
-        <v>49.48</v>
+        <v>49.07</v>
       </c>
       <c r="I134" s="13" t="inlineStr">
         <is>
@@ -6510,10 +6509,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>3.528</v>
+        <v>1.171</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>3.58</v>
+        <v>1.145</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6526,39 +6525,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>0</v>
+        <v>1.79</v>
+      </c>
+      <c r="E135" s="15" t="n">
+        <v>0.0287</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1131900</v>
+        <v>1224100</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.52</v>
+        <v>0.39</v>
       </c>
       <c r="H135" t="n">
-        <v>52.17</v>
-      </c>
-      <c r="I135" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>43.01</v>
+      </c>
+      <c r="I135" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.263</v>
+        <v>1.81</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.242</v>
+        <v>1.938</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6571,28 +6570,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>1.09</v>
+        <v>0.885</v>
       </c>
       <c r="E136" s="17" t="n">
-        <v>-0.018</v>
+        <v>-0.0167</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1127900</v>
+        <v>1197000</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="H136" t="n">
-        <v>43.6</v>
+        <v>28</v>
       </c>
       <c r="I136" s="13" t="inlineStr">
         <is>
@@ -6600,10 +6599,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>1.139</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>1.108</v>
+        <v>0.992</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6616,39 +6615,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>MAXIS</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.65</v>
+        <v>3.52</v>
       </c>
       <c r="E137" s="17" t="n">
-        <v>-0.0076</v>
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1100800</v>
+        <v>1159900</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.51</v>
+        <v>0.85</v>
       </c>
       <c r="H137" t="n">
-        <v>58.18</v>
-      </c>
-      <c r="I137" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.35</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>0.639</v>
+        <v>3.527</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>0.626</v>
+        <v>3.58</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6661,28 +6660,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E138" s="17" t="n">
-        <v>-0.0098</v>
+        <v>0.265</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1100400</v>
+        <v>1143400</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.39</v>
+        <v>0.53</v>
       </c>
       <c r="H138" t="n">
-        <v>29.82</v>
+        <v>52.17</v>
       </c>
       <c r="I138" s="13" t="inlineStr">
         <is>
@@ -6690,10 +6689,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.534</v>
+        <v>0.263</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.242</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6706,28 +6705,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>1.78</v>
+        <v>4.43</v>
       </c>
       <c r="E139" s="15" t="n">
-        <v>0.023</v>
+        <v>0.0068</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>1089300</v>
+        <v>1126800</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
       <c r="H139" t="n">
-        <v>41.42</v>
+        <v>51.71</v>
       </c>
       <c r="I139" s="16" t="inlineStr">
         <is>
@@ -6735,10 +6734,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>1.809</v>
+        <v>4.377</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>1.938</v>
+        <v>4.432</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6751,36 +6750,40 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0475</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>GBBOND</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E140" s="10" t="n">
-        <v>0</v>
+        <v>0.605</v>
+      </c>
+      <c r="E140" s="17" t="n">
+        <v>-0.0472</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1085200</v>
+        <v>1116200</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H140" t="n">
-        <v>86.33</v>
+        <v>30.79</v>
       </c>
       <c r="I140" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J140" s="9" t="n"/>
-      <c r="K140" s="9" t="n"/>
+      <c r="J140" s="9" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>0.74</v>
+      </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
     </row>
@@ -6792,39 +6795,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="E141" s="15" t="n">
-        <v>0.0023</v>
+        <v>0.51</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>1077100</v>
+        <v>1108500</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.21</v>
+        <v>0.39</v>
       </c>
       <c r="H141" t="n">
-        <v>50.93</v>
-      </c>
-      <c r="I141" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.45</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>4.375</v>
+        <v>0.535</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>4.432</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6837,39 +6840,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>10.56</v>
-      </c>
-      <c r="E142" s="17" t="n">
-        <v>-0.0112</v>
+        <v>0.655</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1073200</v>
+        <v>1105200</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.3</v>
+        <v>0.51</v>
       </c>
       <c r="H142" t="n">
-        <v>54.94</v>
-      </c>
-      <c r="I142" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.54</v>
+      </c>
+      <c r="I142" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>10.442</v>
+        <v>0.64</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>9.83</v>
+        <v>0.627</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6891,19 +6894,19 @@
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E143" s="15" t="n">
-        <v>0.0149</v>
+        <v>0.335</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1055400</v>
+        <v>1097400</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="H143" t="n">
-        <v>53.01</v>
+        <v>47.98</v>
       </c>
       <c r="I143" s="16" t="inlineStr">
         <is>
@@ -6927,39 +6930,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>TOYOVEN</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="E144" s="10" t="n">
-        <v>0</v>
+        <v>10.6</v>
+      </c>
+      <c r="E144" s="17" t="n">
+        <v>-0.0075</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1054700</v>
+        <v>1092800</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.96</v>
+        <v>0.31</v>
       </c>
       <c r="H144" t="n">
-        <v>62.09</v>
-      </c>
-      <c r="I144" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.74</v>
+      </c>
+      <c r="I144" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>0.226</v>
+        <v>10.446</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>0.212</v>
+        <v>9.83</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6972,40 +6975,36 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0475</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>GBBOND</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E145" s="17" t="n">
-        <v>-0.0417</v>
+        <v>0.205</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>1041200</v>
+        <v>1092200</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.27</v>
+        <v>0.12</v>
       </c>
       <c r="H145" t="n">
-        <v>46.61</v>
+        <v>86.33</v>
       </c>
       <c r="I145" s="13" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J145" s="9" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="K145" s="9" t="n">
-        <v>0.586</v>
-      </c>
+      <c r="J145" s="9" t="n"/>
+      <c r="K145" s="9" t="n"/>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
     </row>
@@ -7017,39 +7016,39 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>TOYOVEN</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E146" s="17" t="n">
-        <v>-0.0394</v>
+        <v>0.24</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>1039000</v>
+        <v>1068700</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.33</v>
+        <v>0.97</v>
       </c>
       <c r="H146" t="n">
-        <v>31.33</v>
-      </c>
-      <c r="I146" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.09</v>
+      </c>
+      <c r="I146" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>0.697</v>
+        <v>0.226</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>0.74</v>
+        <v>0.212</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7062,28 +7061,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>MULPHA</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>2.6</v>
+        <v>0.575</v>
       </c>
       <c r="E147" s="17" t="n">
-        <v>-0.0114</v>
+        <v>-0.0417</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>1035200</v>
+        <v>1043200</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>9.27</v>
+        <v>0.27</v>
       </c>
       <c r="H147" t="n">
-        <v>39.25</v>
+        <v>46.61</v>
       </c>
       <c r="I147" s="13" t="inlineStr">
         <is>
@@ -7091,10 +7090,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>2.691</v>
+        <v>0.593</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>2.793</v>
+        <v>0.586</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7107,12 +7106,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
@@ -7122,13 +7121,13 @@
         <v>-0.0179</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>1034600</v>
+        <v>1037500</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>1.12</v>
+        <v>0.15</v>
       </c>
       <c r="H148" t="n">
-        <v>50.42</v>
+        <v>36.17</v>
       </c>
       <c r="I148" s="13" t="inlineStr">
         <is>
@@ -7136,10 +7135,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>0.277</v>
+        <v>0.304</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>0.268</v>
+        <v>0.329</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7152,39 +7151,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>MULPHA</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="E149" s="15" t="n">
-        <v>0.0147</v>
+        <v>2.6</v>
+      </c>
+      <c r="E149" s="17" t="n">
+        <v>-0.0114</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>1019400</v>
+        <v>1035200</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.5</v>
+        <v>9.27</v>
       </c>
       <c r="H149" t="n">
-        <v>56.09</v>
-      </c>
-      <c r="I149" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.25</v>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>1.364</v>
+        <v>2.691</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>1.343</v>
+        <v>2.793</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7197,12 +7196,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
@@ -7212,13 +7211,13 @@
         <v>-0.0179</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>1004500</v>
+        <v>1034600</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.15</v>
+        <v>1.12</v>
       </c>
       <c r="H150" t="n">
-        <v>36.17</v>
+        <v>50.42</v>
       </c>
       <c r="I150" s="13" t="inlineStr">
         <is>
@@ -7226,10 +7225,10 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>0.304</v>
+        <v>0.277</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>0.329</v>
+        <v>0.268</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7242,28 +7241,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E151" s="10" t="n">
-        <v>0</v>
+        <v>1.38</v>
+      </c>
+      <c r="E151" s="15" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>982500</v>
+        <v>1019400</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H151" t="n">
-        <v>54.14</v>
+        <v>56.09</v>
       </c>
       <c r="I151" s="16" t="inlineStr">
         <is>
@@ -7271,10 +7270,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>1.264</v>
+        <v>1.364</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>1.273</v>
+        <v>1.343</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7287,28 +7286,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>RALCO</t>
+          <t>CLMT</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>1.02</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E152" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>883600</v>
+        <v>1010200</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>1.41</v>
+        <v>0.62</v>
       </c>
       <c r="H152" t="n">
-        <v>57.63</v>
+        <v>47.59</v>
       </c>
       <c r="I152" s="16" t="inlineStr">
         <is>
@@ -7316,10 +7315,10 @@
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>1.009</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>0.987</v>
+        <v>0.576</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7332,28 +7331,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5180</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>CLMT</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.28</v>
       </c>
       <c r="E153" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>863500</v>
+        <v>997800</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.53</v>
+        <v>0.25</v>
       </c>
       <c r="H153" t="n">
-        <v>47.59</v>
+        <v>54.14</v>
       </c>
       <c r="I153" s="16" t="inlineStr">
         <is>
@@ -7361,10 +7360,10 @@
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.264</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>0.576</v>
+        <v>1.273</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7377,39 +7376,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>2.12</v>
+        <v>0.53</v>
       </c>
       <c r="E154" s="17" t="n">
-        <v>-0.004699999999999999</v>
+        <v>-0.0275</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>851300</v>
+        <v>924000</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.41</v>
+        <v>0.17</v>
       </c>
       <c r="H154" t="n">
-        <v>52.89</v>
-      </c>
-      <c r="I154" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.28</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>2.113</v>
+        <v>0.553</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>2.073</v>
+        <v>0.522</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7422,28 +7421,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>RALCO</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>13.08</v>
-      </c>
-      <c r="E155" s="15" t="n">
-        <v>0.0077</v>
+        <v>1.02</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>845700</v>
+        <v>883600</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.13</v>
+        <v>1.41</v>
       </c>
       <c r="H155" t="n">
-        <v>50.35</v>
+        <v>57.63</v>
       </c>
       <c r="I155" s="16" t="inlineStr">
         <is>
@@ -7451,10 +7450,10 @@
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>13.022</v>
+        <v>1.009</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>13.348</v>
+        <v>0.987</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7467,39 +7466,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E156" s="17" t="n">
-        <v>-0.0367</v>
+        <v>13.08</v>
+      </c>
+      <c r="E156" s="15" t="n">
+        <v>0.0077</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>840100</v>
+        <v>873300</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
       <c r="H156" t="n">
-        <v>45.31</v>
-      </c>
-      <c r="I156" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.35</v>
+      </c>
+      <c r="I156" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>0.552</v>
+        <v>13.022</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>0.522</v>
+        <v>13.348</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7512,39 +7511,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="E157" s="10" t="n">
-        <v>0</v>
+        <v>2.12</v>
+      </c>
+      <c r="E157" s="17" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>836400</v>
+        <v>851300</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.14</v>
+        <v>0.41</v>
       </c>
       <c r="H157" t="n">
-        <v>50.96</v>
-      </c>
-      <c r="I157" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.89</v>
+      </c>
+      <c r="I157" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>1.103</v>
+        <v>2.113</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>0.911</v>
+        <v>2.073</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7557,28 +7556,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E158" s="17" t="n">
-        <v>-0.0438</v>
+        <v>1.08</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>822600</v>
+        <v>836400</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="H158" t="n">
-        <v>40.12</v>
+        <v>50.96</v>
       </c>
       <c r="I158" s="13" t="inlineStr">
         <is>
@@ -7586,10 +7585,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>0.734</v>
+        <v>1.103</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.911</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7602,28 +7601,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>2.71</v>
+        <v>0.66</v>
       </c>
       <c r="E159" s="17" t="n">
-        <v>-0.0073</v>
+        <v>-0.0365</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>802900</v>
+        <v>824700</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="H159" t="n">
-        <v>47.17</v>
+        <v>40.64</v>
       </c>
       <c r="I159" s="13" t="inlineStr">
         <is>
@@ -7631,10 +7630,10 @@
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>2.747</v>
+        <v>0.734</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>2.746</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7647,28 +7646,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5819</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>HLBANK</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>21.48</v>
-      </c>
-      <c r="E160" s="17" t="n">
-        <v>-0.0019</v>
+        <v>0.92</v>
+      </c>
+      <c r="E160" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>797600</v>
+        <v>823800</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.8</v>
+        <v>0.19</v>
       </c>
       <c r="H160" t="n">
-        <v>45.1</v>
+        <v>26.8</v>
       </c>
       <c r="I160" s="13" t="inlineStr">
         <is>
@@ -7676,10 +7675,10 @@
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>21.625</v>
+        <v>0.957</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>22.094</v>
+        <v>1.04</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7692,28 +7691,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E161" s="10" t="n">
-        <v>0</v>
+        <v>2.98</v>
+      </c>
+      <c r="E161" s="15" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>785900</v>
+        <v>804500</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="H161" t="n">
-        <v>33.03</v>
+        <v>50.12</v>
       </c>
       <c r="I161" s="13" t="inlineStr">
         <is>
@@ -7721,10 +7720,10 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>0.879</v>
+        <v>3.007</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>0.9409999999999999</v>
+        <v>2.861</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7737,28 +7736,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="E162" s="15" t="n">
-        <v>0.0068</v>
+        <v>2.71</v>
+      </c>
+      <c r="E162" s="17" t="n">
+        <v>-0.0073</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>779500</v>
+        <v>804100</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.29</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H162" t="n">
-        <v>50.12</v>
+        <v>47.17</v>
       </c>
       <c r="I162" s="13" t="inlineStr">
         <is>
@@ -7766,10 +7765,10 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>3.007</v>
+        <v>2.747</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>2.861</v>
+        <v>2.746</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7782,39 +7781,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t>5819</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>HEKTAR</t>
+          <t>HLBANK</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E163" s="10" t="n">
-        <v>0</v>
+        <v>21.5</v>
+      </c>
+      <c r="E163" s="17" t="n">
+        <v>-0.0009</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>766400</v>
+        <v>799000</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>1.01</v>
+        <v>0.8</v>
       </c>
       <c r="H163" t="n">
-        <v>63.19</v>
-      </c>
-      <c r="I163" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.45</v>
+      </c>
+      <c r="I163" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>0.508</v>
+        <v>21.627</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>0.495</v>
+        <v>22.094</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7827,28 +7826,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="E164" s="15" t="n">
-        <v>0.0095</v>
+        <v>0.835</v>
+      </c>
+      <c r="E164" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>763900</v>
+        <v>795500</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.59</v>
+        <v>0.25</v>
       </c>
       <c r="H164" t="n">
-        <v>37.74</v>
+        <v>33.03</v>
       </c>
       <c r="I164" s="13" t="inlineStr">
         <is>
@@ -7856,10 +7855,10 @@
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>5.426</v>
+        <v>0.879</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>5.757</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7872,39 +7871,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0223</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>SAMAIDEN</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E165" s="17" t="n">
-        <v>-0.0149</v>
+        <v>2.87</v>
+      </c>
+      <c r="E165" s="15" t="n">
+        <v>0.0035</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>748100</v>
+        <v>793200</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.27</v>
+        <v>0.18</v>
       </c>
       <c r="H165" t="n">
-        <v>56.03</v>
-      </c>
-      <c r="I165" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.8</v>
+      </c>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>0.65</v>
+        <v>2.806</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>0.569</v>
+        <v>2.293</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7917,39 +7916,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="E166" s="10" t="n">
-        <v>0</v>
+        <v>0.66</v>
+      </c>
+      <c r="E166" s="17" t="n">
+        <v>-0.0149</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>737000</v>
+        <v>768100</v>
       </c>
       <c r="G166" s="12" t="n">
         <v>0.28</v>
       </c>
       <c r="H166" t="n">
-        <v>44.64</v>
-      </c>
-      <c r="I166" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.03</v>
+      </c>
+      <c r="I166" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>2.071</v>
+        <v>0.65</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>1.993</v>
+        <v>0.569</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7962,28 +7961,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>HEKTAR</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>7.5</v>
+        <v>0.515</v>
       </c>
       <c r="E167" s="17" t="n">
-        <v>-0.004</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>733500</v>
+        <v>767400</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.28</v>
+        <v>1.01</v>
       </c>
       <c r="H167" t="n">
-        <v>46.1</v>
+        <v>58.53</v>
       </c>
       <c r="I167" s="16" t="inlineStr">
         <is>
@@ -7991,10 +7990,10 @@
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>7.558</v>
+        <v>0.507</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>7.732</v>
+        <v>0.494</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8007,28 +8006,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="E168" s="10" t="n">
-        <v>0</v>
+        <v>5.27</v>
+      </c>
+      <c r="E168" s="15" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>726600</v>
+        <v>764800</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.16</v>
+        <v>0.59</v>
       </c>
       <c r="H168" t="n">
-        <v>57.41</v>
+        <v>36.29</v>
       </c>
       <c r="I168" s="13" t="inlineStr">
         <is>
@@ -8036,10 +8035,10 @@
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>2.805</v>
+        <v>5.424</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>2.293</v>
+        <v>5.757</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8052,28 +8051,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>PJBUMI</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="E169" s="10" t="n">
-        <v>0</v>
+        <v>1.25</v>
+      </c>
+      <c r="E169" s="15" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>700800</v>
+        <v>753800</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>1.21</v>
+        <v>0.37</v>
       </c>
       <c r="H169" t="n">
-        <v>61.36</v>
+        <v>44.13</v>
       </c>
       <c r="I169" s="13" t="inlineStr">
         <is>
@@ -8081,10 +8080,10 @@
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>4.168</v>
+        <v>1.301</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>4.024</v>
+        <v>1.296</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8097,28 +8096,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>KOBAY</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>2.79</v>
+        <v>2.08</v>
       </c>
       <c r="E170" s="17" t="n">
-        <v>-0.0071</v>
+        <v>-0.0189</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>693100</v>
+        <v>749200</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>0.2</v>
+        <v>0.59</v>
       </c>
       <c r="H170" t="n">
-        <v>57.77</v>
+        <v>45.41</v>
       </c>
       <c r="I170" s="16" t="inlineStr">
         <is>
@@ -8126,10 +8125,10 @@
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>2.711</v>
+        <v>2.114</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>2.322</v>
+        <v>2.255</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8142,39 +8141,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>2.77</v>
+        <v>1.96</v>
       </c>
       <c r="E171" s="17" t="n">
-        <v>-0.0107</v>
+        <v>-0.0051</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>684400</v>
+        <v>745800</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.47</v>
+        <v>0.29</v>
       </c>
       <c r="H171" t="n">
-        <v>71.88</v>
-      </c>
-      <c r="I171" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.14</v>
+      </c>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>2.647</v>
+        <v>2.07</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>2.466</v>
+        <v>1.992</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8187,39 +8186,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E172" s="10" t="n">
-        <v>0</v>
+        <v>7.51</v>
+      </c>
+      <c r="E172" s="17" t="n">
+        <v>-0.0027</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>675000</v>
+        <v>738300</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.16</v>
+        <v>0.28</v>
       </c>
       <c r="H172" t="n">
-        <v>26.8</v>
-      </c>
-      <c r="I172" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.51</v>
+      </c>
+      <c r="I172" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>0.957</v>
+        <v>7.559</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>1.04</v>
+        <v>7.732</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8232,39 +8231,39 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>7163</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>MSC</t>
+          <t>PJBUMI</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="E173" s="17" t="n">
-        <v>-0.0244</v>
+        <v>4.23</v>
+      </c>
+      <c r="E173" s="15" t="n">
+        <v>0.0024</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>669000</v>
+        <v>701000</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.71</v>
+        <v>1.21</v>
       </c>
       <c r="H173" t="n">
-        <v>42.48</v>
-      </c>
-      <c r="I173" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.3</v>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>1.65</v>
+        <v>4.169</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>1.742</v>
+        <v>4.024</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8277,39 +8276,39 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E174" s="15" t="n">
-        <v>0.008</v>
+        <v>2.79</v>
+      </c>
+      <c r="E174" s="17" t="n">
+        <v>-0.0071</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>641600</v>
+        <v>693100</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="H174" t="n">
-        <v>24.1</v>
-      </c>
-      <c r="I174" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.77</v>
+      </c>
+      <c r="I174" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>1.366</v>
+        <v>2.711</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>1.447</v>
+        <v>2.322</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8322,28 +8321,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>8.25</v>
+        <v>2.77</v>
       </c>
       <c r="E175" s="17" t="n">
-        <v>-0.006</v>
+        <v>-0.0107</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>634800</v>
+        <v>685200</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.36</v>
+        <v>0.47</v>
       </c>
       <c r="H175" t="n">
-        <v>55.27</v>
+        <v>71.88</v>
       </c>
       <c r="I175" s="16" t="inlineStr">
         <is>
@@ -8351,10 +8350,10 @@
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>8.081</v>
+        <v>2.647</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>7.948</v>
+        <v>2.466</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8367,28 +8366,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>SENFONG</t>
+          <t>MSC</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>0.67</v>
+        <v>1.6</v>
       </c>
       <c r="E176" s="17" t="n">
-        <v>-0.0147</v>
+        <v>-0.0244</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>621400</v>
+        <v>669100</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>2.15</v>
+        <v>0.71</v>
       </c>
       <c r="H176" t="n">
-        <v>35.66</v>
+        <v>42.48</v>
       </c>
       <c r="I176" s="16" t="inlineStr">
         <is>
@@ -8396,10 +8395,10 @@
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>0.6850000000000001</v>
+        <v>1.65</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>1.742</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8412,28 +8411,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="E177" s="15" t="n">
-        <v>0.0242</v>
+        <v>0.008</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>600900</v>
+        <v>649300</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
       <c r="H177" t="n">
-        <v>46.44</v>
+        <v>24.1</v>
       </c>
       <c r="I177" s="13" t="inlineStr">
         <is>
@@ -8441,10 +8440,10 @@
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>1.303</v>
+        <v>1.366</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>1.296</v>
+        <v>1.447</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8457,39 +8456,39 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>0376</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>IAB</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="E178" s="10" t="n">
-        <v>0</v>
+        <v>8.25</v>
+      </c>
+      <c r="E178" s="17" t="n">
+        <v>-0.006</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>596600</v>
+        <v>648700</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.24</v>
+        <v>0.37</v>
       </c>
       <c r="H178" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="I178" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.27</v>
+      </c>
+      <c r="I178" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>1.15</v>
+        <v>8.081</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>1.271</v>
+        <v>7.948</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
@@ -8502,28 +8501,28 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>SENFONG</t>
         </is>
       </c>
       <c r="D179" s="9" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="E179" s="15" t="n">
-        <v>0.003</v>
+        <v>0.67</v>
+      </c>
+      <c r="E179" s="17" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F179" s="11" t="n">
-        <v>593500</v>
+        <v>631400</v>
       </c>
       <c r="G179" s="12" t="n">
-        <v>0.09</v>
+        <v>2.19</v>
       </c>
       <c r="H179" t="n">
-        <v>41.4</v>
+        <v>35.66</v>
       </c>
       <c r="I179" s="16" t="inlineStr">
         <is>
@@ -8531,10 +8530,10 @@
         </is>
       </c>
       <c r="J179" s="9" t="n">
-        <v>3.338</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K179" s="9" t="n">
-        <v>3.571</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="14" t="inlineStr"/>
@@ -8547,39 +8546,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>0376</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>KOBAY</t>
+          <t>IAB</t>
         </is>
       </c>
       <c r="D180" s="9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E180" s="17" t="n">
-        <v>-0.009399999999999999</v>
+        <v>1.02</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F180" s="11" t="n">
-        <v>580000</v>
+        <v>604100</v>
       </c>
       <c r="G180" s="12" t="n">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="H180" t="n">
-        <v>46.71</v>
-      </c>
-      <c r="I180" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.9</v>
+      </c>
+      <c r="I180" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J180" s="9" t="n">
-        <v>2.116</v>
+        <v>1.15</v>
       </c>
       <c r="K180" s="9" t="n">
-        <v>2.255</v>
+        <v>1.271</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="14" t="inlineStr"/>
@@ -8592,39 +8591,39 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>ABMB</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D181" s="9" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="E181" s="17" t="n">
-        <v>-0.008800000000000001</v>
+        <v>3.29</v>
+      </c>
+      <c r="E181" s="15" t="n">
+        <v>0.003</v>
       </c>
       <c r="F181" s="11" t="n">
-        <v>567200</v>
+        <v>594100</v>
       </c>
       <c r="G181" s="12" t="n">
-        <v>0.47</v>
+        <v>0.09</v>
       </c>
       <c r="H181" t="n">
-        <v>36.24</v>
-      </c>
-      <c r="I181" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>41.4</v>
+      </c>
+      <c r="I181" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J181" s="9" t="n">
-        <v>4.615</v>
+        <v>3.338</v>
       </c>
       <c r="K181" s="9" t="n">
-        <v>4.762</v>
+        <v>3.571</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="14" t="inlineStr"/>
@@ -8646,19 +8645,19 @@
         </is>
       </c>
       <c r="D182" s="9" t="n">
-        <v>0.88</v>
+        <v>0.875</v>
       </c>
       <c r="E182" s="15" t="n">
-        <v>0.0353</v>
+        <v>0.0294</v>
       </c>
       <c r="F182" s="11" t="n">
-        <v>565100</v>
+        <v>572400</v>
       </c>
       <c r="G182" s="12" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="H182" t="n">
-        <v>39.39</v>
+        <v>38.43</v>
       </c>
       <c r="I182" s="13" t="inlineStr">
         <is>
@@ -8682,39 +8681,39 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>2488</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>ABMB</t>
         </is>
       </c>
       <c r="D183" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E183" s="10" t="n">
-        <v>0</v>
+        <v>4.52</v>
+      </c>
+      <c r="E183" s="17" t="n">
+        <v>-0.008800000000000001</v>
       </c>
       <c r="F183" s="11" t="n">
-        <v>565000</v>
+        <v>567200</v>
       </c>
       <c r="G183" s="12" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="H183" t="n">
-        <v>55.02</v>
-      </c>
-      <c r="I183" s="16" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.24</v>
+      </c>
+      <c r="I183" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J183" s="9" t="n">
-        <v>0.633</v>
+        <v>4.615</v>
       </c>
       <c r="K183" s="9" t="n">
-        <v>0.632</v>
+        <v>4.762</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="14" t="inlineStr"/>
@@ -8727,28 +8726,28 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>CHINHIN</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D184" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E184" s="17" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.635</v>
+      </c>
+      <c r="E184" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F184" s="11" t="n">
-        <v>557200</v>
+        <v>565000</v>
       </c>
       <c r="G184" s="12" t="n">
-        <v>2.03</v>
+        <v>0.52</v>
       </c>
       <c r="H184" t="n">
-        <v>46.12</v>
+        <v>55.02</v>
       </c>
       <c r="I184" s="16" t="inlineStr">
         <is>
@@ -8756,10 +8755,10 @@
         </is>
       </c>
       <c r="J184" s="9" t="n">
-        <v>2.079</v>
+        <v>0.633</v>
       </c>
       <c r="K184" s="9" t="n">
-        <v>2.083</v>
+        <v>0.632</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="14" t="inlineStr"/>
@@ -8772,28 +8771,28 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>TROP</t>
+          <t>HI</t>
         </is>
       </c>
       <c r="D185" s="9" t="n">
-        <v>1.19</v>
+        <v>1.67</v>
       </c>
       <c r="E185" s="15" t="n">
-        <v>0.0171</v>
+        <v>0.0121</v>
       </c>
       <c r="F185" s="11" t="n">
-        <v>538100</v>
+        <v>559000</v>
       </c>
       <c r="G185" s="12" t="n">
-        <v>0.58</v>
+        <v>0.75</v>
       </c>
       <c r="H185" t="n">
-        <v>51</v>
+        <v>35.33</v>
       </c>
       <c r="I185" s="13" t="inlineStr">
         <is>
@@ -8801,10 +8800,10 @@
         </is>
       </c>
       <c r="J185" s="9" t="n">
-        <v>1.186</v>
+        <v>1.739</v>
       </c>
       <c r="K185" s="9" t="n">
-        <v>1.188</v>
+        <v>1.78</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="14" t="inlineStr"/>
@@ -8817,28 +8816,28 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>7076</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>CBIP</t>
+          <t>CHINHIN</t>
         </is>
       </c>
       <c r="D186" s="9" t="n">
-        <v>1.06</v>
+        <v>2.09</v>
       </c>
       <c r="E186" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F186" s="11" t="n">
-        <v>536400</v>
+        <v>558600</v>
       </c>
       <c r="G186" s="12" t="n">
-        <v>17.66</v>
+        <v>2.03</v>
       </c>
       <c r="H186" t="n">
-        <v>40.24</v>
+        <v>53.98</v>
       </c>
       <c r="I186" s="16" t="inlineStr">
         <is>
@@ -8846,10 +8845,10 @@
         </is>
       </c>
       <c r="J186" s="9" t="n">
-        <v>1.073</v>
+        <v>2.081</v>
       </c>
       <c r="K186" s="9" t="n">
-        <v>1.113</v>
+        <v>2.083</v>
       </c>
       <c r="L186" t="inlineStr"/>
       <c r="M186" s="14" t="inlineStr"/>
@@ -8862,28 +8861,28 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>TROP</t>
         </is>
       </c>
       <c r="D187" s="9" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E187" s="17" t="n">
-        <v>-0.0132</v>
+        <v>1.18</v>
+      </c>
+      <c r="E187" s="15" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F187" s="11" t="n">
-        <v>515300</v>
+        <v>542300</v>
       </c>
       <c r="G187" s="12" t="n">
-        <v>0.24</v>
+        <v>0.58</v>
       </c>
       <c r="H187" t="n">
-        <v>58.54</v>
+        <v>48.65</v>
       </c>
       <c r="I187" s="13" t="inlineStr">
         <is>
@@ -8891,10 +8890,10 @@
         </is>
       </c>
       <c r="J187" s="9" t="n">
-        <v>0.736</v>
+        <v>1.185</v>
       </c>
       <c r="K187" s="9" t="n">
-        <v>0.66</v>
+        <v>1.188</v>
       </c>
       <c r="L187" t="inlineStr"/>
       <c r="M187" s="14" t="inlineStr"/>
@@ -8907,39 +8906,39 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>ITMAX</t>
+          <t>CBIP</t>
         </is>
       </c>
       <c r="D188" s="9" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="E188" s="17" t="n">
-        <v>-0.0113</v>
+        <v>1.06</v>
+      </c>
+      <c r="E188" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F188" s="11" t="n">
-        <v>511900</v>
+        <v>536400</v>
       </c>
       <c r="G188" s="12" t="n">
-        <v>0.28</v>
+        <v>17.66</v>
       </c>
       <c r="H188" t="n">
-        <v>38.39</v>
-      </c>
-      <c r="I188" s="13" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.24</v>
+      </c>
+      <c r="I188" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J188" s="9" t="n">
-        <v>4.554</v>
+        <v>1.073</v>
       </c>
       <c r="K188" s="9" t="n">
-        <v>4.48</v>
+        <v>1.113</v>
       </c>
       <c r="L188" t="inlineStr"/>
       <c r="M188" s="14" t="inlineStr"/>
@@ -8952,28 +8951,28 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D189" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E189" s="10" t="n">
-        <v>0</v>
+        <v>0.75</v>
+      </c>
+      <c r="E189" s="17" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F189" s="11" t="n">
-        <v>509800</v>
+        <v>519300</v>
       </c>
       <c r="G189" s="12" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="H189" t="n">
-        <v>41.25</v>
+        <v>58.54</v>
       </c>
       <c r="I189" s="13" t="inlineStr">
         <is>
@@ -8981,16 +8980,151 @@
         </is>
       </c>
       <c r="J189" s="9" t="n">
-        <v>2.541</v>
+        <v>0.736</v>
       </c>
       <c r="K189" s="9" t="n">
-        <v>2.662</v>
+        <v>0.66</v>
       </c>
       <c r="L189" t="inlineStr"/>
       <c r="M189" s="14" t="inlineStr"/>
     </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>5309</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>ITMAX</t>
+        </is>
+      </c>
+      <c r="D190" s="9" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="E190" s="17" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="F190" s="11" t="n">
+        <v>514400</v>
+      </c>
+      <c r="G190" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H190" t="n">
+        <v>39.29</v>
+      </c>
+      <c r="I190" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J190" s="9" t="n">
+        <v>4.556</v>
+      </c>
+      <c r="K190" s="9" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="L190" t="inlineStr"/>
+      <c r="M190" s="14" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>0325</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="D191" s="9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E191" s="17" t="n">
+        <v>-0.0377</v>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>513900</v>
+      </c>
+      <c r="G191" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H191" t="n">
+        <v>43.1</v>
+      </c>
+      <c r="I191" s="16" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J191" s="9" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="K191" s="9" t="n">
+        <v>1.093</v>
+      </c>
+      <c r="L191" t="inlineStr"/>
+      <c r="M191" s="14" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>6947</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="D192" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E192" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F192" s="11" t="n">
+        <v>513300</v>
+      </c>
+      <c r="G192" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H192" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="I192" s="13" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J192" s="9" t="n">
+        <v>2.541</v>
+      </c>
+      <c r="K192" s="9" t="n">
+        <v>2.662</v>
+      </c>
+      <c r="L192" t="inlineStr"/>
+      <c r="M192" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M189"/>
+  <autoFilter ref="A1:M192"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>